--- a/processing_scripts/Inventory_Processing/TEMPEST_SO4_20260501-20260612.xlsx
+++ b/processing_scripts/Inventory_Processing/TEMPEST_SO4_20260501-20260612.xlsx
@@ -1,1034 +1,1147 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sinet-my.sharepoint.com/personal/readz_si_edu1/Documents/TEMPEST_Porewater/processing_scripts/Inventory_Processing/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_B99231273C496B52D774F671E29F0F5CAADF8C41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2881C378-AD97-4298-A00E-E350FD10AC8A}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sample List" sheetId="1" r:id="rId1"/>
+    <sheet name="Sample List" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="334">
-  <si>
-    <t>TEMPEST Sample List: SO4/Cl/H2S 20260501 - 20260612</t>
-  </si>
-  <si>
-    <t>Sample_Number</t>
-  </si>
-  <si>
-    <t>Sample_ID</t>
-  </si>
-  <si>
-    <t>Plot</t>
-  </si>
-  <si>
-    <t>Collection_Date_YYYYMMDD</t>
-  </si>
-  <si>
-    <t>Timepoint</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>TMP_C_PW_C6_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Pre</t>
-  </si>
-  <si>
-    <t>PW</t>
-  </si>
-  <si>
-    <t>TMP_C_PW_F4_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_C_PW_F4_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_C_PW_H3_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_C_PW_H6_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_C_PW_H6_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>Saltwater</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>Freshwater</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_15cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_D5_15cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_30cm_SO4_20260607_D1_PM</t>
-  </si>
-  <si>
-    <t>D1_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_50cm_SO4_20260607_D1_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_30cm_SO4_20260607_D1_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_30cm_SO4_20260607_D1_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_D5_15cm_SO4_20260607_D1_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_50cm_SO4_20260607_D1_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_SW_SO4_20260608_D2-AM</t>
-  </si>
-  <si>
-    <t>D2-AM</t>
-  </si>
-  <si>
-    <t>SW</t>
-  </si>
-  <si>
-    <t>TMP_FW_SW_SO4_20260608_D2-AM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SW_SO4_20260608_D2-AM</t>
-  </si>
-  <si>
-    <t>Estuary</t>
-  </si>
-  <si>
-    <t>TMP_SW_SW_SO4_20260608_D2-PM</t>
-  </si>
-  <si>
-    <t>D2-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_SW_SO4_20260608_D2-PM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SW_SO4_20260608_D2-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260608_D2-T1</t>
-  </si>
-  <si>
-    <t>D2-T1</t>
-  </si>
-  <si>
-    <t>RO</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260608_D2-T2</t>
-  </si>
-  <si>
-    <t>D2-T2</t>
-  </si>
-  <si>
-    <t>TMP_C_PW_C6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_15cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_D5_15cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_SW_SO4_20260609_D3-AM</t>
-  </si>
-  <si>
-    <t>D3-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_SW_SO4_20260609_D3-AM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SW_SO4_20260609_D3-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260609_D3-Macropore</t>
-  </si>
-  <si>
-    <t>D3-Macropore</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_B4_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_D5_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_E3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_I5_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_D5_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_E3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_I5_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_SW_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_SW_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SW_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260609_D3-T1</t>
-  </si>
-  <si>
-    <t>D3-T1</t>
-  </si>
-  <si>
-    <t>TMP_FW_RO_SO4_20260609_D3-T1</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260609_D3-T2</t>
-  </si>
-  <si>
-    <t>D3-T2</t>
-  </si>
-  <si>
-    <t>TMP_FW_RO_SO4_20260609_D3-T2</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_B4_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_D5_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_I5_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F6_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_D5_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_E3_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_B4_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_D5_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_E3_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_I5_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F6_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_D5_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_E3_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_I5_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_SW_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_SW_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SW_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_B4_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_30cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_D5_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_E3_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_30cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_30cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_30cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_D5_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_30cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_30cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_30cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_I5_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F6_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_SW_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_SW_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SW_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260610_D4-T1</t>
-  </si>
-  <si>
-    <t>D4-T1</t>
-  </si>
-  <si>
-    <t>TMP_FW_RO_SO4_20260610_D4-T1</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260610_D4-T2</t>
-  </si>
-  <si>
-    <t>D4-T2</t>
-  </si>
-  <si>
-    <t>TMP_FW_RO_SO4_20260610_D4-T2</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_B4_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_D5_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_E3_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_I5_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F6_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_B4_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_D5_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_E3_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_I5_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_SW_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_SW_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SW_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_C_PW_C6_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_B4_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_D5_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_E3_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_I5_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_B4_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_D5_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_E3_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_I5_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F6_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_SW_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_SW_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SW_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260611_D5-T1</t>
-  </si>
-  <si>
-    <t>D5-T1</t>
-  </si>
-  <si>
-    <t>TMP_FW_RO_SO4_20260611_D5-T1</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260611_D5-T2</t>
-  </si>
-  <si>
-    <t>D5-T2</t>
-  </si>
-  <si>
-    <t>TMP_FW_RO_SO4_20260611_D5-T2</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="374">
+  <si>
+    <t xml:space="preserve">TEMPEST Sample List: SO4/Cl/H2S 20260501 - 20260612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample_Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collection_Date_YYYYMMDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timepoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_C_PW_C6_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_C_PW_F4_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_C_PW_F4_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_C_PW_H3_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_C_PW_H6_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_C_PW_H6_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saltwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freshwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260607_D1_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D1_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260607_D1_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260607_D1_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260607_D1_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260607_D1_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260607_D1_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_SW_SO4_20260608_D2-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D2-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_SW_SO4_20260608_D2-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_EST_SW_SO4_20260608_D2-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_SW_SO4_20260608_D2-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D2-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_SW_SO4_20260608_D2-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_EST_SW_SO4_20260608_D2-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_RO_SO4_20260608_D2-T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D2-T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_RO_SO4_20260608_D2-T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D2-T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_C_PW_C6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_SW_SO4_20260609_D3-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D3-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_SW_SO4_20260609_D3-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_EST_SW_SO4_20260609_D3-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_RO_SO4_20260609_D3-Macropore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D3-Macropore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_B4_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_D5_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_E3_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_I5_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_E3_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_I5_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_SW_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_SW_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_EST_SW_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_RO_SO4_20260609_D3-T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D3-T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_RO_SO4_20260609_D3-T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_RO_SO4_20260609_D3-T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D3-T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_RO_SO4_20260609_D3-T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_B4_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_D5_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_I5_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F6_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_E3_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_B4_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_D5_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_E3_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_I5_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F6_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_E3_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_I5_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_SW_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_SW_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_EST_SW_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_B4_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_D5_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_E3_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_I5_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F6_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_SW_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_SW_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_EST_SW_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_RO_SO4_20260610_D4-T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D4-T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_RO_SO4_20260610_D4-T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_RO_SO4_20260610_D4-T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D4-T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_RO_SO4_20260610_D4-T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_B4_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_D5_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_E3_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_I5_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F6_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_B4_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_E3_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_I5_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_SW_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_SW_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_EST_SW_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_C_PW_C6_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_B4_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_D5_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_E3_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_I5_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_B4_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_E3_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_I5_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F6_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_SW_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_SW_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_EST_SW_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_RO_SO4_20260611_D5-T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D5-T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_RO_SO4_20260611_D5-T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_RO_SO4_20260611_D5-T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D5-T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_RO_SO4_20260611_D5-T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_B4_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_D5_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_E3_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H3_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_I5_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_SW_PW_F6_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_B4_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_E3_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_I5_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP_FW_PW_F6_15cm_SO4_20260612_D6_PM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1064,15 +1177,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1354,20 +1458,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F301"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="63.28515625" customWidth="1"/>
-    <col min="4" max="4" width="32.42578125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1387,8 +1487,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="s">
@@ -1397,7 +1497,7 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>20260604</v>
       </c>
       <c r="E3" t="s">
@@ -1407,8 +1507,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="s">
@@ -1417,7 +1517,7 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>20260604</v>
       </c>
       <c r="E4" t="s">
@@ -1427,8 +1527,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="s">
@@ -1437,7 +1537,7 @@
       <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>20260604</v>
       </c>
       <c r="E5" t="s">
@@ -1447,8 +1547,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="s">
@@ -1457,7 +1557,7 @@
       <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>20260604</v>
       </c>
       <c r="E6" t="s">
@@ -1467,8 +1567,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="7">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="s">
@@ -1477,7 +1577,7 @@
       <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>20260604</v>
       </c>
       <c r="E7" t="s">
@@ -1487,8 +1587,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="s">
@@ -1497,7 +1597,7 @@
       <c r="C8" t="s">
         <v>8</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>20260604</v>
       </c>
       <c r="E8" t="s">
@@ -1507,8 +1607,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9">
+    <row r="9">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="s">
@@ -1517,7 +1617,7 @@
       <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>20260604</v>
       </c>
       <c r="E9" t="s">
@@ -1527,8 +1627,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10">
+    <row r="10">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="s">
@@ -1537,7 +1637,7 @@
       <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>20260604</v>
       </c>
       <c r="E10" t="s">
@@ -1547,8 +1647,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11">
+    <row r="11">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="s">
@@ -1557,7 +1657,7 @@
       <c r="C11" t="s">
         <v>17</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>20260604</v>
       </c>
       <c r="E11" t="s">
@@ -1567,8 +1667,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12">
+    <row r="12">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="s">
@@ -1577,7 +1677,7 @@
       <c r="C12" t="s">
         <v>17</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>20260604</v>
       </c>
       <c r="E12" t="s">
@@ -1587,8 +1687,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13">
+    <row r="13">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="s">
@@ -1597,7 +1697,7 @@
       <c r="C13" t="s">
         <v>17</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>20260604</v>
       </c>
       <c r="E13" t="s">
@@ -1607,8 +1707,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14">
+    <row r="14">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="s">
@@ -1617,7 +1717,7 @@
       <c r="C14" t="s">
         <v>17</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>20260604</v>
       </c>
       <c r="E14" t="s">
@@ -1627,8 +1727,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15">
+    <row r="15">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="s">
@@ -1637,7 +1737,7 @@
       <c r="C15" t="s">
         <v>17</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>20260604</v>
       </c>
       <c r="E15" t="s">
@@ -1647,8 +1747,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16">
+    <row r="16">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="s">
@@ -1657,7 +1757,7 @@
       <c r="C16" t="s">
         <v>25</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>20260604</v>
       </c>
       <c r="E16" t="s">
@@ -1667,8 +1767,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17">
+    <row r="17">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="s">
@@ -1677,7 +1777,7 @@
       <c r="C17" t="s">
         <v>25</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>20260604</v>
       </c>
       <c r="E17" t="s">
@@ -1687,8 +1787,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18">
+    <row r="18">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="s">
@@ -1697,7 +1797,7 @@
       <c r="C18" t="s">
         <v>25</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>20260604</v>
       </c>
       <c r="E18" t="s">
@@ -1707,8 +1807,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19">
+    <row r="19">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="s">
@@ -1717,7 +1817,7 @@
       <c r="C19" t="s">
         <v>25</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>20260604</v>
       </c>
       <c r="E19" t="s">
@@ -1727,8 +1827,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20">
+    <row r="20">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="s">
@@ -1737,7 +1837,7 @@
       <c r="C20" t="s">
         <v>25</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>20260604</v>
       </c>
       <c r="E20" t="s">
@@ -1747,8 +1847,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21">
+    <row r="21">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="s">
@@ -1757,7 +1857,7 @@
       <c r="C21" t="s">
         <v>25</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>20260604</v>
       </c>
       <c r="E21" t="s">
@@ -1767,8 +1867,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22">
+    <row r="22">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="s">
@@ -1777,7 +1877,7 @@
       <c r="C22" t="s">
         <v>25</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>20260604</v>
       </c>
       <c r="E22" t="s">
@@ -1787,8 +1887,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23">
+    <row r="23">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="s">
@@ -1797,7 +1897,7 @@
       <c r="C23" t="s">
         <v>25</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>20260604</v>
       </c>
       <c r="E23" t="s">
@@ -1807,8 +1907,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24">
+    <row r="24">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="s">
@@ -1817,7 +1917,7 @@
       <c r="C24" t="s">
         <v>25</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>20260604</v>
       </c>
       <c r="E24" t="s">
@@ -1827,8 +1927,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25">
+    <row r="25">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="s">
@@ -1837,7 +1937,7 @@
       <c r="C25" t="s">
         <v>17</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>20260607</v>
       </c>
       <c r="E25" t="s">
@@ -1847,8 +1947,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26">
+    <row r="26">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="s">
@@ -1857,7 +1957,7 @@
       <c r="C26" t="s">
         <v>17</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>20260607</v>
       </c>
       <c r="E26" t="s">
@@ -1867,8 +1967,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27">
+    <row r="27">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="s">
@@ -1877,7 +1977,7 @@
       <c r="C27" t="s">
         <v>17</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>20260607</v>
       </c>
       <c r="E27" t="s">
@@ -1887,8 +1987,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28">
+    <row r="28">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="s">
@@ -1897,7 +1997,7 @@
       <c r="C28" t="s">
         <v>17</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>20260607</v>
       </c>
       <c r="E28" t="s">
@@ -1907,8 +2007,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29">
+    <row r="29">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="s">
@@ -1917,7 +2017,7 @@
       <c r="C29" t="s">
         <v>25</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>20260607</v>
       </c>
       <c r="E29" t="s">
@@ -1927,8 +2027,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30">
+    <row r="30">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="s">
@@ -1937,7 +2037,7 @@
       <c r="C30" t="s">
         <v>25</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>20260607</v>
       </c>
       <c r="E30" t="s">
@@ -1947,8 +2047,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31">
+    <row r="31">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="s">
@@ -1957,7 +2057,7 @@
       <c r="C31" t="s">
         <v>17</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>20260608</v>
       </c>
       <c r="E31" t="s">
@@ -1967,8 +2067,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32">
+    <row r="32">
+      <c r="A32" t="n">
         <v>30</v>
       </c>
       <c r="B32" t="s">
@@ -1977,7 +2077,7 @@
       <c r="C32" t="s">
         <v>25</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>20260608</v>
       </c>
       <c r="E32" t="s">
@@ -1987,8 +2087,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33">
+    <row r="33">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
       <c r="B33" t="s">
@@ -1997,7 +2097,7 @@
       <c r="C33" t="s">
         <v>46</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>20260608</v>
       </c>
       <c r="E33" t="s">
@@ -2007,8 +2107,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34">
+    <row r="34">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
       <c r="B34" t="s">
@@ -2017,7 +2117,7 @@
       <c r="C34" t="s">
         <v>17</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>20260608</v>
       </c>
       <c r="E34" t="s">
@@ -2027,8 +2127,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35">
+    <row r="35">
+      <c r="A35" t="n">
         <v>33</v>
       </c>
       <c r="B35" t="s">
@@ -2037,7 +2137,7 @@
       <c r="C35" t="s">
         <v>25</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>20260608</v>
       </c>
       <c r="E35" t="s">
@@ -2047,8 +2147,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36">
+    <row r="36">
+      <c r="A36" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="s">
@@ -2057,7 +2157,7 @@
       <c r="C36" t="s">
         <v>46</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>20260608</v>
       </c>
       <c r="E36" t="s">
@@ -2067,8 +2167,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37">
+    <row r="37">
+      <c r="A37" t="n">
         <v>35</v>
       </c>
       <c r="B37" t="s">
@@ -2077,7 +2177,7 @@
       <c r="C37" t="s">
         <v>17</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>20260608</v>
       </c>
       <c r="E37" t="s">
@@ -2087,8 +2187,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38">
+    <row r="38">
+      <c r="A38" t="n">
         <v>36</v>
       </c>
       <c r="B38" t="s">
@@ -2097,7 +2197,7 @@
       <c r="C38" t="s">
         <v>17</v>
       </c>
-      <c r="D38">
+      <c r="D38" t="n">
         <v>20260608</v>
       </c>
       <c r="E38" t="s">
@@ -2107,8 +2207,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39">
+    <row r="39">
+      <c r="A39" t="n">
         <v>37</v>
       </c>
       <c r="B39" t="s">
@@ -2117,7 +2217,7 @@
       <c r="C39" t="s">
         <v>8</v>
       </c>
-      <c r="D39">
+      <c r="D39" t="n">
         <v>20260608</v>
       </c>
       <c r="E39" t="s">
@@ -2127,8 +2227,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40">
+    <row r="40">
+      <c r="A40" t="n">
         <v>38</v>
       </c>
       <c r="B40" t="s">
@@ -2137,7 +2237,7 @@
       <c r="C40" t="s">
         <v>17</v>
       </c>
-      <c r="D40">
+      <c r="D40" t="n">
         <v>20260608</v>
       </c>
       <c r="E40" t="s">
@@ -2147,8 +2247,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41">
+    <row r="41">
+      <c r="A41" t="n">
         <v>39</v>
       </c>
       <c r="B41" t="s">
@@ -2157,7 +2257,7 @@
       <c r="C41" t="s">
         <v>17</v>
       </c>
-      <c r="D41">
+      <c r="D41" t="n">
         <v>20260608</v>
       </c>
       <c r="E41" t="s">
@@ -2167,8 +2267,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42">
+    <row r="42">
+      <c r="A42" t="n">
         <v>40</v>
       </c>
       <c r="B42" t="s">
@@ -2177,7 +2277,7 @@
       <c r="C42" t="s">
         <v>17</v>
       </c>
-      <c r="D42">
+      <c r="D42" t="n">
         <v>20260608</v>
       </c>
       <c r="E42" t="s">
@@ -2187,8 +2287,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43">
+    <row r="43">
+      <c r="A43" t="n">
         <v>41</v>
       </c>
       <c r="B43" t="s">
@@ -2197,7 +2297,7 @@
       <c r="C43" t="s">
         <v>17</v>
       </c>
-      <c r="D43">
+      <c r="D43" t="n">
         <v>20260608</v>
       </c>
       <c r="E43" t="s">
@@ -2207,8 +2307,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44">
+    <row r="44">
+      <c r="A44" t="n">
         <v>42</v>
       </c>
       <c r="B44" t="s">
@@ -2217,7 +2317,7 @@
       <c r="C44" t="s">
         <v>17</v>
       </c>
-      <c r="D44">
+      <c r="D44" t="n">
         <v>20260608</v>
       </c>
       <c r="E44" t="s">
@@ -2227,8 +2327,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45">
+    <row r="45">
+      <c r="A45" t="n">
         <v>43</v>
       </c>
       <c r="B45" t="s">
@@ -2237,7 +2337,7 @@
       <c r="C45" t="s">
         <v>17</v>
       </c>
-      <c r="D45">
+      <c r="D45" t="n">
         <v>20260608</v>
       </c>
       <c r="E45" t="s">
@@ -2247,8 +2347,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46">
+    <row r="46">
+      <c r="A46" t="n">
         <v>44</v>
       </c>
       <c r="B46" t="s">
@@ -2257,7 +2357,7 @@
       <c r="C46" t="s">
         <v>17</v>
       </c>
-      <c r="D46">
+      <c r="D46" t="n">
         <v>20260608</v>
       </c>
       <c r="E46" t="s">
@@ -2267,8 +2367,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47">
+    <row r="47">
+      <c r="A47" t="n">
         <v>45</v>
       </c>
       <c r="B47" t="s">
@@ -2277,7 +2377,7 @@
       <c r="C47" t="s">
         <v>17</v>
       </c>
-      <c r="D47">
+      <c r="D47" t="n">
         <v>20260608</v>
       </c>
       <c r="E47" t="s">
@@ -2287,8 +2387,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48">
+    <row r="48">
+      <c r="A48" t="n">
         <v>46</v>
       </c>
       <c r="B48" t="s">
@@ -2297,7 +2397,7 @@
       <c r="C48" t="s">
         <v>25</v>
       </c>
-      <c r="D48">
+      <c r="D48" t="n">
         <v>20260608</v>
       </c>
       <c r="E48" t="s">
@@ -2307,8 +2407,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49">
+    <row r="49">
+      <c r="A49" t="n">
         <v>47</v>
       </c>
       <c r="B49" t="s">
@@ -2317,7 +2417,7 @@
       <c r="C49" t="s">
         <v>25</v>
       </c>
-      <c r="D49">
+      <c r="D49" t="n">
         <v>20260608</v>
       </c>
       <c r="E49" t="s">
@@ -2327,8 +2427,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50">
+    <row r="50">
+      <c r="A50" t="n">
         <v>48</v>
       </c>
       <c r="B50" t="s">
@@ -2337,7 +2437,7 @@
       <c r="C50" t="s">
         <v>25</v>
       </c>
-      <c r="D50">
+      <c r="D50" t="n">
         <v>20260608</v>
       </c>
       <c r="E50" t="s">
@@ -2347,8 +2447,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51">
+    <row r="51">
+      <c r="A51" t="n">
         <v>49</v>
       </c>
       <c r="B51" t="s">
@@ -2357,7 +2457,7 @@
       <c r="C51" t="s">
         <v>25</v>
       </c>
-      <c r="D51">
+      <c r="D51" t="n">
         <v>20260608</v>
       </c>
       <c r="E51" t="s">
@@ -2367,8 +2467,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52">
+    <row r="52">
+      <c r="A52" t="n">
         <v>50</v>
       </c>
       <c r="B52" t="s">
@@ -2377,7 +2477,7 @@
       <c r="C52" t="s">
         <v>25</v>
       </c>
-      <c r="D52">
+      <c r="D52" t="n">
         <v>20260608</v>
       </c>
       <c r="E52" t="s">
@@ -2387,8 +2487,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53">
+    <row r="53">
+      <c r="A53" t="n">
         <v>51</v>
       </c>
       <c r="B53" t="s">
@@ -2397,7 +2497,7 @@
       <c r="C53" t="s">
         <v>25</v>
       </c>
-      <c r="D53">
+      <c r="D53" t="n">
         <v>20260608</v>
       </c>
       <c r="E53" t="s">
@@ -2407,8 +2507,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54">
+    <row r="54">
+      <c r="A54" t="n">
         <v>52</v>
       </c>
       <c r="B54" t="s">
@@ -2417,7 +2517,7 @@
       <c r="C54" t="s">
         <v>25</v>
       </c>
-      <c r="D54">
+      <c r="D54" t="n">
         <v>20260608</v>
       </c>
       <c r="E54" t="s">
@@ -2427,8 +2527,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55">
+    <row r="55">
+      <c r="A55" t="n">
         <v>53</v>
       </c>
       <c r="B55" t="s">
@@ -2437,7 +2537,7 @@
       <c r="C55" t="s">
         <v>25</v>
       </c>
-      <c r="D55">
+      <c r="D55" t="n">
         <v>20260608</v>
       </c>
       <c r="E55" t="s">
@@ -2447,8 +2547,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56">
+    <row r="56">
+      <c r="A56" t="n">
         <v>54</v>
       </c>
       <c r="B56" t="s">
@@ -2457,7 +2557,7 @@
       <c r="C56" t="s">
         <v>25</v>
       </c>
-      <c r="D56">
+      <c r="D56" t="n">
         <v>20260608</v>
       </c>
       <c r="E56" t="s">
@@ -2467,8 +2567,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57">
+    <row r="57">
+      <c r="A57" t="n">
         <v>55</v>
       </c>
       <c r="B57" t="s">
@@ -2477,7 +2577,7 @@
       <c r="C57" t="s">
         <v>25</v>
       </c>
-      <c r="D57">
+      <c r="D57" t="n">
         <v>20260608</v>
       </c>
       <c r="E57" t="s">
@@ -2487,8 +2587,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58">
+    <row r="58">
+      <c r="A58" t="n">
         <v>56</v>
       </c>
       <c r="B58" t="s">
@@ -2497,7 +2597,7 @@
       <c r="C58" t="s">
         <v>25</v>
       </c>
-      <c r="D58">
+      <c r="D58" t="n">
         <v>20260608</v>
       </c>
       <c r="E58" t="s">
@@ -2507,8 +2607,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59">
+    <row r="59">
+      <c r="A59" t="n">
         <v>57</v>
       </c>
       <c r="B59" t="s">
@@ -2517,7 +2617,7 @@
       <c r="C59" t="s">
         <v>25</v>
       </c>
-      <c r="D59">
+      <c r="D59" t="n">
         <v>20260608</v>
       </c>
       <c r="E59" t="s">
@@ -2527,8 +2627,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60">
+    <row r="60">
+      <c r="A60" t="n">
         <v>58</v>
       </c>
       <c r="B60" t="s">
@@ -2537,7 +2637,7 @@
       <c r="C60" t="s">
         <v>17</v>
       </c>
-      <c r="D60">
+      <c r="D60" t="n">
         <v>20260609</v>
       </c>
       <c r="E60" t="s">
@@ -2547,8 +2647,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61">
+    <row r="61">
+      <c r="A61" t="n">
         <v>59</v>
       </c>
       <c r="B61" t="s">
@@ -2557,7 +2657,7 @@
       <c r="C61" t="s">
         <v>25</v>
       </c>
-      <c r="D61">
+      <c r="D61" t="n">
         <v>20260609</v>
       </c>
       <c r="E61" t="s">
@@ -2567,8 +2667,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62">
+    <row r="62">
+      <c r="A62" t="n">
         <v>60</v>
       </c>
       <c r="B62" t="s">
@@ -2577,7 +2677,7 @@
       <c r="C62" t="s">
         <v>46</v>
       </c>
-      <c r="D62">
+      <c r="D62" t="n">
         <v>20260609</v>
       </c>
       <c r="E62" t="s">
@@ -2587,8 +2687,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63">
+    <row r="63">
+      <c r="A63" t="n">
         <v>61</v>
       </c>
       <c r="B63" t="s">
@@ -2597,7 +2697,7 @@
       <c r="C63" t="s">
         <v>17</v>
       </c>
-      <c r="D63">
+      <c r="D63" t="n">
         <v>20260609</v>
       </c>
       <c r="E63" t="s">
@@ -2607,8 +2707,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64">
+    <row r="64">
+      <c r="A64" t="n">
         <v>62</v>
       </c>
       <c r="B64" t="s">
@@ -2617,7 +2717,7 @@
       <c r="C64" t="s">
         <v>17</v>
       </c>
-      <c r="D64">
+      <c r="D64" t="n">
         <v>20260609</v>
       </c>
       <c r="E64" t="s">
@@ -2627,8 +2727,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65">
+    <row r="65">
+      <c r="A65" t="n">
         <v>63</v>
       </c>
       <c r="B65" t="s">
@@ -2637,7 +2737,7 @@
       <c r="C65" t="s">
         <v>17</v>
       </c>
-      <c r="D65">
+      <c r="D65" t="n">
         <v>20260609</v>
       </c>
       <c r="E65" t="s">
@@ -2647,8 +2747,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66">
+    <row r="66">
+      <c r="A66" t="n">
         <v>64</v>
       </c>
       <c r="B66" t="s">
@@ -2657,7 +2757,7 @@
       <c r="C66" t="s">
         <v>17</v>
       </c>
-      <c r="D66">
+      <c r="D66" t="n">
         <v>20260609</v>
       </c>
       <c r="E66" t="s">
@@ -2667,8 +2767,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67">
+    <row r="67">
+      <c r="A67" t="n">
         <v>65</v>
       </c>
       <c r="B67" t="s">
@@ -2677,7 +2777,7 @@
       <c r="C67" t="s">
         <v>17</v>
       </c>
-      <c r="D67">
+      <c r="D67" t="n">
         <v>20260609</v>
       </c>
       <c r="E67" t="s">
@@ -2687,8 +2787,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68">
+    <row r="68">
+      <c r="A68" t="n">
         <v>66</v>
       </c>
       <c r="B68" t="s">
@@ -2697,7 +2797,7 @@
       <c r="C68" t="s">
         <v>17</v>
       </c>
-      <c r="D68">
+      <c r="D68" t="n">
         <v>20260609</v>
       </c>
       <c r="E68" t="s">
@@ -2707,8 +2807,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69">
+    <row r="69">
+      <c r="A69" t="n">
         <v>67</v>
       </c>
       <c r="B69" t="s">
@@ -2717,7 +2817,7 @@
       <c r="C69" t="s">
         <v>17</v>
       </c>
-      <c r="D69">
+      <c r="D69" t="n">
         <v>20260609</v>
       </c>
       <c r="E69" t="s">
@@ -2727,8 +2827,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70">
+    <row r="70">
+      <c r="A70" t="n">
         <v>68</v>
       </c>
       <c r="B70" t="s">
@@ -2737,7 +2837,7 @@
       <c r="C70" t="s">
         <v>17</v>
       </c>
-      <c r="D70">
+      <c r="D70" t="n">
         <v>20260609</v>
       </c>
       <c r="E70" t="s">
@@ -2747,8 +2847,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71">
+    <row r="71">
+      <c r="A71" t="n">
         <v>69</v>
       </c>
       <c r="B71" t="s">
@@ -2757,7 +2857,7 @@
       <c r="C71" t="s">
         <v>17</v>
       </c>
-      <c r="D71">
+      <c r="D71" t="n">
         <v>20260609</v>
       </c>
       <c r="E71" t="s">
@@ -2767,8 +2867,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72">
+    <row r="72">
+      <c r="A72" t="n">
         <v>70</v>
       </c>
       <c r="B72" t="s">
@@ -2777,7 +2877,7 @@
       <c r="C72" t="s">
         <v>17</v>
       </c>
-      <c r="D72">
+      <c r="D72" t="n">
         <v>20260609</v>
       </c>
       <c r="E72" t="s">
@@ -2787,8 +2887,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73">
+    <row r="73">
+      <c r="A73" t="n">
         <v>71</v>
       </c>
       <c r="B73" t="s">
@@ -2797,7 +2897,7 @@
       <c r="C73" t="s">
         <v>17</v>
       </c>
-      <c r="D73">
+      <c r="D73" t="n">
         <v>20260609</v>
       </c>
       <c r="E73" t="s">
@@ -2807,8 +2907,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74">
+    <row r="74">
+      <c r="A74" t="n">
         <v>72</v>
       </c>
       <c r="B74" t="s">
@@ -2817,7 +2917,7 @@
       <c r="C74" t="s">
         <v>17</v>
       </c>
-      <c r="D74">
+      <c r="D74" t="n">
         <v>20260609</v>
       </c>
       <c r="E74" t="s">
@@ -2827,8 +2927,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75">
+    <row r="75">
+      <c r="A75" t="n">
         <v>73</v>
       </c>
       <c r="B75" t="s">
@@ -2837,7 +2937,7 @@
       <c r="C75" t="s">
         <v>17</v>
       </c>
-      <c r="D75">
+      <c r="D75" t="n">
         <v>20260609</v>
       </c>
       <c r="E75" t="s">
@@ -2847,8 +2947,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76">
+    <row r="76">
+      <c r="A76" t="n">
         <v>74</v>
       </c>
       <c r="B76" t="s">
@@ -2857,7 +2957,7 @@
       <c r="C76" t="s">
         <v>17</v>
       </c>
-      <c r="D76">
+      <c r="D76" t="n">
         <v>20260609</v>
       </c>
       <c r="E76" t="s">
@@ -2867,8 +2967,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77">
+    <row r="77">
+      <c r="A77" t="n">
         <v>75</v>
       </c>
       <c r="B77" t="s">
@@ -2877,7 +2977,7 @@
       <c r="C77" t="s">
         <v>17</v>
       </c>
-      <c r="D77">
+      <c r="D77" t="n">
         <v>20260609</v>
       </c>
       <c r="E77" t="s">
@@ -2887,8 +2987,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78">
+    <row r="78">
+      <c r="A78" t="n">
         <v>76</v>
       </c>
       <c r="B78" t="s">
@@ -2897,7 +2997,7 @@
       <c r="C78" t="s">
         <v>17</v>
       </c>
-      <c r="D78">
+      <c r="D78" t="n">
         <v>20260609</v>
       </c>
       <c r="E78" t="s">
@@ -2907,8 +3007,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79">
+    <row r="79">
+      <c r="A79" t="n">
         <v>77</v>
       </c>
       <c r="B79" t="s">
@@ -2917,7 +3017,7 @@
       <c r="C79" t="s">
         <v>25</v>
       </c>
-      <c r="D79">
+      <c r="D79" t="n">
         <v>20260609</v>
       </c>
       <c r="E79" t="s">
@@ -2927,8 +3027,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80">
+    <row r="80">
+      <c r="A80" t="n">
         <v>78</v>
       </c>
       <c r="B80" t="s">
@@ -2937,7 +3037,7 @@
       <c r="C80" t="s">
         <v>25</v>
       </c>
-      <c r="D80">
+      <c r="D80" t="n">
         <v>20260609</v>
       </c>
       <c r="E80" t="s">
@@ -2947,8 +3047,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81">
+    <row r="81">
+      <c r="A81" t="n">
         <v>79</v>
       </c>
       <c r="B81" t="s">
@@ -2957,7 +3057,7 @@
       <c r="C81" t="s">
         <v>25</v>
       </c>
-      <c r="D81">
+      <c r="D81" t="n">
         <v>20260609</v>
       </c>
       <c r="E81" t="s">
@@ -2967,8 +3067,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82">
+    <row r="82">
+      <c r="A82" t="n">
         <v>80</v>
       </c>
       <c r="B82" t="s">
@@ -2977,7 +3077,7 @@
       <c r="C82" t="s">
         <v>25</v>
       </c>
-      <c r="D82">
+      <c r="D82" t="n">
         <v>20260609</v>
       </c>
       <c r="E82" t="s">
@@ -2987,8 +3087,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83">
+    <row r="83">
+      <c r="A83" t="n">
         <v>81</v>
       </c>
       <c r="B83" t="s">
@@ -2997,7 +3097,7 @@
       <c r="C83" t="s">
         <v>25</v>
       </c>
-      <c r="D83">
+      <c r="D83" t="n">
         <v>20260609</v>
       </c>
       <c r="E83" t="s">
@@ -3007,8 +3107,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84">
+    <row r="84">
+      <c r="A84" t="n">
         <v>82</v>
       </c>
       <c r="B84" t="s">
@@ -3017,7 +3117,7 @@
       <c r="C84" t="s">
         <v>25</v>
       </c>
-      <c r="D84">
+      <c r="D84" t="n">
         <v>20260609</v>
       </c>
       <c r="E84" t="s">
@@ -3027,8 +3127,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85">
+    <row r="85">
+      <c r="A85" t="n">
         <v>83</v>
       </c>
       <c r="B85" t="s">
@@ -3037,7 +3137,7 @@
       <c r="C85" t="s">
         <v>25</v>
       </c>
-      <c r="D85">
+      <c r="D85" t="n">
         <v>20260609</v>
       </c>
       <c r="E85" t="s">
@@ -3047,8 +3147,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86">
+    <row r="86">
+      <c r="A86" t="n">
         <v>84</v>
       </c>
       <c r="B86" t="s">
@@ -3057,7 +3157,7 @@
       <c r="C86" t="s">
         <v>25</v>
       </c>
-      <c r="D86">
+      <c r="D86" t="n">
         <v>20260609</v>
       </c>
       <c r="E86" t="s">
@@ -3067,8 +3167,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87">
+    <row r="87">
+      <c r="A87" t="n">
         <v>85</v>
       </c>
       <c r="B87" t="s">
@@ -3077,7 +3177,7 @@
       <c r="C87" t="s">
         <v>25</v>
       </c>
-      <c r="D87">
+      <c r="D87" t="n">
         <v>20260609</v>
       </c>
       <c r="E87" t="s">
@@ -3087,8 +3187,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88">
+    <row r="88">
+      <c r="A88" t="n">
         <v>86</v>
       </c>
       <c r="B88" t="s">
@@ -3097,7 +3197,7 @@
       <c r="C88" t="s">
         <v>25</v>
       </c>
-      <c r="D88">
+      <c r="D88" t="n">
         <v>20260609</v>
       </c>
       <c r="E88" t="s">
@@ -3107,8 +3207,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89">
+    <row r="89">
+      <c r="A89" t="n">
         <v>87</v>
       </c>
       <c r="B89" t="s">
@@ -3117,7 +3217,7 @@
       <c r="C89" t="s">
         <v>25</v>
       </c>
-      <c r="D89">
+      <c r="D89" t="n">
         <v>20260609</v>
       </c>
       <c r="E89" t="s">
@@ -3127,8 +3227,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90">
+    <row r="90">
+      <c r="A90" t="n">
         <v>88</v>
       </c>
       <c r="B90" t="s">
@@ -3137,7 +3237,7 @@
       <c r="C90" t="s">
         <v>25</v>
       </c>
-      <c r="D90">
+      <c r="D90" t="n">
         <v>20260609</v>
       </c>
       <c r="E90" t="s">
@@ -3147,8 +3247,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91">
+    <row r="91">
+      <c r="A91" t="n">
         <v>89</v>
       </c>
       <c r="B91" t="s">
@@ -3157,7 +3257,7 @@
       <c r="C91" t="s">
         <v>25</v>
       </c>
-      <c r="D91">
+      <c r="D91" t="n">
         <v>20260609</v>
       </c>
       <c r="E91" t="s">
@@ -3167,8 +3267,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92">
+    <row r="92">
+      <c r="A92" t="n">
         <v>90</v>
       </c>
       <c r="B92" t="s">
@@ -3177,7 +3277,7 @@
       <c r="C92" t="s">
         <v>25</v>
       </c>
-      <c r="D92">
+      <c r="D92" t="n">
         <v>20260609</v>
       </c>
       <c r="E92" t="s">
@@ -3187,8 +3287,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93">
+    <row r="93">
+      <c r="A93" t="n">
         <v>91</v>
       </c>
       <c r="B93" t="s">
@@ -3197,7 +3297,7 @@
       <c r="C93" t="s">
         <v>25</v>
       </c>
-      <c r="D93">
+      <c r="D93" t="n">
         <v>20260609</v>
       </c>
       <c r="E93" t="s">
@@ -3207,8 +3307,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94">
+    <row r="94">
+      <c r="A94" t="n">
         <v>92</v>
       </c>
       <c r="B94" t="s">
@@ -3217,7 +3317,7 @@
       <c r="C94" t="s">
         <v>25</v>
       </c>
-      <c r="D94">
+      <c r="D94" t="n">
         <v>20260609</v>
       </c>
       <c r="E94" t="s">
@@ -3227,8 +3327,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95">
+    <row r="95">
+      <c r="A95" t="n">
         <v>93</v>
       </c>
       <c r="B95" t="s">
@@ -3237,7 +3337,7 @@
       <c r="C95" t="s">
         <v>25</v>
       </c>
-      <c r="D95">
+      <c r="D95" t="n">
         <v>20260609</v>
       </c>
       <c r="E95" t="s">
@@ -3247,8 +3347,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96">
+    <row r="96">
+      <c r="A96" t="n">
         <v>94</v>
       </c>
       <c r="B96" t="s">
@@ -3257,7 +3357,7 @@
       <c r="C96" t="s">
         <v>25</v>
       </c>
-      <c r="D96">
+      <c r="D96" t="n">
         <v>20260609</v>
       </c>
       <c r="E96" t="s">
@@ -3267,8 +3367,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97">
+    <row r="97">
+      <c r="A97" t="n">
         <v>95</v>
       </c>
       <c r="B97" t="s">
@@ -3277,7 +3377,7 @@
       <c r="C97" t="s">
         <v>17</v>
       </c>
-      <c r="D97">
+      <c r="D97" t="n">
         <v>20260609</v>
       </c>
       <c r="E97" t="s">
@@ -3287,8 +3387,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98">
+    <row r="98">
+      <c r="A98" t="n">
         <v>96</v>
       </c>
       <c r="B98" t="s">
@@ -3297,7 +3397,7 @@
       <c r="C98" t="s">
         <v>25</v>
       </c>
-      <c r="D98">
+      <c r="D98" t="n">
         <v>20260609</v>
       </c>
       <c r="E98" t="s">
@@ -3307,8 +3407,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99">
+    <row r="99">
+      <c r="A99" t="n">
         <v>97</v>
       </c>
       <c r="B99" t="s">
@@ -3317,7 +3417,7 @@
       <c r="C99" t="s">
         <v>46</v>
       </c>
-      <c r="D99">
+      <c r="D99" t="n">
         <v>20260609</v>
       </c>
       <c r="E99" t="s">
@@ -3327,8 +3427,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100">
+    <row r="100">
+      <c r="A100" t="n">
         <v>98</v>
       </c>
       <c r="B100" t="s">
@@ -3337,7 +3437,7 @@
       <c r="C100" t="s">
         <v>17</v>
       </c>
-      <c r="D100">
+      <c r="D100" t="n">
         <v>20260609</v>
       </c>
       <c r="E100" t="s">
@@ -3347,8 +3447,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101">
+    <row r="101">
+      <c r="A101" t="n">
         <v>99</v>
       </c>
       <c r="B101" t="s">
@@ -3357,7 +3457,7 @@
       <c r="C101" t="s">
         <v>25</v>
       </c>
-      <c r="D101">
+      <c r="D101" t="n">
         <v>20260609</v>
       </c>
       <c r="E101" t="s">
@@ -3367,8 +3467,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102">
+    <row r="102">
+      <c r="A102" t="n">
         <v>100</v>
       </c>
       <c r="B102" t="s">
@@ -3377,7 +3477,7 @@
       <c r="C102" t="s">
         <v>17</v>
       </c>
-      <c r="D102">
+      <c r="D102" t="n">
         <v>20260609</v>
       </c>
       <c r="E102" t="s">
@@ -3387,8 +3487,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103">
+    <row r="103">
+      <c r="A103" t="n">
         <v>101</v>
       </c>
       <c r="B103" t="s">
@@ -3397,7 +3497,7 @@
       <c r="C103" t="s">
         <v>25</v>
       </c>
-      <c r="D103">
+      <c r="D103" t="n">
         <v>20260609</v>
       </c>
       <c r="E103" t="s">
@@ -3407,8 +3507,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104">
+    <row r="104">
+      <c r="A104" t="n">
         <v>102</v>
       </c>
       <c r="B104" t="s">
@@ -3417,7 +3517,7 @@
       <c r="C104" t="s">
         <v>17</v>
       </c>
-      <c r="D104">
+      <c r="D104" t="n">
         <v>20260609</v>
       </c>
       <c r="E104" t="s">
@@ -3427,8 +3527,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105">
+    <row r="105">
+      <c r="A105" t="n">
         <v>103</v>
       </c>
       <c r="B105" t="s">
@@ -3437,7 +3537,7 @@
       <c r="C105" t="s">
         <v>17</v>
       </c>
-      <c r="D105">
+      <c r="D105" t="n">
         <v>20260609</v>
       </c>
       <c r="E105" t="s">
@@ -3447,8 +3547,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106">
+    <row r="106">
+      <c r="A106" t="n">
         <v>104</v>
       </c>
       <c r="B106" t="s">
@@ -3457,7 +3557,7 @@
       <c r="C106" t="s">
         <v>17</v>
       </c>
-      <c r="D106">
+      <c r="D106" t="n">
         <v>20260609</v>
       </c>
       <c r="E106" t="s">
@@ -3467,8 +3567,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107">
+    <row r="107">
+      <c r="A107" t="n">
         <v>105</v>
       </c>
       <c r="B107" t="s">
@@ -3477,7 +3577,7 @@
       <c r="C107" t="s">
         <v>17</v>
       </c>
-      <c r="D107">
+      <c r="D107" t="n">
         <v>20260609</v>
       </c>
       <c r="E107" t="s">
@@ -3487,8 +3587,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108">
+    <row r="108">
+      <c r="A108" t="n">
         <v>106</v>
       </c>
       <c r="B108" t="s">
@@ -3497,7 +3597,7 @@
       <c r="C108" t="s">
         <v>17</v>
       </c>
-      <c r="D108">
+      <c r="D108" t="n">
         <v>20260609</v>
       </c>
       <c r="E108" t="s">
@@ -3507,8 +3607,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109">
+    <row r="109">
+      <c r="A109" t="n">
         <v>107</v>
       </c>
       <c r="B109" t="s">
@@ -3517,7 +3617,7 @@
       <c r="C109" t="s">
         <v>17</v>
       </c>
-      <c r="D109">
+      <c r="D109" t="n">
         <v>20260609</v>
       </c>
       <c r="E109" t="s">
@@ -3527,8 +3627,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110">
+    <row r="110">
+      <c r="A110" t="n">
         <v>108</v>
       </c>
       <c r="B110" t="s">
@@ -3537,7 +3637,7 @@
       <c r="C110" t="s">
         <v>17</v>
       </c>
-      <c r="D110">
+      <c r="D110" t="n">
         <v>20260609</v>
       </c>
       <c r="E110" t="s">
@@ -3547,8 +3647,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111">
+    <row r="111">
+      <c r="A111" t="n">
         <v>109</v>
       </c>
       <c r="B111" t="s">
@@ -3557,7 +3657,7 @@
       <c r="C111" t="s">
         <v>17</v>
       </c>
-      <c r="D111">
+      <c r="D111" t="n">
         <v>20260609</v>
       </c>
       <c r="E111" t="s">
@@ -3567,8 +3667,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112">
+    <row r="112">
+      <c r="A112" t="n">
         <v>110</v>
       </c>
       <c r="B112" t="s">
@@ -3577,7 +3677,7 @@
       <c r="C112" t="s">
         <v>17</v>
       </c>
-      <c r="D112">
+      <c r="D112" t="n">
         <v>20260609</v>
       </c>
       <c r="E112" t="s">
@@ -3587,8 +3687,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113">
+    <row r="113">
+      <c r="A113" t="n">
         <v>111</v>
       </c>
       <c r="B113" t="s">
@@ -3597,7 +3697,7 @@
       <c r="C113" t="s">
         <v>17</v>
       </c>
-      <c r="D113">
+      <c r="D113" t="n">
         <v>20260609</v>
       </c>
       <c r="E113" t="s">
@@ -3607,8 +3707,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114">
+    <row r="114">
+      <c r="A114" t="n">
         <v>112</v>
       </c>
       <c r="B114" t="s">
@@ -3617,7 +3717,7 @@
       <c r="C114" t="s">
         <v>17</v>
       </c>
-      <c r="D114">
+      <c r="D114" t="n">
         <v>20260609</v>
       </c>
       <c r="E114" t="s">
@@ -3627,8 +3727,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115">
+    <row r="115">
+      <c r="A115" t="n">
         <v>113</v>
       </c>
       <c r="B115" t="s">
@@ -3637,7 +3737,7 @@
       <c r="C115" t="s">
         <v>17</v>
       </c>
-      <c r="D115">
+      <c r="D115" t="n">
         <v>20260609</v>
       </c>
       <c r="E115" t="s">
@@ -3647,8 +3747,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116">
+    <row r="116">
+      <c r="A116" t="n">
         <v>114</v>
       </c>
       <c r="B116" t="s">
@@ -3657,7 +3757,7 @@
       <c r="C116" t="s">
         <v>17</v>
       </c>
-      <c r="D116">
+      <c r="D116" t="n">
         <v>20260609</v>
       </c>
       <c r="E116" t="s">
@@ -3667,8 +3767,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117">
+    <row r="117">
+      <c r="A117" t="n">
         <v>115</v>
       </c>
       <c r="B117" t="s">
@@ -3677,7 +3777,7 @@
       <c r="C117" t="s">
         <v>17</v>
       </c>
-      <c r="D117">
+      <c r="D117" t="n">
         <v>20260609</v>
       </c>
       <c r="E117" t="s">
@@ -3687,8 +3787,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118">
+    <row r="118">
+      <c r="A118" t="n">
         <v>116</v>
       </c>
       <c r="B118" t="s">
@@ -3697,7 +3797,7 @@
       <c r="C118" t="s">
         <v>17</v>
       </c>
-      <c r="D118">
+      <c r="D118" t="n">
         <v>20260609</v>
       </c>
       <c r="E118" t="s">
@@ -3707,8 +3807,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119">
+    <row r="119">
+      <c r="A119" t="n">
         <v>117</v>
       </c>
       <c r="B119" t="s">
@@ -3717,7 +3817,7 @@
       <c r="C119" t="s">
         <v>25</v>
       </c>
-      <c r="D119">
+      <c r="D119" t="n">
         <v>20260609</v>
       </c>
       <c r="E119" t="s">
@@ -3727,8 +3827,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120">
+    <row r="120">
+      <c r="A120" t="n">
         <v>118</v>
       </c>
       <c r="B120" t="s">
@@ -3737,7 +3837,7 @@
       <c r="C120" t="s">
         <v>25</v>
       </c>
-      <c r="D120">
+      <c r="D120" t="n">
         <v>20260609</v>
       </c>
       <c r="E120" t="s">
@@ -3747,8 +3847,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121">
+    <row r="121">
+      <c r="A121" t="n">
         <v>119</v>
       </c>
       <c r="B121" t="s">
@@ -3757,7 +3857,7 @@
       <c r="C121" t="s">
         <v>25</v>
       </c>
-      <c r="D121">
+      <c r="D121" t="n">
         <v>20260609</v>
       </c>
       <c r="E121" t="s">
@@ -3767,8 +3867,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122">
+    <row r="122">
+      <c r="A122" t="n">
         <v>120</v>
       </c>
       <c r="B122" t="s">
@@ -3777,7 +3877,7 @@
       <c r="C122" t="s">
         <v>25</v>
       </c>
-      <c r="D122">
+      <c r="D122" t="n">
         <v>20260609</v>
       </c>
       <c r="E122" t="s">
@@ -3787,8 +3887,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123">
+    <row r="123">
+      <c r="A123" t="n">
         <v>121</v>
       </c>
       <c r="B123" t="s">
@@ -3797,7 +3897,7 @@
       <c r="C123" t="s">
         <v>25</v>
       </c>
-      <c r="D123">
+      <c r="D123" t="n">
         <v>20260609</v>
       </c>
       <c r="E123" t="s">
@@ -3807,8 +3907,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124">
+    <row r="124">
+      <c r="A124" t="n">
         <v>122</v>
       </c>
       <c r="B124" t="s">
@@ -3817,7 +3917,7 @@
       <c r="C124" t="s">
         <v>25</v>
       </c>
-      <c r="D124">
+      <c r="D124" t="n">
         <v>20260609</v>
       </c>
       <c r="E124" t="s">
@@ -3827,8 +3927,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125">
+    <row r="125">
+      <c r="A125" t="n">
         <v>123</v>
       </c>
       <c r="B125" t="s">
@@ -3837,7 +3937,7 @@
       <c r="C125" t="s">
         <v>25</v>
       </c>
-      <c r="D125">
+      <c r="D125" t="n">
         <v>20260609</v>
       </c>
       <c r="E125" t="s">
@@ -3847,8 +3947,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126">
+    <row r="126">
+      <c r="A126" t="n">
         <v>124</v>
       </c>
       <c r="B126" t="s">
@@ -3857,7 +3957,7 @@
       <c r="C126" t="s">
         <v>25</v>
       </c>
-      <c r="D126">
+      <c r="D126" t="n">
         <v>20260609</v>
       </c>
       <c r="E126" t="s">
@@ -3867,8 +3967,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127">
+    <row r="127">
+      <c r="A127" t="n">
         <v>125</v>
       </c>
       <c r="B127" t="s">
@@ -3877,7 +3977,7 @@
       <c r="C127" t="s">
         <v>25</v>
       </c>
-      <c r="D127">
+      <c r="D127" t="n">
         <v>20260609</v>
       </c>
       <c r="E127" t="s">
@@ -3887,8 +3987,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128">
+    <row r="128">
+      <c r="A128" t="n">
         <v>126</v>
       </c>
       <c r="B128" t="s">
@@ -3897,7 +3997,7 @@
       <c r="C128" t="s">
         <v>25</v>
       </c>
-      <c r="D128">
+      <c r="D128" t="n">
         <v>20260609</v>
       </c>
       <c r="E128" t="s">
@@ -3907,8 +4007,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129">
+    <row r="129">
+      <c r="A129" t="n">
         <v>127</v>
       </c>
       <c r="B129" t="s">
@@ -3917,7 +4017,7 @@
       <c r="C129" t="s">
         <v>25</v>
       </c>
-      <c r="D129">
+      <c r="D129" t="n">
         <v>20260609</v>
       </c>
       <c r="E129" t="s">
@@ -3927,8 +4027,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130">
+    <row r="130">
+      <c r="A130" t="n">
         <v>128</v>
       </c>
       <c r="B130" t="s">
@@ -3937,7 +4037,7 @@
       <c r="C130" t="s">
         <v>25</v>
       </c>
-      <c r="D130">
+      <c r="D130" t="n">
         <v>20260609</v>
       </c>
       <c r="E130" t="s">
@@ -3947,8 +4047,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131">
+    <row r="131">
+      <c r="A131" t="n">
         <v>129</v>
       </c>
       <c r="B131" t="s">
@@ -3957,7 +4057,7 @@
       <c r="C131" t="s">
         <v>25</v>
       </c>
-      <c r="D131">
+      <c r="D131" t="n">
         <v>20260609</v>
       </c>
       <c r="E131" t="s">
@@ -3967,8 +4067,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132">
+    <row r="132">
+      <c r="A132" t="n">
         <v>130</v>
       </c>
       <c r="B132" t="s">
@@ -3977,7 +4077,7 @@
       <c r="C132" t="s">
         <v>25</v>
       </c>
-      <c r="D132">
+      <c r="D132" t="n">
         <v>20260609</v>
       </c>
       <c r="E132" t="s">
@@ -3987,8 +4087,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133">
+    <row r="133">
+      <c r="A133" t="n">
         <v>131</v>
       </c>
       <c r="B133" t="s">
@@ -3997,7 +4097,7 @@
       <c r="C133" t="s">
         <v>25</v>
       </c>
-      <c r="D133">
+      <c r="D133" t="n">
         <v>20260609</v>
       </c>
       <c r="E133" t="s">
@@ -4007,8 +4107,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134">
+    <row r="134">
+      <c r="A134" t="n">
         <v>132</v>
       </c>
       <c r="B134" t="s">
@@ -4017,7 +4117,7 @@
       <c r="C134" t="s">
         <v>25</v>
       </c>
-      <c r="D134">
+      <c r="D134" t="n">
         <v>20260609</v>
       </c>
       <c r="E134" t="s">
@@ -4027,8 +4127,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135">
+    <row r="135">
+      <c r="A135" t="n">
         <v>133</v>
       </c>
       <c r="B135" t="s">
@@ -4037,7 +4137,7 @@
       <c r="C135" t="s">
         <v>25</v>
       </c>
-      <c r="D135">
+      <c r="D135" t="n">
         <v>20260609</v>
       </c>
       <c r="E135" t="s">
@@ -4047,8 +4147,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136">
+    <row r="136">
+      <c r="A136" t="n">
         <v>134</v>
       </c>
       <c r="B136" t="s">
@@ -4057,7 +4157,7 @@
       <c r="C136" t="s">
         <v>17</v>
       </c>
-      <c r="D136">
+      <c r="D136" t="n">
         <v>20260610</v>
       </c>
       <c r="E136" t="s">
@@ -4067,8 +4167,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137">
+    <row r="137">
+      <c r="A137" t="n">
         <v>135</v>
       </c>
       <c r="B137" t="s">
@@ -4077,7 +4177,7 @@
       <c r="C137" t="s">
         <v>17</v>
       </c>
-      <c r="D137">
+      <c r="D137" t="n">
         <v>20260610</v>
       </c>
       <c r="E137" t="s">
@@ -4087,8 +4187,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138">
+    <row r="138">
+      <c r="A138" t="n">
         <v>136</v>
       </c>
       <c r="B138" t="s">
@@ -4097,7 +4197,7 @@
       <c r="C138" t="s">
         <v>17</v>
       </c>
-      <c r="D138">
+      <c r="D138" t="n">
         <v>20260610</v>
       </c>
       <c r="E138" t="s">
@@ -4107,8 +4207,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139">
+    <row r="139">
+      <c r="A139" t="n">
         <v>137</v>
       </c>
       <c r="B139" t="s">
@@ -4117,7 +4217,7 @@
       <c r="C139" t="s">
         <v>17</v>
       </c>
-      <c r="D139">
+      <c r="D139" t="n">
         <v>20260610</v>
       </c>
       <c r="E139" t="s">
@@ -4127,8 +4227,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140">
+    <row r="140">
+      <c r="A140" t="n">
         <v>138</v>
       </c>
       <c r="B140" t="s">
@@ -4137,7 +4237,7 @@
       <c r="C140" t="s">
         <v>17</v>
       </c>
-      <c r="D140">
+      <c r="D140" t="n">
         <v>20260610</v>
       </c>
       <c r="E140" t="s">
@@ -4147,8 +4247,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141">
+    <row r="141">
+      <c r="A141" t="n">
         <v>139</v>
       </c>
       <c r="B141" t="s">
@@ -4157,7 +4257,7 @@
       <c r="C141" t="s">
         <v>17</v>
       </c>
-      <c r="D141">
+      <c r="D141" t="n">
         <v>20260610</v>
       </c>
       <c r="E141" t="s">
@@ -4167,8 +4267,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142">
+    <row r="142">
+      <c r="A142" t="n">
         <v>140</v>
       </c>
       <c r="B142" t="s">
@@ -4177,7 +4277,7 @@
       <c r="C142" t="s">
         <v>17</v>
       </c>
-      <c r="D142">
+      <c r="D142" t="n">
         <v>20260610</v>
       </c>
       <c r="E142" t="s">
@@ -4187,8 +4287,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143">
+    <row r="143">
+      <c r="A143" t="n">
         <v>141</v>
       </c>
       <c r="B143" t="s">
@@ -4197,7 +4297,7 @@
       <c r="C143" t="s">
         <v>17</v>
       </c>
-      <c r="D143">
+      <c r="D143" t="n">
         <v>20260610</v>
       </c>
       <c r="E143" t="s">
@@ -4207,8 +4307,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144">
+    <row r="144">
+      <c r="A144" t="n">
         <v>142</v>
       </c>
       <c r="B144" t="s">
@@ -4217,7 +4317,7 @@
       <c r="C144" t="s">
         <v>17</v>
       </c>
-      <c r="D144">
+      <c r="D144" t="n">
         <v>20260610</v>
       </c>
       <c r="E144" t="s">
@@ -4227,8 +4327,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145">
+    <row r="145">
+      <c r="A145" t="n">
         <v>143</v>
       </c>
       <c r="B145" t="s">
@@ -4237,7 +4337,7 @@
       <c r="C145" t="s">
         <v>17</v>
       </c>
-      <c r="D145">
+      <c r="D145" t="n">
         <v>20260610</v>
       </c>
       <c r="E145" t="s">
@@ -4247,8 +4347,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146">
+    <row r="146">
+      <c r="A146" t="n">
         <v>144</v>
       </c>
       <c r="B146" t="s">
@@ -4257,7 +4357,7 @@
       <c r="C146" t="s">
         <v>17</v>
       </c>
-      <c r="D146">
+      <c r="D146" t="n">
         <v>20260610</v>
       </c>
       <c r="E146" t="s">
@@ -4267,8 +4367,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147">
+    <row r="147">
+      <c r="A147" t="n">
         <v>145</v>
       </c>
       <c r="B147" t="s">
@@ -4277,7 +4377,7 @@
       <c r="C147" t="s">
         <v>17</v>
       </c>
-      <c r="D147">
+      <c r="D147" t="n">
         <v>20260610</v>
       </c>
       <c r="E147" t="s">
@@ -4287,8 +4387,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148">
+    <row r="148">
+      <c r="A148" t="n">
         <v>146</v>
       </c>
       <c r="B148" t="s">
@@ -4297,7 +4397,7 @@
       <c r="C148" t="s">
         <v>17</v>
       </c>
-      <c r="D148">
+      <c r="D148" t="n">
         <v>20260610</v>
       </c>
       <c r="E148" t="s">
@@ -4307,8 +4407,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149">
+    <row r="149">
+      <c r="A149" t="n">
         <v>147</v>
       </c>
       <c r="B149" t="s">
@@ -4317,7 +4417,7 @@
       <c r="C149" t="s">
         <v>17</v>
       </c>
-      <c r="D149">
+      <c r="D149" t="n">
         <v>20260610</v>
       </c>
       <c r="E149" t="s">
@@ -4327,8 +4427,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150">
+    <row r="150">
+      <c r="A150" t="n">
         <v>148</v>
       </c>
       <c r="B150" t="s">
@@ -4337,7 +4437,7 @@
       <c r="C150" t="s">
         <v>17</v>
       </c>
-      <c r="D150">
+      <c r="D150" t="n">
         <v>20260610</v>
       </c>
       <c r="E150" t="s">
@@ -4347,8 +4447,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151">
+    <row r="151">
+      <c r="A151" t="n">
         <v>149</v>
       </c>
       <c r="B151" t="s">
@@ -4357,7 +4457,7 @@
       <c r="C151" t="s">
         <v>17</v>
       </c>
-      <c r="D151">
+      <c r="D151" t="n">
         <v>20260610</v>
       </c>
       <c r="E151" t="s">
@@ -4367,8 +4467,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152">
+    <row r="152">
+      <c r="A152" t="n">
         <v>150</v>
       </c>
       <c r="B152" t="s">
@@ -4377,7 +4477,7 @@
       <c r="C152" t="s">
         <v>17</v>
       </c>
-      <c r="D152">
+      <c r="D152" t="n">
         <v>20260610</v>
       </c>
       <c r="E152" t="s">
@@ -4387,8 +4487,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153">
+    <row r="153">
+      <c r="A153" t="n">
         <v>151</v>
       </c>
       <c r="B153" t="s">
@@ -4397,7 +4497,7 @@
       <c r="C153" t="s">
         <v>17</v>
       </c>
-      <c r="D153">
+      <c r="D153" t="n">
         <v>20260610</v>
       </c>
       <c r="E153" t="s">
@@ -4407,8 +4507,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154">
+    <row r="154">
+      <c r="A154" t="n">
         <v>152</v>
       </c>
       <c r="B154" t="s">
@@ -4417,7 +4517,7 @@
       <c r="C154" t="s">
         <v>25</v>
       </c>
-      <c r="D154">
+      <c r="D154" t="n">
         <v>20260610</v>
       </c>
       <c r="E154" t="s">
@@ -4427,8 +4527,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155">
+    <row r="155">
+      <c r="A155" t="n">
         <v>153</v>
       </c>
       <c r="B155" t="s">
@@ -4437,7 +4537,7 @@
       <c r="C155" t="s">
         <v>25</v>
       </c>
-      <c r="D155">
+      <c r="D155" t="n">
         <v>20260610</v>
       </c>
       <c r="E155" t="s">
@@ -4447,8 +4547,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156">
+    <row r="156">
+      <c r="A156" t="n">
         <v>154</v>
       </c>
       <c r="B156" t="s">
@@ -4457,7 +4557,7 @@
       <c r="C156" t="s">
         <v>25</v>
       </c>
-      <c r="D156">
+      <c r="D156" t="n">
         <v>20260610</v>
       </c>
       <c r="E156" t="s">
@@ -4467,8 +4567,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157">
+    <row r="157">
+      <c r="A157" t="n">
         <v>155</v>
       </c>
       <c r="B157" t="s">
@@ -4477,7 +4577,7 @@
       <c r="C157" t="s">
         <v>25</v>
       </c>
-      <c r="D157">
+      <c r="D157" t="n">
         <v>20260610</v>
       </c>
       <c r="E157" t="s">
@@ -4487,8 +4587,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158">
+    <row r="158">
+      <c r="A158" t="n">
         <v>156</v>
       </c>
       <c r="B158" t="s">
@@ -4497,7 +4597,7 @@
       <c r="C158" t="s">
         <v>25</v>
       </c>
-      <c r="D158">
+      <c r="D158" t="n">
         <v>20260610</v>
       </c>
       <c r="E158" t="s">
@@ -4507,8 +4607,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159">
+    <row r="159">
+      <c r="A159" t="n">
         <v>157</v>
       </c>
       <c r="B159" t="s">
@@ -4517,7 +4617,7 @@
       <c r="C159" t="s">
         <v>25</v>
       </c>
-      <c r="D159">
+      <c r="D159" t="n">
         <v>20260610</v>
       </c>
       <c r="E159" t="s">
@@ -4527,8 +4627,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160">
+    <row r="160">
+      <c r="A160" t="n">
         <v>158</v>
       </c>
       <c r="B160" t="s">
@@ -4537,7 +4637,7 @@
       <c r="C160" t="s">
         <v>25</v>
       </c>
-      <c r="D160">
+      <c r="D160" t="n">
         <v>20260610</v>
       </c>
       <c r="E160" t="s">
@@ -4547,8 +4647,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161">
+    <row r="161">
+      <c r="A161" t="n">
         <v>159</v>
       </c>
       <c r="B161" t="s">
@@ -4557,7 +4657,7 @@
       <c r="C161" t="s">
         <v>25</v>
       </c>
-      <c r="D161">
+      <c r="D161" t="n">
         <v>20260610</v>
       </c>
       <c r="E161" t="s">
@@ -4567,8 +4667,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162">
+    <row r="162">
+      <c r="A162" t="n">
         <v>160</v>
       </c>
       <c r="B162" t="s">
@@ -4577,7 +4677,7 @@
       <c r="C162" t="s">
         <v>25</v>
       </c>
-      <c r="D162">
+      <c r="D162" t="n">
         <v>20260610</v>
       </c>
       <c r="E162" t="s">
@@ -4587,8 +4687,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163">
+    <row r="163">
+      <c r="A163" t="n">
         <v>161</v>
       </c>
       <c r="B163" t="s">
@@ -4597,7 +4697,7 @@
       <c r="C163" t="s">
         <v>25</v>
       </c>
-      <c r="D163">
+      <c r="D163" t="n">
         <v>20260610</v>
       </c>
       <c r="E163" t="s">
@@ -4607,8 +4707,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164">
+    <row r="164">
+      <c r="A164" t="n">
         <v>162</v>
       </c>
       <c r="B164" t="s">
@@ -4617,7 +4717,7 @@
       <c r="C164" t="s">
         <v>25</v>
       </c>
-      <c r="D164">
+      <c r="D164" t="n">
         <v>20260610</v>
       </c>
       <c r="E164" t="s">
@@ -4627,8 +4727,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165">
+    <row r="165">
+      <c r="A165" t="n">
         <v>163</v>
       </c>
       <c r="B165" t="s">
@@ -4637,7 +4737,7 @@
       <c r="C165" t="s">
         <v>25</v>
       </c>
-      <c r="D165">
+      <c r="D165" t="n">
         <v>20260610</v>
       </c>
       <c r="E165" t="s">
@@ -4647,8 +4747,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166">
+    <row r="166">
+      <c r="A166" t="n">
         <v>164</v>
       </c>
       <c r="B166" t="s">
@@ -4657,7 +4757,7 @@
       <c r="C166" t="s">
         <v>25</v>
       </c>
-      <c r="D166">
+      <c r="D166" t="n">
         <v>20260610</v>
       </c>
       <c r="E166" t="s">
@@ -4667,8 +4767,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167">
+    <row r="167">
+      <c r="A167" t="n">
         <v>165</v>
       </c>
       <c r="B167" t="s">
@@ -4677,7 +4777,7 @@
       <c r="C167" t="s">
         <v>25</v>
       </c>
-      <c r="D167">
+      <c r="D167" t="n">
         <v>20260610</v>
       </c>
       <c r="E167" t="s">
@@ -4687,8 +4787,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168">
+    <row r="168">
+      <c r="A168" t="n">
         <v>166</v>
       </c>
       <c r="B168" t="s">
@@ -4697,7 +4797,7 @@
       <c r="C168" t="s">
         <v>25</v>
       </c>
-      <c r="D168">
+      <c r="D168" t="n">
         <v>20260610</v>
       </c>
       <c r="E168" t="s">
@@ -4707,8 +4807,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169">
+    <row r="169">
+      <c r="A169" t="n">
         <v>167</v>
       </c>
       <c r="B169" t="s">
@@ -4717,7 +4817,7 @@
       <c r="C169" t="s">
         <v>25</v>
       </c>
-      <c r="D169">
+      <c r="D169" t="n">
         <v>20260610</v>
       </c>
       <c r="E169" t="s">
@@ -4727,8 +4827,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170">
+    <row r="170">
+      <c r="A170" t="n">
         <v>168</v>
       </c>
       <c r="B170" t="s">
@@ -4737,7 +4837,7 @@
       <c r="C170" t="s">
         <v>25</v>
       </c>
-      <c r="D170">
+      <c r="D170" t="n">
         <v>20260610</v>
       </c>
       <c r="E170" t="s">
@@ -4747,8 +4847,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171">
+    <row r="171">
+      <c r="A171" t="n">
         <v>169</v>
       </c>
       <c r="B171" t="s">
@@ -4757,7 +4857,7 @@
       <c r="C171" t="s">
         <v>25</v>
       </c>
-      <c r="D171">
+      <c r="D171" t="n">
         <v>20260610</v>
       </c>
       <c r="E171" t="s">
@@ -4767,8 +4867,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172">
+    <row r="172">
+      <c r="A172" t="n">
         <v>170</v>
       </c>
       <c r="B172" t="s">
@@ -4777,7 +4877,7 @@
       <c r="C172" t="s">
         <v>17</v>
       </c>
-      <c r="D172">
+      <c r="D172" t="n">
         <v>20260610</v>
       </c>
       <c r="E172" t="s">
@@ -4787,8 +4887,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173">
+    <row r="173">
+      <c r="A173" t="n">
         <v>171</v>
       </c>
       <c r="B173" t="s">
@@ -4797,7 +4897,7 @@
       <c r="C173" t="s">
         <v>25</v>
       </c>
-      <c r="D173">
+      <c r="D173" t="n">
         <v>20260610</v>
       </c>
       <c r="E173" t="s">
@@ -4807,8 +4907,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174">
+    <row r="174">
+      <c r="A174" t="n">
         <v>172</v>
       </c>
       <c r="B174" t="s">
@@ -4817,7 +4917,7 @@
       <c r="C174" t="s">
         <v>46</v>
       </c>
-      <c r="D174">
+      <c r="D174" t="n">
         <v>20260610</v>
       </c>
       <c r="E174" t="s">
@@ -4827,8 +4927,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175">
+    <row r="175">
+      <c r="A175" t="n">
         <v>173</v>
       </c>
       <c r="B175" t="s">
@@ -4837,7 +4937,7 @@
       <c r="C175" t="s">
         <v>17</v>
       </c>
-      <c r="D175">
+      <c r="D175" t="n">
         <v>20260610</v>
       </c>
       <c r="E175" t="s">
@@ -4847,8 +4947,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176">
+    <row r="176">
+      <c r="A176" t="n">
         <v>174</v>
       </c>
       <c r="B176" t="s">
@@ -4857,7 +4957,7 @@
       <c r="C176" t="s">
         <v>17</v>
       </c>
-      <c r="D176">
+      <c r="D176" t="n">
         <v>20260610</v>
       </c>
       <c r="E176" t="s">
@@ -4867,8 +4967,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A177">
+    <row r="177">
+      <c r="A177" t="n">
         <v>175</v>
       </c>
       <c r="B177" t="s">
@@ -4877,7 +4977,7 @@
       <c r="C177" t="s">
         <v>17</v>
       </c>
-      <c r="D177">
+      <c r="D177" t="n">
         <v>20260610</v>
       </c>
       <c r="E177" t="s">
@@ -4887,8 +4987,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178">
+    <row r="178">
+      <c r="A178" t="n">
         <v>176</v>
       </c>
       <c r="B178" t="s">
@@ -4897,7 +4997,7 @@
       <c r="C178" t="s">
         <v>17</v>
       </c>
-      <c r="D178">
+      <c r="D178" t="n">
         <v>20260610</v>
       </c>
       <c r="E178" t="s">
@@ -4907,8 +5007,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A179">
+    <row r="179">
+      <c r="A179" t="n">
         <v>177</v>
       </c>
       <c r="B179" t="s">
@@ -4917,7 +5017,7 @@
       <c r="C179" t="s">
         <v>17</v>
       </c>
-      <c r="D179">
+      <c r="D179" t="n">
         <v>20260610</v>
       </c>
       <c r="E179" t="s">
@@ -4927,8 +5027,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A180">
+    <row r="180">
+      <c r="A180" t="n">
         <v>178</v>
       </c>
       <c r="B180" t="s">
@@ -4937,7 +5037,7 @@
       <c r="C180" t="s">
         <v>17</v>
       </c>
-      <c r="D180">
+      <c r="D180" t="n">
         <v>20260610</v>
       </c>
       <c r="E180" t="s">
@@ -4947,8 +5047,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181">
+    <row r="181">
+      <c r="A181" t="n">
         <v>179</v>
       </c>
       <c r="B181" t="s">
@@ -4957,7 +5057,7 @@
       <c r="C181" t="s">
         <v>17</v>
       </c>
-      <c r="D181">
+      <c r="D181" t="n">
         <v>20260610</v>
       </c>
       <c r="E181" t="s">
@@ -4967,8 +5067,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A182">
+    <row r="182">
+      <c r="A182" t="n">
         <v>180</v>
       </c>
       <c r="B182" t="s">
@@ -4977,7 +5077,7 @@
       <c r="C182" t="s">
         <v>17</v>
       </c>
-      <c r="D182">
+      <c r="D182" t="n">
         <v>20260610</v>
       </c>
       <c r="E182" t="s">
@@ -4987,8 +5087,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183">
+    <row r="183">
+      <c r="A183" t="n">
         <v>181</v>
       </c>
       <c r="B183" t="s">
@@ -4997,7 +5097,7 @@
       <c r="C183" t="s">
         <v>17</v>
       </c>
-      <c r="D183">
+      <c r="D183" t="n">
         <v>20260610</v>
       </c>
       <c r="E183" t="s">
@@ -5007,8 +5107,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184">
+    <row r="184">
+      <c r="A184" t="n">
         <v>182</v>
       </c>
       <c r="B184" t="s">
@@ -5017,7 +5117,7 @@
       <c r="C184" t="s">
         <v>17</v>
       </c>
-      <c r="D184">
+      <c r="D184" t="n">
         <v>20260610</v>
       </c>
       <c r="E184" t="s">
@@ -5027,8 +5127,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185">
+    <row r="185">
+      <c r="A185" t="n">
         <v>183</v>
       </c>
       <c r="B185" t="s">
@@ -5037,7 +5137,7 @@
       <c r="C185" t="s">
         <v>17</v>
       </c>
-      <c r="D185">
+      <c r="D185" t="n">
         <v>20260610</v>
       </c>
       <c r="E185" t="s">
@@ -5047,8 +5147,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A186">
+    <row r="186">
+      <c r="A186" t="n">
         <v>184</v>
       </c>
       <c r="B186" t="s">
@@ -5057,7 +5157,7 @@
       <c r="C186" t="s">
         <v>17</v>
       </c>
-      <c r="D186">
+      <c r="D186" t="n">
         <v>20260610</v>
       </c>
       <c r="E186" t="s">
@@ -5067,8 +5167,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187">
+    <row r="187">
+      <c r="A187" t="n">
         <v>185</v>
       </c>
       <c r="B187" t="s">
@@ -5077,7 +5177,7 @@
       <c r="C187" t="s">
         <v>17</v>
       </c>
-      <c r="D187">
+      <c r="D187" t="n">
         <v>20260610</v>
       </c>
       <c r="E187" t="s">
@@ -5087,8 +5187,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188">
+    <row r="188">
+      <c r="A188" t="n">
         <v>186</v>
       </c>
       <c r="B188" t="s">
@@ -5097,7 +5197,7 @@
       <c r="C188" t="s">
         <v>25</v>
       </c>
-      <c r="D188">
+      <c r="D188" t="n">
         <v>20260610</v>
       </c>
       <c r="E188" t="s">
@@ -5107,8 +5207,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189">
+    <row r="189">
+      <c r="A189" t="n">
         <v>187</v>
       </c>
       <c r="B189" t="s">
@@ -5117,7 +5217,7 @@
       <c r="C189" t="s">
         <v>25</v>
       </c>
-      <c r="D189">
+      <c r="D189" t="n">
         <v>20260610</v>
       </c>
       <c r="E189" t="s">
@@ -5127,8 +5227,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190">
+    <row r="190">
+      <c r="A190" t="n">
         <v>188</v>
       </c>
       <c r="B190" t="s">
@@ -5137,7 +5237,7 @@
       <c r="C190" t="s">
         <v>25</v>
       </c>
-      <c r="D190">
+      <c r="D190" t="n">
         <v>20260610</v>
       </c>
       <c r="E190" t="s">
@@ -5147,8 +5247,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A191">
+    <row r="191">
+      <c r="A191" t="n">
         <v>189</v>
       </c>
       <c r="B191" t="s">
@@ -5157,7 +5257,7 @@
       <c r="C191" t="s">
         <v>25</v>
       </c>
-      <c r="D191">
+      <c r="D191" t="n">
         <v>20260610</v>
       </c>
       <c r="E191" t="s">
@@ -5167,8 +5267,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192">
+    <row r="192">
+      <c r="A192" t="n">
         <v>190</v>
       </c>
       <c r="B192" t="s">
@@ -5177,7 +5277,7 @@
       <c r="C192" t="s">
         <v>25</v>
       </c>
-      <c r="D192">
+      <c r="D192" t="n">
         <v>20260610</v>
       </c>
       <c r="E192" t="s">
@@ -5187,8 +5287,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A193">
+    <row r="193">
+      <c r="A193" t="n">
         <v>191</v>
       </c>
       <c r="B193" t="s">
@@ -5197,7 +5297,7 @@
       <c r="C193" t="s">
         <v>25</v>
       </c>
-      <c r="D193">
+      <c r="D193" t="n">
         <v>20260610</v>
       </c>
       <c r="E193" t="s">
@@ -5207,8 +5307,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A194">
+    <row r="194">
+      <c r="A194" t="n">
         <v>192</v>
       </c>
       <c r="B194" t="s">
@@ -5217,7 +5317,7 @@
       <c r="C194" t="s">
         <v>25</v>
       </c>
-      <c r="D194">
+      <c r="D194" t="n">
         <v>20260610</v>
       </c>
       <c r="E194" t="s">
@@ -5227,8 +5327,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A195">
+    <row r="195">
+      <c r="A195" t="n">
         <v>193</v>
       </c>
       <c r="B195" t="s">
@@ -5237,7 +5337,7 @@
       <c r="C195" t="s">
         <v>25</v>
       </c>
-      <c r="D195">
+      <c r="D195" t="n">
         <v>20260610</v>
       </c>
       <c r="E195" t="s">
@@ -5247,8 +5347,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A196">
+    <row r="196">
+      <c r="A196" t="n">
         <v>194</v>
       </c>
       <c r="B196" t="s">
@@ -5257,7 +5357,7 @@
       <c r="C196" t="s">
         <v>25</v>
       </c>
-      <c r="D196">
+      <c r="D196" t="n">
         <v>20260610</v>
       </c>
       <c r="E196" t="s">
@@ -5267,8 +5367,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A197">
+    <row r="197">
+      <c r="A197" t="n">
         <v>195</v>
       </c>
       <c r="B197" t="s">
@@ -5277,7 +5377,7 @@
       <c r="C197" t="s">
         <v>25</v>
       </c>
-      <c r="D197">
+      <c r="D197" t="n">
         <v>20260610</v>
       </c>
       <c r="E197" t="s">
@@ -5287,8 +5387,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A198">
+    <row r="198">
+      <c r="A198" t="n">
         <v>196</v>
       </c>
       <c r="B198" t="s">
@@ -5297,7 +5397,7 @@
       <c r="C198" t="s">
         <v>25</v>
       </c>
-      <c r="D198">
+      <c r="D198" t="n">
         <v>20260610</v>
       </c>
       <c r="E198" t="s">
@@ -5307,8 +5407,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A199">
+    <row r="199">
+      <c r="A199" t="n">
         <v>197</v>
       </c>
       <c r="B199" t="s">
@@ -5317,7 +5417,7 @@
       <c r="C199" t="s">
         <v>25</v>
       </c>
-      <c r="D199">
+      <c r="D199" t="n">
         <v>20260610</v>
       </c>
       <c r="E199" t="s">
@@ -5327,8 +5427,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200">
+    <row r="200">
+      <c r="A200" t="n">
         <v>198</v>
       </c>
       <c r="B200" t="s">
@@ -5337,7 +5437,7 @@
       <c r="C200" t="s">
         <v>25</v>
       </c>
-      <c r="D200">
+      <c r="D200" t="n">
         <v>20260610</v>
       </c>
       <c r="E200" t="s">
@@ -5347,8 +5447,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201">
+    <row r="201">
+      <c r="A201" t="n">
         <v>199</v>
       </c>
       <c r="B201" t="s">
@@ -5357,7 +5457,7 @@
       <c r="C201" t="s">
         <v>25</v>
       </c>
-      <c r="D201">
+      <c r="D201" t="n">
         <v>20260610</v>
       </c>
       <c r="E201" t="s">
@@ -5367,8 +5467,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202">
+    <row r="202">
+      <c r="A202" t="n">
         <v>200</v>
       </c>
       <c r="B202" t="s">
@@ -5377,7 +5477,7 @@
       <c r="C202" t="s">
         <v>25</v>
       </c>
-      <c r="D202">
+      <c r="D202" t="n">
         <v>20260610</v>
       </c>
       <c r="E202" t="s">
@@ -5387,8 +5487,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203">
+    <row r="203">
+      <c r="A203" t="n">
         <v>201</v>
       </c>
       <c r="B203" t="s">
@@ -5397,7 +5497,7 @@
       <c r="C203" t="s">
         <v>25</v>
       </c>
-      <c r="D203">
+      <c r="D203" t="n">
         <v>20260610</v>
       </c>
       <c r="E203" t="s">
@@ -5407,8 +5507,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204">
+    <row r="204">
+      <c r="A204" t="n">
         <v>202</v>
       </c>
       <c r="B204" t="s">
@@ -5417,7 +5517,7 @@
       <c r="C204" t="s">
         <v>25</v>
       </c>
-      <c r="D204">
+      <c r="D204" t="n">
         <v>20260610</v>
       </c>
       <c r="E204" t="s">
@@ -5427,8 +5527,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A205">
+    <row r="205">
+      <c r="A205" t="n">
         <v>203</v>
       </c>
       <c r="B205" t="s">
@@ -5437,7 +5537,7 @@
       <c r="C205" t="s">
         <v>25</v>
       </c>
-      <c r="D205">
+      <c r="D205" t="n">
         <v>20260610</v>
       </c>
       <c r="E205" t="s">
@@ -5447,8 +5547,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206">
+    <row r="206">
+      <c r="A206" t="n">
         <v>204</v>
       </c>
       <c r="B206" t="s">
@@ -5457,7 +5557,7 @@
       <c r="C206" t="s">
         <v>17</v>
       </c>
-      <c r="D206">
+      <c r="D206" t="n">
         <v>20260610</v>
       </c>
       <c r="E206" t="s">
@@ -5467,8 +5567,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207">
+    <row r="207">
+      <c r="A207" t="n">
         <v>205</v>
       </c>
       <c r="B207" t="s">
@@ -5477,7 +5577,7 @@
       <c r="C207" t="s">
         <v>25</v>
       </c>
-      <c r="D207">
+      <c r="D207" t="n">
         <v>20260610</v>
       </c>
       <c r="E207" t="s">
@@ -5487,8 +5587,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208">
+    <row r="208">
+      <c r="A208" t="n">
         <v>206</v>
       </c>
       <c r="B208" t="s">
@@ -5497,7 +5597,7 @@
       <c r="C208" t="s">
         <v>46</v>
       </c>
-      <c r="D208">
+      <c r="D208" t="n">
         <v>20260610</v>
       </c>
       <c r="E208" t="s">
@@ -5507,8 +5607,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209">
+    <row r="209">
+      <c r="A209" t="n">
         <v>207</v>
       </c>
       <c r="B209" t="s">
@@ -5517,7 +5617,7 @@
       <c r="C209" t="s">
         <v>17</v>
       </c>
-      <c r="D209">
+      <c r="D209" t="n">
         <v>20260610</v>
       </c>
       <c r="E209" t="s">
@@ -5527,8 +5627,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A210">
+    <row r="210">
+      <c r="A210" t="n">
         <v>208</v>
       </c>
       <c r="B210" t="s">
@@ -5537,7 +5637,7 @@
       <c r="C210" t="s">
         <v>25</v>
       </c>
-      <c r="D210">
+      <c r="D210" t="n">
         <v>20260610</v>
       </c>
       <c r="E210" t="s">
@@ -5547,8 +5647,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A211">
+    <row r="211">
+      <c r="A211" t="n">
         <v>209</v>
       </c>
       <c r="B211" t="s">
@@ -5557,7 +5657,7 @@
       <c r="C211" t="s">
         <v>17</v>
       </c>
-      <c r="D211">
+      <c r="D211" t="n">
         <v>20260610</v>
       </c>
       <c r="E211" t="s">
@@ -5567,8 +5667,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212">
+    <row r="212">
+      <c r="A212" t="n">
         <v>210</v>
       </c>
       <c r="B212" t="s">
@@ -5577,7 +5677,7 @@
       <c r="C212" t="s">
         <v>25</v>
       </c>
-      <c r="D212">
+      <c r="D212" t="n">
         <v>20260610</v>
       </c>
       <c r="E212" t="s">
@@ -5587,8 +5687,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A213">
+    <row r="213">
+      <c r="A213" t="n">
         <v>211</v>
       </c>
       <c r="B213" t="s">
@@ -5597,7 +5697,7 @@
       <c r="C213" t="s">
         <v>17</v>
       </c>
-      <c r="D213">
+      <c r="D213" t="n">
         <v>20260611</v>
       </c>
       <c r="E213" t="s">
@@ -5607,8 +5707,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A214">
+    <row r="214">
+      <c r="A214" t="n">
         <v>212</v>
       </c>
       <c r="B214" t="s">
@@ -5617,7 +5717,7 @@
       <c r="C214" t="s">
         <v>17</v>
       </c>
-      <c r="D214">
+      <c r="D214" t="n">
         <v>20260611</v>
       </c>
       <c r="E214" t="s">
@@ -5627,8 +5727,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A215">
+    <row r="215">
+      <c r="A215" t="n">
         <v>213</v>
       </c>
       <c r="B215" t="s">
@@ -5637,7 +5737,7 @@
       <c r="C215" t="s">
         <v>17</v>
       </c>
-      <c r="D215">
+      <c r="D215" t="n">
         <v>20260611</v>
       </c>
       <c r="E215" t="s">
@@ -5647,8 +5747,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A216">
+    <row r="216">
+      <c r="A216" t="n">
         <v>214</v>
       </c>
       <c r="B216" t="s">
@@ -5657,7 +5757,7 @@
       <c r="C216" t="s">
         <v>17</v>
       </c>
-      <c r="D216">
+      <c r="D216" t="n">
         <v>20260611</v>
       </c>
       <c r="E216" t="s">
@@ -5667,8 +5767,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A217">
+    <row r="217">
+      <c r="A217" t="n">
         <v>215</v>
       </c>
       <c r="B217" t="s">
@@ -5677,7 +5777,7 @@
       <c r="C217" t="s">
         <v>17</v>
       </c>
-      <c r="D217">
+      <c r="D217" t="n">
         <v>20260611</v>
       </c>
       <c r="E217" t="s">
@@ -5687,8 +5787,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A218">
+    <row r="218">
+      <c r="A218" t="n">
         <v>216</v>
       </c>
       <c r="B218" t="s">
@@ -5697,7 +5797,7 @@
       <c r="C218" t="s">
         <v>17</v>
       </c>
-      <c r="D218">
+      <c r="D218" t="n">
         <v>20260611</v>
       </c>
       <c r="E218" t="s">
@@ -5707,8 +5807,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A219">
+    <row r="219">
+      <c r="A219" t="n">
         <v>217</v>
       </c>
       <c r="B219" t="s">
@@ -5717,7 +5817,7 @@
       <c r="C219" t="s">
         <v>17</v>
       </c>
-      <c r="D219">
+      <c r="D219" t="n">
         <v>20260611</v>
       </c>
       <c r="E219" t="s">
@@ -5727,8 +5827,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A220">
+    <row r="220">
+      <c r="A220" t="n">
         <v>218</v>
       </c>
       <c r="B220" t="s">
@@ -5737,7 +5837,7 @@
       <c r="C220" t="s">
         <v>17</v>
       </c>
-      <c r="D220">
+      <c r="D220" t="n">
         <v>20260611</v>
       </c>
       <c r="E220" t="s">
@@ -5747,8 +5847,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221">
+    <row r="221">
+      <c r="A221" t="n">
         <v>219</v>
       </c>
       <c r="B221" t="s">
@@ -5757,7 +5857,7 @@
       <c r="C221" t="s">
         <v>17</v>
       </c>
-      <c r="D221">
+      <c r="D221" t="n">
         <v>20260611</v>
       </c>
       <c r="E221" t="s">
@@ -5767,8 +5867,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A222">
+    <row r="222">
+      <c r="A222" t="n">
         <v>220</v>
       </c>
       <c r="B222" t="s">
@@ -5777,7 +5877,7 @@
       <c r="C222" t="s">
         <v>17</v>
       </c>
-      <c r="D222">
+      <c r="D222" t="n">
         <v>20260611</v>
       </c>
       <c r="E222" t="s">
@@ -5787,8 +5887,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A223">
+    <row r="223">
+      <c r="A223" t="n">
         <v>221</v>
       </c>
       <c r="B223" t="s">
@@ -5797,7 +5897,7 @@
       <c r="C223" t="s">
         <v>17</v>
       </c>
-      <c r="D223">
+      <c r="D223" t="n">
         <v>20260611</v>
       </c>
       <c r="E223" t="s">
@@ -5807,8 +5907,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A224">
+    <row r="224">
+      <c r="A224" t="n">
         <v>222</v>
       </c>
       <c r="B224" t="s">
@@ -5817,7 +5917,7 @@
       <c r="C224" t="s">
         <v>17</v>
       </c>
-      <c r="D224">
+      <c r="D224" t="n">
         <v>20260611</v>
       </c>
       <c r="E224" t="s">
@@ -5827,8 +5927,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A225">
+    <row r="225">
+      <c r="A225" t="n">
         <v>223</v>
       </c>
       <c r="B225" t="s">
@@ -5837,7 +5937,7 @@
       <c r="C225" t="s">
         <v>17</v>
       </c>
-      <c r="D225">
+      <c r="D225" t="n">
         <v>20260611</v>
       </c>
       <c r="E225" t="s">
@@ -5847,8 +5947,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A226">
+    <row r="226">
+      <c r="A226" t="n">
         <v>224</v>
       </c>
       <c r="B226" t="s">
@@ -5857,7 +5957,7 @@
       <c r="C226" t="s">
         <v>17</v>
       </c>
-      <c r="D226">
+      <c r="D226" t="n">
         <v>20260611</v>
       </c>
       <c r="E226" t="s">
@@ -5867,8 +5967,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A227">
+    <row r="227">
+      <c r="A227" t="n">
         <v>225</v>
       </c>
       <c r="B227" t="s">
@@ -5877,7 +5977,7 @@
       <c r="C227" t="s">
         <v>17</v>
       </c>
-      <c r="D227">
+      <c r="D227" t="n">
         <v>20260611</v>
       </c>
       <c r="E227" t="s">
@@ -5887,8 +5987,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A228">
+    <row r="228">
+      <c r="A228" t="n">
         <v>226</v>
       </c>
       <c r="B228" t="s">
@@ -5897,7 +5997,7 @@
       <c r="C228" t="s">
         <v>17</v>
       </c>
-      <c r="D228">
+      <c r="D228" t="n">
         <v>20260611</v>
       </c>
       <c r="E228" t="s">
@@ -5907,8 +6007,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A229">
+    <row r="229">
+      <c r="A229" t="n">
         <v>227</v>
       </c>
       <c r="B229" t="s">
@@ -5917,7 +6017,7 @@
       <c r="C229" t="s">
         <v>17</v>
       </c>
-      <c r="D229">
+      <c r="D229" t="n">
         <v>20260611</v>
       </c>
       <c r="E229" t="s">
@@ -5927,8 +6027,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A230">
+    <row r="230">
+      <c r="A230" t="n">
         <v>228</v>
       </c>
       <c r="B230" t="s">
@@ -5937,7 +6037,7 @@
       <c r="C230" t="s">
         <v>17</v>
       </c>
-      <c r="D230">
+      <c r="D230" t="n">
         <v>20260611</v>
       </c>
       <c r="E230" t="s">
@@ -5947,8 +6047,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A231">
+    <row r="231">
+      <c r="A231" t="n">
         <v>229</v>
       </c>
       <c r="B231" t="s">
@@ -5957,7 +6057,7 @@
       <c r="C231" t="s">
         <v>17</v>
       </c>
-      <c r="D231">
+      <c r="D231" t="n">
         <v>20260611</v>
       </c>
       <c r="E231" t="s">
@@ -5967,8 +6067,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A232">
+    <row r="232">
+      <c r="A232" t="n">
         <v>230</v>
       </c>
       <c r="B232" t="s">
@@ -5977,7 +6077,7 @@
       <c r="C232" t="s">
         <v>17</v>
       </c>
-      <c r="D232">
+      <c r="D232" t="n">
         <v>20260611</v>
       </c>
       <c r="E232" t="s">
@@ -5987,8 +6087,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A233">
+    <row r="233">
+      <c r="A233" t="n">
         <v>231</v>
       </c>
       <c r="B233" t="s">
@@ -5997,7 +6097,7 @@
       <c r="C233" t="s">
         <v>25</v>
       </c>
-      <c r="D233">
+      <c r="D233" t="n">
         <v>20260611</v>
       </c>
       <c r="E233" t="s">
@@ -6007,8 +6107,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A234">
+    <row r="234">
+      <c r="A234" t="n">
         <v>232</v>
       </c>
       <c r="B234" t="s">
@@ -6017,7 +6117,7 @@
       <c r="C234" t="s">
         <v>25</v>
       </c>
-      <c r="D234">
+      <c r="D234" t="n">
         <v>20260611</v>
       </c>
       <c r="E234" t="s">
@@ -6027,8 +6127,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235">
+    <row r="235">
+      <c r="A235" t="n">
         <v>233</v>
       </c>
       <c r="B235" t="s">
@@ -6037,7 +6137,7 @@
       <c r="C235" t="s">
         <v>25</v>
       </c>
-      <c r="D235">
+      <c r="D235" t="n">
         <v>20260611</v>
       </c>
       <c r="E235" t="s">
@@ -6047,8 +6147,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A236">
+    <row r="236">
+      <c r="A236" t="n">
         <v>234</v>
       </c>
       <c r="B236" t="s">
@@ -6057,7 +6157,7 @@
       <c r="C236" t="s">
         <v>25</v>
       </c>
-      <c r="D236">
+      <c r="D236" t="n">
         <v>20260611</v>
       </c>
       <c r="E236" t="s">
@@ -6067,8 +6167,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A237">
+    <row r="237">
+      <c r="A237" t="n">
         <v>235</v>
       </c>
       <c r="B237" t="s">
@@ -6077,7 +6177,7 @@
       <c r="C237" t="s">
         <v>25</v>
       </c>
-      <c r="D237">
+      <c r="D237" t="n">
         <v>20260611</v>
       </c>
       <c r="E237" t="s">
@@ -6087,8 +6187,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A238">
+    <row r="238">
+      <c r="A238" t="n">
         <v>236</v>
       </c>
       <c r="B238" t="s">
@@ -6097,7 +6197,7 @@
       <c r="C238" t="s">
         <v>25</v>
       </c>
-      <c r="D238">
+      <c r="D238" t="n">
         <v>20260611</v>
       </c>
       <c r="E238" t="s">
@@ -6107,8 +6207,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A239">
+    <row r="239">
+      <c r="A239" t="n">
         <v>237</v>
       </c>
       <c r="B239" t="s">
@@ -6117,7 +6217,7 @@
       <c r="C239" t="s">
         <v>25</v>
       </c>
-      <c r="D239">
+      <c r="D239" t="n">
         <v>20260611</v>
       </c>
       <c r="E239" t="s">
@@ -6127,8 +6227,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A240">
+    <row r="240">
+      <c r="A240" t="n">
         <v>238</v>
       </c>
       <c r="B240" t="s">
@@ -6137,7 +6237,7 @@
       <c r="C240" t="s">
         <v>25</v>
       </c>
-      <c r="D240">
+      <c r="D240" t="n">
         <v>20260611</v>
       </c>
       <c r="E240" t="s">
@@ -6147,8 +6247,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A241">
+    <row r="241">
+      <c r="A241" t="n">
         <v>239</v>
       </c>
       <c r="B241" t="s">
@@ -6157,7 +6257,7 @@
       <c r="C241" t="s">
         <v>25</v>
       </c>
-      <c r="D241">
+      <c r="D241" t="n">
         <v>20260611</v>
       </c>
       <c r="E241" t="s">
@@ -6167,8 +6267,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A242">
+    <row r="242">
+      <c r="A242" t="n">
         <v>240</v>
       </c>
       <c r="B242" t="s">
@@ -6177,7 +6277,7 @@
       <c r="C242" t="s">
         <v>25</v>
       </c>
-      <c r="D242">
+      <c r="D242" t="n">
         <v>20260611</v>
       </c>
       <c r="E242" t="s">
@@ -6187,8 +6287,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A243">
+    <row r="243">
+      <c r="A243" t="n">
         <v>241</v>
       </c>
       <c r="B243" t="s">
@@ -6197,7 +6297,7 @@
       <c r="C243" t="s">
         <v>25</v>
       </c>
-      <c r="D243">
+      <c r="D243" t="n">
         <v>20260611</v>
       </c>
       <c r="E243" t="s">
@@ -6207,8 +6307,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A244">
+    <row r="244">
+      <c r="A244" t="n">
         <v>242</v>
       </c>
       <c r="B244" t="s">
@@ -6217,7 +6317,7 @@
       <c r="C244" t="s">
         <v>25</v>
       </c>
-      <c r="D244">
+      <c r="D244" t="n">
         <v>20260611</v>
       </c>
       <c r="E244" t="s">
@@ -6227,8 +6327,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A245">
+    <row r="245">
+      <c r="A245" t="n">
         <v>243</v>
       </c>
       <c r="B245" t="s">
@@ -6237,7 +6337,7 @@
       <c r="C245" t="s">
         <v>25</v>
       </c>
-      <c r="D245">
+      <c r="D245" t="n">
         <v>20260611</v>
       </c>
       <c r="E245" t="s">
@@ -6247,8 +6347,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A246">
+    <row r="246">
+      <c r="A246" t="n">
         <v>244</v>
       </c>
       <c r="B246" t="s">
@@ -6257,7 +6357,7 @@
       <c r="C246" t="s">
         <v>25</v>
       </c>
-      <c r="D246">
+      <c r="D246" t="n">
         <v>20260611</v>
       </c>
       <c r="E246" t="s">
@@ -6267,8 +6367,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A247">
+    <row r="247">
+      <c r="A247" t="n">
         <v>245</v>
       </c>
       <c r="B247" t="s">
@@ -6277,7 +6377,7 @@
       <c r="C247" t="s">
         <v>25</v>
       </c>
-      <c r="D247">
+      <c r="D247" t="n">
         <v>20260611</v>
       </c>
       <c r="E247" t="s">
@@ -6287,8 +6387,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A248">
+    <row r="248">
+      <c r="A248" t="n">
         <v>246</v>
       </c>
       <c r="B248" t="s">
@@ -6297,7 +6397,7 @@
       <c r="C248" t="s">
         <v>25</v>
       </c>
-      <c r="D248">
+      <c r="D248" t="n">
         <v>20260611</v>
       </c>
       <c r="E248" t="s">
@@ -6307,8 +6407,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A249">
+    <row r="249">
+      <c r="A249" t="n">
         <v>247</v>
       </c>
       <c r="B249" t="s">
@@ -6317,7 +6417,7 @@
       <c r="C249" t="s">
         <v>25</v>
       </c>
-      <c r="D249">
+      <c r="D249" t="n">
         <v>20260611</v>
       </c>
       <c r="E249" t="s">
@@ -6327,8 +6427,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A250">
+    <row r="250">
+      <c r="A250" t="n">
         <v>248</v>
       </c>
       <c r="B250" t="s">
@@ -6337,7 +6437,7 @@
       <c r="C250" t="s">
         <v>25</v>
       </c>
-      <c r="D250">
+      <c r="D250" t="n">
         <v>20260611</v>
       </c>
       <c r="E250" t="s">
@@ -6347,8 +6447,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A251">
+    <row r="251">
+      <c r="A251" t="n">
         <v>249</v>
       </c>
       <c r="B251" t="s">
@@ -6357,7 +6457,7 @@
       <c r="C251" t="s">
         <v>25</v>
       </c>
-      <c r="D251">
+      <c r="D251" t="n">
         <v>20260611</v>
       </c>
       <c r="E251" t="s">
@@ -6367,8 +6467,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A252">
+    <row r="252">
+      <c r="A252" t="n">
         <v>250</v>
       </c>
       <c r="B252" t="s">
@@ -6377,7 +6477,7 @@
       <c r="C252" t="s">
         <v>17</v>
       </c>
-      <c r="D252">
+      <c r="D252" t="n">
         <v>20260611</v>
       </c>
       <c r="E252" t="s">
@@ -6387,8 +6487,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A253">
+    <row r="253">
+      <c r="A253" t="n">
         <v>251</v>
       </c>
       <c r="B253" t="s">
@@ -6397,7 +6497,7 @@
       <c r="C253" t="s">
         <v>25</v>
       </c>
-      <c r="D253">
+      <c r="D253" t="n">
         <v>20260611</v>
       </c>
       <c r="E253" t="s">
@@ -6407,8 +6507,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A254">
+    <row r="254">
+      <c r="A254" t="n">
         <v>252</v>
       </c>
       <c r="B254" t="s">
@@ -6417,7 +6517,7 @@
       <c r="C254" t="s">
         <v>46</v>
       </c>
-      <c r="D254">
+      <c r="D254" t="n">
         <v>20260611</v>
       </c>
       <c r="E254" t="s">
@@ -6427,8 +6527,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A255">
+    <row r="255">
+      <c r="A255" t="n">
         <v>253</v>
       </c>
       <c r="B255" t="s">
@@ -6437,7 +6537,7 @@
       <c r="C255" t="s">
         <v>8</v>
       </c>
-      <c r="D255">
+      <c r="D255" t="n">
         <v>20260611</v>
       </c>
       <c r="E255" t="s">
@@ -6447,8 +6547,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A256">
+    <row r="256">
+      <c r="A256" t="n">
         <v>254</v>
       </c>
       <c r="B256" t="s">
@@ -6457,7 +6557,7 @@
       <c r="C256" t="s">
         <v>17</v>
       </c>
-      <c r="D256">
+      <c r="D256" t="n">
         <v>20260611</v>
       </c>
       <c r="E256" t="s">
@@ -6467,8 +6567,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A257">
+    <row r="257">
+      <c r="A257" t="n">
         <v>255</v>
       </c>
       <c r="B257" t="s">
@@ -6477,7 +6577,7 @@
       <c r="C257" t="s">
         <v>17</v>
       </c>
-      <c r="D257">
+      <c r="D257" t="n">
         <v>20260611</v>
       </c>
       <c r="E257" t="s">
@@ -6487,8 +6587,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A258">
+    <row r="258">
+      <c r="A258" t="n">
         <v>256</v>
       </c>
       <c r="B258" t="s">
@@ -6497,7 +6597,7 @@
       <c r="C258" t="s">
         <v>17</v>
       </c>
-      <c r="D258">
+      <c r="D258" t="n">
         <v>20260611</v>
       </c>
       <c r="E258" t="s">
@@ -6507,8 +6607,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A259">
+    <row r="259">
+      <c r="A259" t="n">
         <v>257</v>
       </c>
       <c r="B259" t="s">
@@ -6517,7 +6617,7 @@
       <c r="C259" t="s">
         <v>17</v>
       </c>
-      <c r="D259">
+      <c r="D259" t="n">
         <v>20260611</v>
       </c>
       <c r="E259" t="s">
@@ -6527,8 +6627,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A260">
+    <row r="260">
+      <c r="A260" t="n">
         <v>258</v>
       </c>
       <c r="B260" t="s">
@@ -6537,7 +6637,7 @@
       <c r="C260" t="s">
         <v>17</v>
       </c>
-      <c r="D260">
+      <c r="D260" t="n">
         <v>20260611</v>
       </c>
       <c r="E260" t="s">
@@ -6547,8 +6647,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A261">
+    <row r="261">
+      <c r="A261" t="n">
         <v>259</v>
       </c>
       <c r="B261" t="s">
@@ -6557,7 +6657,7 @@
       <c r="C261" t="s">
         <v>17</v>
       </c>
-      <c r="D261">
+      <c r="D261" t="n">
         <v>20260611</v>
       </c>
       <c r="E261" t="s">
@@ -6567,8 +6667,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A262">
+    <row r="262">
+      <c r="A262" t="n">
         <v>260</v>
       </c>
       <c r="B262" t="s">
@@ -6577,7 +6677,7 @@
       <c r="C262" t="s">
         <v>17</v>
       </c>
-      <c r="D262">
+      <c r="D262" t="n">
         <v>20260611</v>
       </c>
       <c r="E262" t="s">
@@ -6587,8 +6687,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A263">
+    <row r="263">
+      <c r="A263" t="n">
         <v>261</v>
       </c>
       <c r="B263" t="s">
@@ -6597,7 +6697,7 @@
       <c r="C263" t="s">
         <v>17</v>
       </c>
-      <c r="D263">
+      <c r="D263" t="n">
         <v>20260611</v>
       </c>
       <c r="E263" t="s">
@@ -6607,8 +6707,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A264">
+    <row r="264">
+      <c r="A264" t="n">
         <v>262</v>
       </c>
       <c r="B264" t="s">
@@ -6617,7 +6717,7 @@
       <c r="C264" t="s">
         <v>17</v>
       </c>
-      <c r="D264">
+      <c r="D264" t="n">
         <v>20260611</v>
       </c>
       <c r="E264" t="s">
@@ -6627,8 +6727,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A265">
+    <row r="265">
+      <c r="A265" t="n">
         <v>263</v>
       </c>
       <c r="B265" t="s">
@@ -6637,7 +6737,7 @@
       <c r="C265" t="s">
         <v>17</v>
       </c>
-      <c r="D265">
+      <c r="D265" t="n">
         <v>20260611</v>
       </c>
       <c r="E265" t="s">
@@ -6647,8 +6747,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A266">
+    <row r="266">
+      <c r="A266" t="n">
         <v>264</v>
       </c>
       <c r="B266" t="s">
@@ -6657,7 +6757,7 @@
       <c r="C266" t="s">
         <v>17</v>
       </c>
-      <c r="D266">
+      <c r="D266" t="n">
         <v>20260611</v>
       </c>
       <c r="E266" t="s">
@@ -6667,8 +6767,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A267">
+    <row r="267">
+      <c r="A267" t="n">
         <v>265</v>
       </c>
       <c r="B267" t="s">
@@ -6677,7 +6777,7 @@
       <c r="C267" t="s">
         <v>17</v>
       </c>
-      <c r="D267">
+      <c r="D267" t="n">
         <v>20260611</v>
       </c>
       <c r="E267" t="s">
@@ -6687,8 +6787,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A268">
+    <row r="268">
+      <c r="A268" t="n">
         <v>266</v>
       </c>
       <c r="B268" t="s">
@@ -6697,7 +6797,7 @@
       <c r="C268" t="s">
         <v>17</v>
       </c>
-      <c r="D268">
+      <c r="D268" t="n">
         <v>20260611</v>
       </c>
       <c r="E268" t="s">
@@ -6707,8 +6807,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A269">
+    <row r="269">
+      <c r="A269" t="n">
         <v>267</v>
       </c>
       <c r="B269" t="s">
@@ -6717,7 +6817,7 @@
       <c r="C269" t="s">
         <v>17</v>
       </c>
-      <c r="D269">
+      <c r="D269" t="n">
         <v>20260611</v>
       </c>
       <c r="E269" t="s">
@@ -6727,8 +6827,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A270">
+    <row r="270">
+      <c r="A270" t="n">
         <v>268</v>
       </c>
       <c r="B270" t="s">
@@ -6737,7 +6837,7 @@
       <c r="C270" t="s">
         <v>17</v>
       </c>
-      <c r="D270">
+      <c r="D270" t="n">
         <v>20260611</v>
       </c>
       <c r="E270" t="s">
@@ -6747,8 +6847,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A271">
+    <row r="271">
+      <c r="A271" t="n">
         <v>269</v>
       </c>
       <c r="B271" t="s">
@@ -6757,7 +6857,7 @@
       <c r="C271" t="s">
         <v>17</v>
       </c>
-      <c r="D271">
+      <c r="D271" t="n">
         <v>20260611</v>
       </c>
       <c r="E271" t="s">
@@ -6767,8 +6867,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A272">
+    <row r="272">
+      <c r="A272" t="n">
         <v>270</v>
       </c>
       <c r="B272" t="s">
@@ -6777,7 +6877,7 @@
       <c r="C272" t="s">
         <v>17</v>
       </c>
-      <c r="D272">
+      <c r="D272" t="n">
         <v>20260611</v>
       </c>
       <c r="E272" t="s">
@@ -6787,8 +6887,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A273">
+    <row r="273">
+      <c r="A273" t="n">
         <v>271</v>
       </c>
       <c r="B273" t="s">
@@ -6797,7 +6897,7 @@
       <c r="C273" t="s">
         <v>17</v>
       </c>
-      <c r="D273">
+      <c r="D273" t="n">
         <v>20260611</v>
       </c>
       <c r="E273" t="s">
@@ -6807,8 +6907,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A274">
+    <row r="274">
+      <c r="A274" t="n">
         <v>272</v>
       </c>
       <c r="B274" t="s">
@@ -6817,7 +6917,7 @@
       <c r="C274" t="s">
         <v>17</v>
       </c>
-      <c r="D274">
+      <c r="D274" t="n">
         <v>20260611</v>
       </c>
       <c r="E274" t="s">
@@ -6827,8 +6927,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A275">
+    <row r="275">
+      <c r="A275" t="n">
         <v>273</v>
       </c>
       <c r="B275" t="s">
@@ -6837,7 +6937,7 @@
       <c r="C275" t="s">
         <v>25</v>
       </c>
-      <c r="D275">
+      <c r="D275" t="n">
         <v>20260611</v>
       </c>
       <c r="E275" t="s">
@@ -6847,8 +6947,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A276">
+    <row r="276">
+      <c r="A276" t="n">
         <v>274</v>
       </c>
       <c r="B276" t="s">
@@ -6857,7 +6957,7 @@
       <c r="C276" t="s">
         <v>25</v>
       </c>
-      <c r="D276">
+      <c r="D276" t="n">
         <v>20260611</v>
       </c>
       <c r="E276" t="s">
@@ -6867,8 +6967,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A277">
+    <row r="277">
+      <c r="A277" t="n">
         <v>275</v>
       </c>
       <c r="B277" t="s">
@@ -6877,7 +6977,7 @@
       <c r="C277" t="s">
         <v>25</v>
       </c>
-      <c r="D277">
+      <c r="D277" t="n">
         <v>20260611</v>
       </c>
       <c r="E277" t="s">
@@ -6887,8 +6987,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A278">
+    <row r="278">
+      <c r="A278" t="n">
         <v>276</v>
       </c>
       <c r="B278" t="s">
@@ -6897,7 +6997,7 @@
       <c r="C278" t="s">
         <v>25</v>
       </c>
-      <c r="D278">
+      <c r="D278" t="n">
         <v>20260611</v>
       </c>
       <c r="E278" t="s">
@@ -6907,8 +7007,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A279">
+    <row r="279">
+      <c r="A279" t="n">
         <v>277</v>
       </c>
       <c r="B279" t="s">
@@ -6917,7 +7017,7 @@
       <c r="C279" t="s">
         <v>25</v>
       </c>
-      <c r="D279">
+      <c r="D279" t="n">
         <v>20260611</v>
       </c>
       <c r="E279" t="s">
@@ -6927,8 +7027,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A280">
+    <row r="280">
+      <c r="A280" t="n">
         <v>278</v>
       </c>
       <c r="B280" t="s">
@@ -6937,7 +7037,7 @@
       <c r="C280" t="s">
         <v>25</v>
       </c>
-      <c r="D280">
+      <c r="D280" t="n">
         <v>20260611</v>
       </c>
       <c r="E280" t="s">
@@ -6947,8 +7047,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A281">
+    <row r="281">
+      <c r="A281" t="n">
         <v>279</v>
       </c>
       <c r="B281" t="s">
@@ -6957,7 +7057,7 @@
       <c r="C281" t="s">
         <v>25</v>
       </c>
-      <c r="D281">
+      <c r="D281" t="n">
         <v>20260611</v>
       </c>
       <c r="E281" t="s">
@@ -6967,8 +7067,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A282">
+    <row r="282">
+      <c r="A282" t="n">
         <v>280</v>
       </c>
       <c r="B282" t="s">
@@ -6977,7 +7077,7 @@
       <c r="C282" t="s">
         <v>25</v>
       </c>
-      <c r="D282">
+      <c r="D282" t="n">
         <v>20260611</v>
       </c>
       <c r="E282" t="s">
@@ -6987,8 +7087,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A283">
+    <row r="283">
+      <c r="A283" t="n">
         <v>281</v>
       </c>
       <c r="B283" t="s">
@@ -6997,7 +7097,7 @@
       <c r="C283" t="s">
         <v>25</v>
       </c>
-      <c r="D283">
+      <c r="D283" t="n">
         <v>20260611</v>
       </c>
       <c r="E283" t="s">
@@ -7007,8 +7107,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A284">
+    <row r="284">
+      <c r="A284" t="n">
         <v>282</v>
       </c>
       <c r="B284" t="s">
@@ -7017,7 +7117,7 @@
       <c r="C284" t="s">
         <v>25</v>
       </c>
-      <c r="D284">
+      <c r="D284" t="n">
         <v>20260611</v>
       </c>
       <c r="E284" t="s">
@@ -7027,8 +7127,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A285">
+    <row r="285">
+      <c r="A285" t="n">
         <v>283</v>
       </c>
       <c r="B285" t="s">
@@ -7037,7 +7137,7 @@
       <c r="C285" t="s">
         <v>25</v>
       </c>
-      <c r="D285">
+      <c r="D285" t="n">
         <v>20260611</v>
       </c>
       <c r="E285" t="s">
@@ -7047,8 +7147,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A286">
+    <row r="286">
+      <c r="A286" t="n">
         <v>284</v>
       </c>
       <c r="B286" t="s">
@@ -7057,7 +7157,7 @@
       <c r="C286" t="s">
         <v>25</v>
       </c>
-      <c r="D286">
+      <c r="D286" t="n">
         <v>20260611</v>
       </c>
       <c r="E286" t="s">
@@ -7067,8 +7167,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A287">
+    <row r="287">
+      <c r="A287" t="n">
         <v>285</v>
       </c>
       <c r="B287" t="s">
@@ -7077,7 +7177,7 @@
       <c r="C287" t="s">
         <v>25</v>
       </c>
-      <c r="D287">
+      <c r="D287" t="n">
         <v>20260611</v>
       </c>
       <c r="E287" t="s">
@@ -7087,8 +7187,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A288">
+    <row r="288">
+      <c r="A288" t="n">
         <v>286</v>
       </c>
       <c r="B288" t="s">
@@ -7097,7 +7197,7 @@
       <c r="C288" t="s">
         <v>25</v>
       </c>
-      <c r="D288">
+      <c r="D288" t="n">
         <v>20260611</v>
       </c>
       <c r="E288" t="s">
@@ -7107,8 +7207,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A289">
+    <row r="289">
+      <c r="A289" t="n">
         <v>287</v>
       </c>
       <c r="B289" t="s">
@@ -7117,7 +7217,7 @@
       <c r="C289" t="s">
         <v>25</v>
       </c>
-      <c r="D289">
+      <c r="D289" t="n">
         <v>20260611</v>
       </c>
       <c r="E289" t="s">
@@ -7127,8 +7227,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A290">
+    <row r="290">
+      <c r="A290" t="n">
         <v>288</v>
       </c>
       <c r="B290" t="s">
@@ -7137,7 +7237,7 @@
       <c r="C290" t="s">
         <v>25</v>
       </c>
-      <c r="D290">
+      <c r="D290" t="n">
         <v>20260611</v>
       </c>
       <c r="E290" t="s">
@@ -7147,8 +7247,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A291">
+    <row r="291">
+      <c r="A291" t="n">
         <v>289</v>
       </c>
       <c r="B291" t="s">
@@ -7157,7 +7257,7 @@
       <c r="C291" t="s">
         <v>25</v>
       </c>
-      <c r="D291">
+      <c r="D291" t="n">
         <v>20260611</v>
       </c>
       <c r="E291" t="s">
@@ -7167,8 +7267,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A292">
+    <row r="292">
+      <c r="A292" t="n">
         <v>290</v>
       </c>
       <c r="B292" t="s">
@@ -7177,7 +7277,7 @@
       <c r="C292" t="s">
         <v>25</v>
       </c>
-      <c r="D292">
+      <c r="D292" t="n">
         <v>20260611</v>
       </c>
       <c r="E292" t="s">
@@ -7187,8 +7287,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A293">
+    <row r="293">
+      <c r="A293" t="n">
         <v>291</v>
       </c>
       <c r="B293" t="s">
@@ -7197,7 +7297,7 @@
       <c r="C293" t="s">
         <v>25</v>
       </c>
-      <c r="D293">
+      <c r="D293" t="n">
         <v>20260611</v>
       </c>
       <c r="E293" t="s">
@@ -7207,8 +7307,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A294">
+    <row r="294">
+      <c r="A294" t="n">
         <v>292</v>
       </c>
       <c r="B294" t="s">
@@ -7217,7 +7317,7 @@
       <c r="C294" t="s">
         <v>25</v>
       </c>
-      <c r="D294">
+      <c r="D294" t="n">
         <v>20260611</v>
       </c>
       <c r="E294" t="s">
@@ -7227,8 +7327,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A295">
+    <row r="295">
+      <c r="A295" t="n">
         <v>293</v>
       </c>
       <c r="B295" t="s">
@@ -7237,7 +7337,7 @@
       <c r="C295" t="s">
         <v>17</v>
       </c>
-      <c r="D295">
+      <c r="D295" t="n">
         <v>20260611</v>
       </c>
       <c r="E295" t="s">
@@ -7247,8 +7347,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A296">
+    <row r="296">
+      <c r="A296" t="n">
         <v>294</v>
       </c>
       <c r="B296" t="s">
@@ -7257,7 +7357,7 @@
       <c r="C296" t="s">
         <v>25</v>
       </c>
-      <c r="D296">
+      <c r="D296" t="n">
         <v>20260611</v>
       </c>
       <c r="E296" t="s">
@@ -7267,8 +7367,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A297">
+    <row r="297">
+      <c r="A297" t="n">
         <v>295</v>
       </c>
       <c r="B297" t="s">
@@ -7277,7 +7377,7 @@
       <c r="C297" t="s">
         <v>46</v>
       </c>
-      <c r="D297">
+      <c r="D297" t="n">
         <v>20260611</v>
       </c>
       <c r="E297" t="s">
@@ -7287,8 +7387,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A298">
+    <row r="298">
+      <c r="A298" t="n">
         <v>296</v>
       </c>
       <c r="B298" t="s">
@@ -7297,7 +7397,7 @@
       <c r="C298" t="s">
         <v>17</v>
       </c>
-      <c r="D298">
+      <c r="D298" t="n">
         <v>20260611</v>
       </c>
       <c r="E298" t="s">
@@ -7307,8 +7407,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A299">
+    <row r="299">
+      <c r="A299" t="n">
         <v>297</v>
       </c>
       <c r="B299" t="s">
@@ -7317,7 +7417,7 @@
       <c r="C299" t="s">
         <v>25</v>
       </c>
-      <c r="D299">
+      <c r="D299" t="n">
         <v>20260611</v>
       </c>
       <c r="E299" t="s">
@@ -7327,8 +7427,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A300">
+    <row r="300">
+      <c r="A300" t="n">
         <v>298</v>
       </c>
       <c r="B300" t="s">
@@ -7337,7 +7437,7 @@
       <c r="C300" t="s">
         <v>17</v>
       </c>
-      <c r="D300">
+      <c r="D300" t="n">
         <v>20260611</v>
       </c>
       <c r="E300" t="s">
@@ -7347,8 +7447,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A301">
+    <row r="301">
+      <c r="A301" t="n">
         <v>299</v>
       </c>
       <c r="B301" t="s">
@@ -7357,7 +7457,7 @@
       <c r="C301" t="s">
         <v>25</v>
       </c>
-      <c r="D301">
+      <c r="D301" t="n">
         <v>20260611</v>
       </c>
       <c r="E301" t="s">
@@ -7367,8 +7467,788 @@
         <v>53</v>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>300</v>
+      </c>
+      <c r="B302" t="s">
+        <v>334</v>
+      </c>
+      <c r="C302" t="s">
+        <v>17</v>
+      </c>
+      <c r="D302" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E302" t="s">
+        <v>335</v>
+      </c>
+      <c r="F302" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>301</v>
+      </c>
+      <c r="B303" t="s">
+        <v>336</v>
+      </c>
+      <c r="C303" t="s">
+        <v>17</v>
+      </c>
+      <c r="D303" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E303" t="s">
+        <v>335</v>
+      </c>
+      <c r="F303" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>302</v>
+      </c>
+      <c r="B304" t="s">
+        <v>337</v>
+      </c>
+      <c r="C304" t="s">
+        <v>17</v>
+      </c>
+      <c r="D304" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E304" t="s">
+        <v>335</v>
+      </c>
+      <c r="F304" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>303</v>
+      </c>
+      <c r="B305" t="s">
+        <v>338</v>
+      </c>
+      <c r="C305" t="s">
+        <v>17</v>
+      </c>
+      <c r="D305" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E305" t="s">
+        <v>335</v>
+      </c>
+      <c r="F305" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>304</v>
+      </c>
+      <c r="B306" t="s">
+        <v>339</v>
+      </c>
+      <c r="C306" t="s">
+        <v>17</v>
+      </c>
+      <c r="D306" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E306" t="s">
+        <v>335</v>
+      </c>
+      <c r="F306" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>305</v>
+      </c>
+      <c r="B307" t="s">
+        <v>340</v>
+      </c>
+      <c r="C307" t="s">
+        <v>17</v>
+      </c>
+      <c r="D307" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E307" t="s">
+        <v>335</v>
+      </c>
+      <c r="F307" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>306</v>
+      </c>
+      <c r="B308" t="s">
+        <v>341</v>
+      </c>
+      <c r="C308" t="s">
+        <v>17</v>
+      </c>
+      <c r="D308" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E308" t="s">
+        <v>335</v>
+      </c>
+      <c r="F308" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>307</v>
+      </c>
+      <c r="B309" t="s">
+        <v>342</v>
+      </c>
+      <c r="C309" t="s">
+        <v>17</v>
+      </c>
+      <c r="D309" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E309" t="s">
+        <v>335</v>
+      </c>
+      <c r="F309" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>308</v>
+      </c>
+      <c r="B310" t="s">
+        <v>343</v>
+      </c>
+      <c r="C310" t="s">
+        <v>17</v>
+      </c>
+      <c r="D310" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E310" t="s">
+        <v>335</v>
+      </c>
+      <c r="F310" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>309</v>
+      </c>
+      <c r="B311" t="s">
+        <v>344</v>
+      </c>
+      <c r="C311" t="s">
+        <v>17</v>
+      </c>
+      <c r="D311" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E311" t="s">
+        <v>335</v>
+      </c>
+      <c r="F311" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>310</v>
+      </c>
+      <c r="B312" t="s">
+        <v>345</v>
+      </c>
+      <c r="C312" t="s">
+        <v>17</v>
+      </c>
+      <c r="D312" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E312" t="s">
+        <v>335</v>
+      </c>
+      <c r="F312" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>311</v>
+      </c>
+      <c r="B313" t="s">
+        <v>346</v>
+      </c>
+      <c r="C313" t="s">
+        <v>17</v>
+      </c>
+      <c r="D313" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E313" t="s">
+        <v>335</v>
+      </c>
+      <c r="F313" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>312</v>
+      </c>
+      <c r="B314" t="s">
+        <v>347</v>
+      </c>
+      <c r="C314" t="s">
+        <v>17</v>
+      </c>
+      <c r="D314" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E314" t="s">
+        <v>335</v>
+      </c>
+      <c r="F314" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>313</v>
+      </c>
+      <c r="B315" t="s">
+        <v>348</v>
+      </c>
+      <c r="C315" t="s">
+        <v>17</v>
+      </c>
+      <c r="D315" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E315" t="s">
+        <v>335</v>
+      </c>
+      <c r="F315" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>314</v>
+      </c>
+      <c r="B316" t="s">
+        <v>349</v>
+      </c>
+      <c r="C316" t="s">
+        <v>17</v>
+      </c>
+      <c r="D316" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E316" t="s">
+        <v>335</v>
+      </c>
+      <c r="F316" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>315</v>
+      </c>
+      <c r="B317" t="s">
+        <v>350</v>
+      </c>
+      <c r="C317" t="s">
+        <v>17</v>
+      </c>
+      <c r="D317" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E317" t="s">
+        <v>335</v>
+      </c>
+      <c r="F317" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>316</v>
+      </c>
+      <c r="B318" t="s">
+        <v>351</v>
+      </c>
+      <c r="C318" t="s">
+        <v>17</v>
+      </c>
+      <c r="D318" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E318" t="s">
+        <v>335</v>
+      </c>
+      <c r="F318" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>317</v>
+      </c>
+      <c r="B319" t="s">
+        <v>352</v>
+      </c>
+      <c r="C319" t="s">
+        <v>17</v>
+      </c>
+      <c r="D319" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E319" t="s">
+        <v>335</v>
+      </c>
+      <c r="F319" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>318</v>
+      </c>
+      <c r="B320" t="s">
+        <v>353</v>
+      </c>
+      <c r="C320" t="s">
+        <v>17</v>
+      </c>
+      <c r="D320" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E320" t="s">
+        <v>335</v>
+      </c>
+      <c r="F320" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>319</v>
+      </c>
+      <c r="B321" t="s">
+        <v>354</v>
+      </c>
+      <c r="C321" t="s">
+        <v>25</v>
+      </c>
+      <c r="D321" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E321" t="s">
+        <v>335</v>
+      </c>
+      <c r="F321" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>320</v>
+      </c>
+      <c r="B322" t="s">
+        <v>355</v>
+      </c>
+      <c r="C322" t="s">
+        <v>25</v>
+      </c>
+      <c r="D322" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E322" t="s">
+        <v>335</v>
+      </c>
+      <c r="F322" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>321</v>
+      </c>
+      <c r="B323" t="s">
+        <v>356</v>
+      </c>
+      <c r="C323" t="s">
+        <v>25</v>
+      </c>
+      <c r="D323" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E323" t="s">
+        <v>335</v>
+      </c>
+      <c r="F323" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>322</v>
+      </c>
+      <c r="B324" t="s">
+        <v>357</v>
+      </c>
+      <c r="C324" t="s">
+        <v>25</v>
+      </c>
+      <c r="D324" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E324" t="s">
+        <v>335</v>
+      </c>
+      <c r="F324" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>323</v>
+      </c>
+      <c r="B325" t="s">
+        <v>358</v>
+      </c>
+      <c r="C325" t="s">
+        <v>25</v>
+      </c>
+      <c r="D325" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E325" t="s">
+        <v>335</v>
+      </c>
+      <c r="F325" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>324</v>
+      </c>
+      <c r="B326" t="s">
+        <v>359</v>
+      </c>
+      <c r="C326" t="s">
+        <v>25</v>
+      </c>
+      <c r="D326" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E326" t="s">
+        <v>335</v>
+      </c>
+      <c r="F326" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>325</v>
+      </c>
+      <c r="B327" t="s">
+        <v>360</v>
+      </c>
+      <c r="C327" t="s">
+        <v>25</v>
+      </c>
+      <c r="D327" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E327" t="s">
+        <v>335</v>
+      </c>
+      <c r="F327" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>326</v>
+      </c>
+      <c r="B328" t="s">
+        <v>361</v>
+      </c>
+      <c r="C328" t="s">
+        <v>25</v>
+      </c>
+      <c r="D328" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E328" t="s">
+        <v>335</v>
+      </c>
+      <c r="F328" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>327</v>
+      </c>
+      <c r="B329" t="s">
+        <v>362</v>
+      </c>
+      <c r="C329" t="s">
+        <v>25</v>
+      </c>
+      <c r="D329" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E329" t="s">
+        <v>335</v>
+      </c>
+      <c r="F329" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>328</v>
+      </c>
+      <c r="B330" t="s">
+        <v>363</v>
+      </c>
+      <c r="C330" t="s">
+        <v>25</v>
+      </c>
+      <c r="D330" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E330" t="s">
+        <v>335</v>
+      </c>
+      <c r="F330" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>329</v>
+      </c>
+      <c r="B331" t="s">
+        <v>364</v>
+      </c>
+      <c r="C331" t="s">
+        <v>25</v>
+      </c>
+      <c r="D331" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E331" t="s">
+        <v>335</v>
+      </c>
+      <c r="F331" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>330</v>
+      </c>
+      <c r="B332" t="s">
+        <v>365</v>
+      </c>
+      <c r="C332" t="s">
+        <v>25</v>
+      </c>
+      <c r="D332" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+      <c r="F332" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>331</v>
+      </c>
+      <c r="B333" t="s">
+        <v>366</v>
+      </c>
+      <c r="C333" t="s">
+        <v>25</v>
+      </c>
+      <c r="D333" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E333" t="s">
+        <v>335</v>
+      </c>
+      <c r="F333" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>332</v>
+      </c>
+      <c r="B334" t="s">
+        <v>367</v>
+      </c>
+      <c r="C334" t="s">
+        <v>25</v>
+      </c>
+      <c r="D334" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E334" t="s">
+        <v>335</v>
+      </c>
+      <c r="F334" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>333</v>
+      </c>
+      <c r="B335" t="s">
+        <v>368</v>
+      </c>
+      <c r="C335" t="s">
+        <v>25</v>
+      </c>
+      <c r="D335" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E335" t="s">
+        <v>335</v>
+      </c>
+      <c r="F335" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>334</v>
+      </c>
+      <c r="B336" t="s">
+        <v>369</v>
+      </c>
+      <c r="C336" t="s">
+        <v>25</v>
+      </c>
+      <c r="D336" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E336" t="s">
+        <v>335</v>
+      </c>
+      <c r="F336" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>335</v>
+      </c>
+      <c r="B337" t="s">
+        <v>370</v>
+      </c>
+      <c r="C337" t="s">
+        <v>25</v>
+      </c>
+      <c r="D337" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E337" t="s">
+        <v>335</v>
+      </c>
+      <c r="F337" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>336</v>
+      </c>
+      <c r="B338" t="s">
+        <v>371</v>
+      </c>
+      <c r="C338" t="s">
+        <v>25</v>
+      </c>
+      <c r="D338" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E338" t="s">
+        <v>335</v>
+      </c>
+      <c r="F338" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>337</v>
+      </c>
+      <c r="B339" t="s">
+        <v>372</v>
+      </c>
+      <c r="C339" t="s">
+        <v>25</v>
+      </c>
+      <c r="D339" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E339" t="s">
+        <v>335</v>
+      </c>
+      <c r="F339" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>338</v>
+      </c>
+      <c r="B340" t="s">
+        <v>373</v>
+      </c>
+      <c r="C340" t="s">
+        <v>25</v>
+      </c>
+      <c r="D340" t="n">
+        <v>20260612</v>
+      </c>
+      <c r="E340" t="s">
+        <v>335</v>
+      </c>
+      <c r="F340" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/processing_scripts/Inventory_Processing/TEMPEST_SO4_20260501-20260612.xlsx
+++ b/processing_scripts/Inventory_Processing/TEMPEST_SO4_20260501-20260612.xlsx
@@ -1,1147 +1,1154 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sinet-my.sharepoint.com/personal/readz_si_edu1/Documents/TEMPEST_Porewater/processing_scripts/Inventory_Processing/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_B89231273CF96668CBB5F26DB23E1D420A5CD295" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{070B892B-CF8C-4AC5-B85F-30394BB0384B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sample List" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sample List" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="374">
-  <si>
-    <t xml:space="preserve">TEMPEST Sample List: SO4/Cl/H2S 20260501 - 20260612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample_Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collection_Date_YYYYMMDD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timepoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_C_PW_C6_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_C_PW_F4_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_C_PW_F4_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_C_PW_H3_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_C_PW_H6_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_C_PW_H6_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saltwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freshwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260604_Pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260607_D1_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D1_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260607_D1_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260607_D1_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260607_D1_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260607_D1_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260607_D1_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_SW_SO4_20260608_D2-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_SW_SO4_20260608_D2-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_EST_SW_SO4_20260608_D2-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estuary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_SW_SO4_20260608_D2-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_SW_SO4_20260608_D2-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_EST_SW_SO4_20260608_D2-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_RO_SO4_20260608_D2-T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2-T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_RO_SO4_20260608_D2-T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2-T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_C_PW_C6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_SW_SO4_20260609_D3-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D3-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_SW_SO4_20260609_D3-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_EST_SW_SO4_20260609_D3-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_RO_SO4_20260609_D3-Macropore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D3-Macropore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_B4_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_D5_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_E3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_I5_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_E3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_I5_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_SW_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_SW_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_EST_SW_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_RO_SO4_20260609_D3-T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D3-T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_RO_SO4_20260609_D3-T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_RO_SO4_20260609_D3-T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D3-T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_RO_SO4_20260609_D3-T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_B4_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_D5_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_I5_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F6_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_E3_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_15cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260609_D3_AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_B4_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_D5_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_E3_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_I5_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F6_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_E3_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_I5_15cm_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_SW_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_SW_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_EST_SW_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_B4_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_D5_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_E3_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_I5_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F6_15cm_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_SW_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_SW_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_EST_SW_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_RO_SO4_20260610_D4-T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D4-T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_RO_SO4_20260610_D4-T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_RO_SO4_20260610_D4-T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D4-T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_RO_SO4_20260610_D4-T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_B4_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_D5_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_E3_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_I5_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F6_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_B4_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_E3_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_I5_15cm_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_SW_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_SW_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_EST_SW_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_C_PW_C6_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_B4_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_D5_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_E3_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_I5_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_B4_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_E3_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_I5_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F6_15cm_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_SW_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_SW_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_EST_SW_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_RO_SO4_20260611_D5-T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D5-T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_RO_SO4_20260611_D5-T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_RO_SO4_20260611_D5-T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D5-T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_RO_SO4_20260611_D5-T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_B4_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C3_50cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_30cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_C6_50cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_D5_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_E3_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_30cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F4_50cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_30cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H3_50cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_30cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_H6_50cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_I5_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_SW_PW_F6_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_B4_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_30cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C3_50cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_30cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_C6_50cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_D5_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_E3_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_30cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F4_50cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_30cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H3_50cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_30cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_H6_50cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_I5_15cm_SO4_20260612_D6_PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMP_FW_PW_F6_15cm_SO4_20260612_D6_PM</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="374">
+  <si>
+    <t>TEMPEST Sample List: SO4/Cl/H2S 20260501 - 20260612</t>
+  </si>
+  <si>
+    <t>Sample_Number</t>
+  </si>
+  <si>
+    <t>Sample_ID</t>
+  </si>
+  <si>
+    <t>Plot</t>
+  </si>
+  <si>
+    <t>Collection_Date_YYYYMMDD</t>
+  </si>
+  <si>
+    <t>Timepoint</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>TMP_C_PW_C6_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Pre</t>
+  </si>
+  <si>
+    <t>PW</t>
+  </si>
+  <si>
+    <t>TMP_C_PW_F4_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_C_PW_F4_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_C_PW_H3_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_C_PW_H6_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_C_PW_H6_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>Saltwater</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>Freshwater</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_15cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_D5_15cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_30cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_50cm_SO4_20260604_Pre</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_30cm_SO4_20260607_D1_PM</t>
+  </si>
+  <si>
+    <t>D1_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_50cm_SO4_20260607_D1_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_30cm_SO4_20260607_D1_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_30cm_SO4_20260607_D1_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_D5_15cm_SO4_20260607_D1_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_50cm_SO4_20260607_D1_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_SCE_SO4_20260608_D2-AM</t>
+  </si>
+  <si>
+    <t>D2-AM</t>
+  </si>
+  <si>
+    <t>SCE</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260608_D2-AM</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260608_D2-AM</t>
+  </si>
+  <si>
+    <t>Estuary</t>
+  </si>
+  <si>
+    <t>TMP_SW_SCE_SO4_20260608_D2-PM</t>
+  </si>
+  <si>
+    <t>D2-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260608_D2-PM</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260608_D2-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260608_D2-T1</t>
+  </si>
+  <si>
+    <t>D2-T1</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260608_D2-T2</t>
+  </si>
+  <si>
+    <t>D2-T2</t>
+  </si>
+  <si>
+    <t>TMP_C_PW_C6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_15cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_D5_15cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_SCE_SO4_20260609_D3-AM</t>
+  </si>
+  <si>
+    <t>D3-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260609_D3-AM</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260609_D3-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260609_D3-Macropore</t>
+  </si>
+  <si>
+    <t>D3-Macropore</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_B4_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_D5_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_E3_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_I5_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_D5_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_E3_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_30cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_50cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_I5_15cm_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_SCE_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260609_D3-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260609_D3-T1</t>
+  </si>
+  <si>
+    <t>D3-T1</t>
+  </si>
+  <si>
+    <t>TMP_FW_RO_SO4_20260609_D3-T1</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260609_D3-T2</t>
+  </si>
+  <si>
+    <t>D3-T2</t>
+  </si>
+  <si>
+    <t>TMP_FW_RO_SO4_20260609_D3-T2</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_B4_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_D5_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_I5_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F6_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_D5_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_E3_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_15cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_30cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_50cm_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_B4_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_D5_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_E3_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_I5_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F6_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_D5_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_E3_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_30cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_50cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_I5_15cm_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_SCE_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260610_D4-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_B4_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_30cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_D5_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_E3_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_30cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_30cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_30cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_D5_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_30cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_30cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_30cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_50cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_I5_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F6_15cm_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_SCE_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260610_D4-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260610_D4-T1</t>
+  </si>
+  <si>
+    <t>D4-T1</t>
+  </si>
+  <si>
+    <t>TMP_FW_RO_SO4_20260610_D4-T1</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260610_D4-T2</t>
+  </si>
+  <si>
+    <t>D4-T2</t>
+  </si>
+  <si>
+    <t>TMP_FW_RO_SO4_20260610_D4-T2</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_B4_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_D5_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_E3_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_I5_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F6_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_B4_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_D5_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_E3_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_30cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_50cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_I5_15cm_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_SW_SCE_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260611_D5-AM</t>
+  </si>
+  <si>
+    <t>TMP_C_PW_C6_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_B4_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_D5_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_E3_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_I5_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_B4_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_D5_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_E3_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_30cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_50cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_I5_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F6_15cm_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_SCE_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260611_D5-PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260611_D5-T1</t>
+  </si>
+  <si>
+    <t>D5-T1</t>
+  </si>
+  <si>
+    <t>TMP_FW_RO_SO4_20260611_D5-T1</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260611_D5-T2</t>
+  </si>
+  <si>
+    <t>D5-T2</t>
+  </si>
+  <si>
+    <t>TMP_FW_RO_SO4_20260611_D5-T2</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_B4_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_D5_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_E3_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_I5_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F6_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_B4_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_D5_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_E3_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_30cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_50cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_I5_15cm_SO4_20260612_D6_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F6_15cm_SO4_20260612_D6_PM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1177,6 +1184,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1458,16 +1474,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F340"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="55.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1487,8 +1506,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
@@ -1497,7 +1516,7 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>20260604</v>
       </c>
       <c r="E3" t="s">
@@ -1507,8 +1526,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
@@ -1517,7 +1536,7 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>20260604</v>
       </c>
       <c r="E4" t="s">
@@ -1527,8 +1546,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
@@ -1537,7 +1556,7 @@
       <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>20260604</v>
       </c>
       <c r="E5" t="s">
@@ -1547,8 +1566,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
@@ -1557,7 +1576,7 @@
       <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>20260604</v>
       </c>
       <c r="E6" t="s">
@@ -1567,8 +1586,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
@@ -1577,7 +1596,7 @@
       <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>20260604</v>
       </c>
       <c r="E7" t="s">
@@ -1587,8 +1606,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
@@ -1597,7 +1616,7 @@
       <c r="C8" t="s">
         <v>8</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>20260604</v>
       </c>
       <c r="E8" t="s">
@@ -1607,8 +1626,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
@@ -1617,7 +1636,7 @@
       <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>20260604</v>
       </c>
       <c r="E9" t="s">
@@ -1627,8 +1646,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
@@ -1637,7 +1656,7 @@
       <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>20260604</v>
       </c>
       <c r="E10" t="s">
@@ -1647,8 +1666,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
@@ -1657,7 +1676,7 @@
       <c r="C11" t="s">
         <v>17</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>20260604</v>
       </c>
       <c r="E11" t="s">
@@ -1667,8 +1686,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
@@ -1677,7 +1696,7 @@
       <c r="C12" t="s">
         <v>17</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>20260604</v>
       </c>
       <c r="E12" t="s">
@@ -1687,8 +1706,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
@@ -1697,7 +1716,7 @@
       <c r="C13" t="s">
         <v>17</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>20260604</v>
       </c>
       <c r="E13" t="s">
@@ -1707,8 +1726,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
@@ -1717,7 +1736,7 @@
       <c r="C14" t="s">
         <v>17</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>20260604</v>
       </c>
       <c r="E14" t="s">
@@ -1727,8 +1746,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
@@ -1737,7 +1756,7 @@
       <c r="C15" t="s">
         <v>17</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>20260604</v>
       </c>
       <c r="E15" t="s">
@@ -1747,8 +1766,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
@@ -1757,7 +1776,7 @@
       <c r="C16" t="s">
         <v>25</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>20260604</v>
       </c>
       <c r="E16" t="s">
@@ -1767,8 +1786,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
@@ -1777,7 +1796,7 @@
       <c r="C17" t="s">
         <v>25</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>20260604</v>
       </c>
       <c r="E17" t="s">
@@ -1787,8 +1806,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
@@ -1797,7 +1816,7 @@
       <c r="C18" t="s">
         <v>25</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>20260604</v>
       </c>
       <c r="E18" t="s">
@@ -1807,8 +1826,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
@@ -1817,7 +1836,7 @@
       <c r="C19" t="s">
         <v>25</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>20260604</v>
       </c>
       <c r="E19" t="s">
@@ -1827,8 +1846,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
@@ -1837,7 +1856,7 @@
       <c r="C20" t="s">
         <v>25</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>20260604</v>
       </c>
       <c r="E20" t="s">
@@ -1847,8 +1866,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
@@ -1857,7 +1876,7 @@
       <c r="C21" t="s">
         <v>25</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>20260604</v>
       </c>
       <c r="E21" t="s">
@@ -1867,8 +1886,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
@@ -1877,7 +1896,7 @@
       <c r="C22" t="s">
         <v>25</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>20260604</v>
       </c>
       <c r="E22" t="s">
@@ -1887,8 +1906,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
@@ -1897,7 +1916,7 @@
       <c r="C23" t="s">
         <v>25</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>20260604</v>
       </c>
       <c r="E23" t="s">
@@ -1907,8 +1926,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
@@ -1917,7 +1936,7 @@
       <c r="C24" t="s">
         <v>25</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>20260604</v>
       </c>
       <c r="E24" t="s">
@@ -1927,8 +1946,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
@@ -1937,7 +1956,7 @@
       <c r="C25" t="s">
         <v>17</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>20260607</v>
       </c>
       <c r="E25" t="s">
@@ -1947,8 +1966,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
@@ -1957,7 +1976,7 @@
       <c r="C26" t="s">
         <v>17</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>20260607</v>
       </c>
       <c r="E26" t="s">
@@ -1967,8 +1986,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
@@ -1977,7 +1996,7 @@
       <c r="C27" t="s">
         <v>17</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>20260607</v>
       </c>
       <c r="E27" t="s">
@@ -1987,8 +2006,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
@@ -1997,7 +2016,7 @@
       <c r="C28" t="s">
         <v>17</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>20260607</v>
       </c>
       <c r="E28" t="s">
@@ -2007,8 +2026,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
@@ -2017,7 +2036,7 @@
       <c r="C29" t="s">
         <v>25</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>20260607</v>
       </c>
       <c r="E29" t="s">
@@ -2027,8 +2046,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
@@ -2037,7 +2056,7 @@
       <c r="C30" t="s">
         <v>25</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>20260607</v>
       </c>
       <c r="E30" t="s">
@@ -2047,8 +2066,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
@@ -2057,7 +2076,7 @@
       <c r="C31" t="s">
         <v>17</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>20260608</v>
       </c>
       <c r="E31" t="s">
@@ -2067,8 +2086,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
@@ -2077,7 +2096,7 @@
       <c r="C32" t="s">
         <v>25</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>20260608</v>
       </c>
       <c r="E32" t="s">
@@ -2087,8 +2106,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
@@ -2097,7 +2116,7 @@
       <c r="C33" t="s">
         <v>46</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>20260608</v>
       </c>
       <c r="E33" t="s">
@@ -2107,8 +2126,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
@@ -2117,7 +2136,7 @@
       <c r="C34" t="s">
         <v>17</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>20260608</v>
       </c>
       <c r="E34" t="s">
@@ -2127,8 +2146,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
@@ -2137,7 +2156,7 @@
       <c r="C35" t="s">
         <v>25</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>20260608</v>
       </c>
       <c r="E35" t="s">
@@ -2147,8 +2166,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
@@ -2157,7 +2176,7 @@
       <c r="C36" t="s">
         <v>46</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>20260608</v>
       </c>
       <c r="E36" t="s">
@@ -2167,8 +2186,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
@@ -2177,7 +2196,7 @@
       <c r="C37" t="s">
         <v>17</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>20260608</v>
       </c>
       <c r="E37" t="s">
@@ -2187,8 +2206,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
@@ -2197,7 +2216,7 @@
       <c r="C38" t="s">
         <v>17</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>20260608</v>
       </c>
       <c r="E38" t="s">
@@ -2207,8 +2226,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
@@ -2217,7 +2236,7 @@
       <c r="C39" t="s">
         <v>8</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>20260608</v>
       </c>
       <c r="E39" t="s">
@@ -2227,8 +2246,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" t="s">
@@ -2237,7 +2256,7 @@
       <c r="C40" t="s">
         <v>17</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>20260608</v>
       </c>
       <c r="E40" t="s">
@@ -2247,8 +2266,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" t="s">
@@ -2257,7 +2276,7 @@
       <c r="C41" t="s">
         <v>17</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>20260608</v>
       </c>
       <c r="E41" t="s">
@@ -2267,8 +2286,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
@@ -2277,7 +2296,7 @@
       <c r="C42" t="s">
         <v>17</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>20260608</v>
       </c>
       <c r="E42" t="s">
@@ -2287,8 +2306,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" t="s">
@@ -2297,7 +2316,7 @@
       <c r="C43" t="s">
         <v>17</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>20260608</v>
       </c>
       <c r="E43" t="s">
@@ -2307,8 +2326,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" t="s">
@@ -2317,7 +2336,7 @@
       <c r="C44" t="s">
         <v>17</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>20260608</v>
       </c>
       <c r="E44" t="s">
@@ -2327,8 +2346,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" t="s">
@@ -2337,7 +2356,7 @@
       <c r="C45" t="s">
         <v>17</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>20260608</v>
       </c>
       <c r="E45" t="s">
@@ -2347,8 +2366,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" t="s">
@@ -2357,7 +2376,7 @@
       <c r="C46" t="s">
         <v>17</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>20260608</v>
       </c>
       <c r="E46" t="s">
@@ -2367,8 +2386,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" t="s">
@@ -2377,7 +2396,7 @@
       <c r="C47" t="s">
         <v>17</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>20260608</v>
       </c>
       <c r="E47" t="s">
@@ -2387,8 +2406,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48">
         <v>46</v>
       </c>
       <c r="B48" t="s">
@@ -2397,7 +2416,7 @@
       <c r="C48" t="s">
         <v>25</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>20260608</v>
       </c>
       <c r="E48" t="s">
@@ -2407,8 +2426,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49">
         <v>47</v>
       </c>
       <c r="B49" t="s">
@@ -2417,7 +2436,7 @@
       <c r="C49" t="s">
         <v>25</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>20260608</v>
       </c>
       <c r="E49" t="s">
@@ -2427,8 +2446,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50">
         <v>48</v>
       </c>
       <c r="B50" t="s">
@@ -2437,7 +2456,7 @@
       <c r="C50" t="s">
         <v>25</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>20260608</v>
       </c>
       <c r="E50" t="s">
@@ -2447,8 +2466,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51">
         <v>49</v>
       </c>
       <c r="B51" t="s">
@@ -2457,7 +2476,7 @@
       <c r="C51" t="s">
         <v>25</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>20260608</v>
       </c>
       <c r="E51" t="s">
@@ -2467,8 +2486,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52">
         <v>50</v>
       </c>
       <c r="B52" t="s">
@@ -2477,7 +2496,7 @@
       <c r="C52" t="s">
         <v>25</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>20260608</v>
       </c>
       <c r="E52" t="s">
@@ -2487,8 +2506,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53">
         <v>51</v>
       </c>
       <c r="B53" t="s">
@@ -2497,7 +2516,7 @@
       <c r="C53" t="s">
         <v>25</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>20260608</v>
       </c>
       <c r="E53" t="s">
@@ -2507,8 +2526,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54">
         <v>52</v>
       </c>
       <c r="B54" t="s">
@@ -2517,7 +2536,7 @@
       <c r="C54" t="s">
         <v>25</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>20260608</v>
       </c>
       <c r="E54" t="s">
@@ -2527,8 +2546,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55">
         <v>53</v>
       </c>
       <c r="B55" t="s">
@@ -2537,7 +2556,7 @@
       <c r="C55" t="s">
         <v>25</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>20260608</v>
       </c>
       <c r="E55" t="s">
@@ -2547,8 +2566,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="n">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56">
         <v>54</v>
       </c>
       <c r="B56" t="s">
@@ -2557,7 +2576,7 @@
       <c r="C56" t="s">
         <v>25</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>20260608</v>
       </c>
       <c r="E56" t="s">
@@ -2567,8 +2586,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57">
         <v>55</v>
       </c>
       <c r="B57" t="s">
@@ -2577,7 +2596,7 @@
       <c r="C57" t="s">
         <v>25</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>20260608</v>
       </c>
       <c r="E57" t="s">
@@ -2587,8 +2606,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="n">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58">
         <v>56</v>
       </c>
       <c r="B58" t="s">
@@ -2597,7 +2616,7 @@
       <c r="C58" t="s">
         <v>25</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>20260608</v>
       </c>
       <c r="E58" t="s">
@@ -2607,8 +2626,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="n">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59">
         <v>57</v>
       </c>
       <c r="B59" t="s">
@@ -2617,7 +2636,7 @@
       <c r="C59" t="s">
         <v>25</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>20260608</v>
       </c>
       <c r="E59" t="s">
@@ -2627,8 +2646,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="n">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60">
         <v>58</v>
       </c>
       <c r="B60" t="s">
@@ -2637,7 +2656,7 @@
       <c r="C60" t="s">
         <v>17</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>20260609</v>
       </c>
       <c r="E60" t="s">
@@ -2647,8 +2666,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="n">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61">
         <v>59</v>
       </c>
       <c r="B61" t="s">
@@ -2657,7 +2676,7 @@
       <c r="C61" t="s">
         <v>25</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>20260609</v>
       </c>
       <c r="E61" t="s">
@@ -2667,8 +2686,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62">
         <v>60</v>
       </c>
       <c r="B62" t="s">
@@ -2677,7 +2696,7 @@
       <c r="C62" t="s">
         <v>46</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>20260609</v>
       </c>
       <c r="E62" t="s">
@@ -2687,8 +2706,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63">
         <v>61</v>
       </c>
       <c r="B63" t="s">
@@ -2697,7 +2716,7 @@
       <c r="C63" t="s">
         <v>17</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>20260609</v>
       </c>
       <c r="E63" t="s">
@@ -2707,8 +2726,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="n">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64">
         <v>62</v>
       </c>
       <c r="B64" t="s">
@@ -2717,7 +2736,7 @@
       <c r="C64" t="s">
         <v>17</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>20260609</v>
       </c>
       <c r="E64" t="s">
@@ -2727,8 +2746,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="n">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65">
         <v>63</v>
       </c>
       <c r="B65" t="s">
@@ -2737,7 +2756,7 @@
       <c r="C65" t="s">
         <v>17</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>20260609</v>
       </c>
       <c r="E65" t="s">
@@ -2747,8 +2766,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="n">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66">
         <v>64</v>
       </c>
       <c r="B66" t="s">
@@ -2757,7 +2776,7 @@
       <c r="C66" t="s">
         <v>17</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>20260609</v>
       </c>
       <c r="E66" t="s">
@@ -2767,8 +2786,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="n">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67">
         <v>65</v>
       </c>
       <c r="B67" t="s">
@@ -2777,7 +2796,7 @@
       <c r="C67" t="s">
         <v>17</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>20260609</v>
       </c>
       <c r="E67" t="s">
@@ -2787,8 +2806,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="n">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68">
         <v>66</v>
       </c>
       <c r="B68" t="s">
@@ -2797,7 +2816,7 @@
       <c r="C68" t="s">
         <v>17</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>20260609</v>
       </c>
       <c r="E68" t="s">
@@ -2807,8 +2826,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="n">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69">
         <v>67</v>
       </c>
       <c r="B69" t="s">
@@ -2817,7 +2836,7 @@
       <c r="C69" t="s">
         <v>17</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>20260609</v>
       </c>
       <c r="E69" t="s">
@@ -2827,8 +2846,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="n">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70">
         <v>68</v>
       </c>
       <c r="B70" t="s">
@@ -2837,7 +2856,7 @@
       <c r="C70" t="s">
         <v>17</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70">
         <v>20260609</v>
       </c>
       <c r="E70" t="s">
@@ -2847,8 +2866,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="n">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71">
         <v>69</v>
       </c>
       <c r="B71" t="s">
@@ -2857,7 +2876,7 @@
       <c r="C71" t="s">
         <v>17</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>20260609</v>
       </c>
       <c r="E71" t="s">
@@ -2867,8 +2886,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="n">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72">
         <v>70</v>
       </c>
       <c r="B72" t="s">
@@ -2877,7 +2896,7 @@
       <c r="C72" t="s">
         <v>17</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72">
         <v>20260609</v>
       </c>
       <c r="E72" t="s">
@@ -2887,8 +2906,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73">
         <v>71</v>
       </c>
       <c r="B73" t="s">
@@ -2897,7 +2916,7 @@
       <c r="C73" t="s">
         <v>17</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>20260609</v>
       </c>
       <c r="E73" t="s">
@@ -2907,8 +2926,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="n">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74">
         <v>72</v>
       </c>
       <c r="B74" t="s">
@@ -2917,7 +2936,7 @@
       <c r="C74" t="s">
         <v>17</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74">
         <v>20260609</v>
       </c>
       <c r="E74" t="s">
@@ -2927,8 +2946,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="n">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75">
         <v>73</v>
       </c>
       <c r="B75" t="s">
@@ -2937,7 +2956,7 @@
       <c r="C75" t="s">
         <v>17</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75">
         <v>20260609</v>
       </c>
       <c r="E75" t="s">
@@ -2947,8 +2966,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="n">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76">
         <v>74</v>
       </c>
       <c r="B76" t="s">
@@ -2957,7 +2976,7 @@
       <c r="C76" t="s">
         <v>17</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76">
         <v>20260609</v>
       </c>
       <c r="E76" t="s">
@@ -2967,8 +2986,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77">
         <v>75</v>
       </c>
       <c r="B77" t="s">
@@ -2977,7 +2996,7 @@
       <c r="C77" t="s">
         <v>17</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77">
         <v>20260609</v>
       </c>
       <c r="E77" t="s">
@@ -2987,8 +3006,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78">
         <v>76</v>
       </c>
       <c r="B78" t="s">
@@ -2997,7 +3016,7 @@
       <c r="C78" t="s">
         <v>17</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78">
         <v>20260609</v>
       </c>
       <c r="E78" t="s">
@@ -3007,8 +3026,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79">
         <v>77</v>
       </c>
       <c r="B79" t="s">
@@ -3017,7 +3036,7 @@
       <c r="C79" t="s">
         <v>25</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79">
         <v>20260609</v>
       </c>
       <c r="E79" t="s">
@@ -3027,8 +3046,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="n">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80">
         <v>78</v>
       </c>
       <c r="B80" t="s">
@@ -3037,7 +3056,7 @@
       <c r="C80" t="s">
         <v>25</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80">
         <v>20260609</v>
       </c>
       <c r="E80" t="s">
@@ -3047,8 +3066,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="n">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81">
         <v>79</v>
       </c>
       <c r="B81" t="s">
@@ -3057,7 +3076,7 @@
       <c r="C81" t="s">
         <v>25</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81">
         <v>20260609</v>
       </c>
       <c r="E81" t="s">
@@ -3067,8 +3086,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="n">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82">
         <v>80</v>
       </c>
       <c r="B82" t="s">
@@ -3077,7 +3096,7 @@
       <c r="C82" t="s">
         <v>25</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82">
         <v>20260609</v>
       </c>
       <c r="E82" t="s">
@@ -3087,8 +3106,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="n">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83">
         <v>81</v>
       </c>
       <c r="B83" t="s">
@@ -3097,7 +3116,7 @@
       <c r="C83" t="s">
         <v>25</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83">
         <v>20260609</v>
       </c>
       <c r="E83" t="s">
@@ -3107,8 +3126,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="n">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84">
         <v>82</v>
       </c>
       <c r="B84" t="s">
@@ -3117,7 +3136,7 @@
       <c r="C84" t="s">
         <v>25</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84">
         <v>20260609</v>
       </c>
       <c r="E84" t="s">
@@ -3127,8 +3146,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="n">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85">
         <v>83</v>
       </c>
       <c r="B85" t="s">
@@ -3137,7 +3156,7 @@
       <c r="C85" t="s">
         <v>25</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85">
         <v>20260609</v>
       </c>
       <c r="E85" t="s">
@@ -3147,8 +3166,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="n">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86">
         <v>84</v>
       </c>
       <c r="B86" t="s">
@@ -3157,7 +3176,7 @@
       <c r="C86" t="s">
         <v>25</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86">
         <v>20260609</v>
       </c>
       <c r="E86" t="s">
@@ -3167,8 +3186,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="n">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87">
         <v>85</v>
       </c>
       <c r="B87" t="s">
@@ -3177,7 +3196,7 @@
       <c r="C87" t="s">
         <v>25</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87">
         <v>20260609</v>
       </c>
       <c r="E87" t="s">
@@ -3187,8 +3206,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="n">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88">
         <v>86</v>
       </c>
       <c r="B88" t="s">
@@ -3197,7 +3216,7 @@
       <c r="C88" t="s">
         <v>25</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88">
         <v>20260609</v>
       </c>
       <c r="E88" t="s">
@@ -3207,8 +3226,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="n">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89">
         <v>87</v>
       </c>
       <c r="B89" t="s">
@@ -3217,7 +3236,7 @@
       <c r="C89" t="s">
         <v>25</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89">
         <v>20260609</v>
       </c>
       <c r="E89" t="s">
@@ -3227,8 +3246,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="n">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90">
         <v>88</v>
       </c>
       <c r="B90" t="s">
@@ -3237,7 +3256,7 @@
       <c r="C90" t="s">
         <v>25</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90">
         <v>20260609</v>
       </c>
       <c r="E90" t="s">
@@ -3247,8 +3266,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="n">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91">
         <v>89</v>
       </c>
       <c r="B91" t="s">
@@ -3257,7 +3276,7 @@
       <c r="C91" t="s">
         <v>25</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91">
         <v>20260609</v>
       </c>
       <c r="E91" t="s">
@@ -3267,8 +3286,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="n">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92">
         <v>90</v>
       </c>
       <c r="B92" t="s">
@@ -3277,7 +3296,7 @@
       <c r="C92" t="s">
         <v>25</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92">
         <v>20260609</v>
       </c>
       <c r="E92" t="s">
@@ -3287,8 +3306,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="n">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93">
         <v>91</v>
       </c>
       <c r="B93" t="s">
@@ -3297,7 +3316,7 @@
       <c r="C93" t="s">
         <v>25</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93">
         <v>20260609</v>
       </c>
       <c r="E93" t="s">
@@ -3307,8 +3326,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="n">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94">
         <v>92</v>
       </c>
       <c r="B94" t="s">
@@ -3317,7 +3336,7 @@
       <c r="C94" t="s">
         <v>25</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94">
         <v>20260609</v>
       </c>
       <c r="E94" t="s">
@@ -3327,8 +3346,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="n">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95">
         <v>93</v>
       </c>
       <c r="B95" t="s">
@@ -3337,7 +3356,7 @@
       <c r="C95" t="s">
         <v>25</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95">
         <v>20260609</v>
       </c>
       <c r="E95" t="s">
@@ -3347,8 +3366,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="n">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96">
         <v>94</v>
       </c>
       <c r="B96" t="s">
@@ -3357,7 +3376,7 @@
       <c r="C96" t="s">
         <v>25</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96">
         <v>20260609</v>
       </c>
       <c r="E96" t="s">
@@ -3367,8 +3386,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="n">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97">
         <v>95</v>
       </c>
       <c r="B97" t="s">
@@ -3377,7 +3396,7 @@
       <c r="C97" t="s">
         <v>17</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97">
         <v>20260609</v>
       </c>
       <c r="E97" t="s">
@@ -3387,8 +3406,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="n">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98">
         <v>96</v>
       </c>
       <c r="B98" t="s">
@@ -3397,7 +3416,7 @@
       <c r="C98" t="s">
         <v>25</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98">
         <v>20260609</v>
       </c>
       <c r="E98" t="s">
@@ -3407,8 +3426,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="n">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99">
         <v>97</v>
       </c>
       <c r="B99" t="s">
@@ -3417,7 +3436,7 @@
       <c r="C99" t="s">
         <v>46</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99">
         <v>20260609</v>
       </c>
       <c r="E99" t="s">
@@ -3427,8 +3446,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="n">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100">
         <v>98</v>
       </c>
       <c r="B100" t="s">
@@ -3437,7 +3456,7 @@
       <c r="C100" t="s">
         <v>17</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100">
         <v>20260609</v>
       </c>
       <c r="E100" t="s">
@@ -3447,8 +3466,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="n">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101">
         <v>99</v>
       </c>
       <c r="B101" t="s">
@@ -3457,7 +3476,7 @@
       <c r="C101" t="s">
         <v>25</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101">
         <v>20260609</v>
       </c>
       <c r="E101" t="s">
@@ -3467,8 +3486,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="n">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102">
         <v>100</v>
       </c>
       <c r="B102" t="s">
@@ -3477,7 +3496,7 @@
       <c r="C102" t="s">
         <v>17</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102">
         <v>20260609</v>
       </c>
       <c r="E102" t="s">
@@ -3487,8 +3506,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="n">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103">
         <v>101</v>
       </c>
       <c r="B103" t="s">
@@ -3497,7 +3516,7 @@
       <c r="C103" t="s">
         <v>25</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103">
         <v>20260609</v>
       </c>
       <c r="E103" t="s">
@@ -3507,8 +3526,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="n">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104">
         <v>102</v>
       </c>
       <c r="B104" t="s">
@@ -3517,7 +3536,7 @@
       <c r="C104" t="s">
         <v>17</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104">
         <v>20260609</v>
       </c>
       <c r="E104" t="s">
@@ -3527,8 +3546,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="n">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105">
         <v>103</v>
       </c>
       <c r="B105" t="s">
@@ -3537,7 +3556,7 @@
       <c r="C105" t="s">
         <v>17</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105">
         <v>20260609</v>
       </c>
       <c r="E105" t="s">
@@ -3547,8 +3566,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="n">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106">
         <v>104</v>
       </c>
       <c r="B106" t="s">
@@ -3557,7 +3576,7 @@
       <c r="C106" t="s">
         <v>17</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106">
         <v>20260609</v>
       </c>
       <c r="E106" t="s">
@@ -3567,8 +3586,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="n">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107">
         <v>105</v>
       </c>
       <c r="B107" t="s">
@@ -3577,7 +3596,7 @@
       <c r="C107" t="s">
         <v>17</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107">
         <v>20260609</v>
       </c>
       <c r="E107" t="s">
@@ -3587,8 +3606,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="n">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108">
         <v>106</v>
       </c>
       <c r="B108" t="s">
@@ -3597,7 +3616,7 @@
       <c r="C108" t="s">
         <v>17</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108">
         <v>20260609</v>
       </c>
       <c r="E108" t="s">
@@ -3607,8 +3626,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="n">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109">
         <v>107</v>
       </c>
       <c r="B109" t="s">
@@ -3617,7 +3636,7 @@
       <c r="C109" t="s">
         <v>17</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109">
         <v>20260609</v>
       </c>
       <c r="E109" t="s">
@@ -3627,8 +3646,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="n">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110">
         <v>108</v>
       </c>
       <c r="B110" t="s">
@@ -3637,7 +3656,7 @@
       <c r="C110" t="s">
         <v>17</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110">
         <v>20260609</v>
       </c>
       <c r="E110" t="s">
@@ -3647,8 +3666,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="n">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111">
         <v>109</v>
       </c>
       <c r="B111" t="s">
@@ -3657,7 +3676,7 @@
       <c r="C111" t="s">
         <v>17</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111">
         <v>20260609</v>
       </c>
       <c r="E111" t="s">
@@ -3667,8 +3686,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="n">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112">
         <v>110</v>
       </c>
       <c r="B112" t="s">
@@ -3677,7 +3696,7 @@
       <c r="C112" t="s">
         <v>17</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112">
         <v>20260609</v>
       </c>
       <c r="E112" t="s">
@@ -3687,8 +3706,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="n">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113">
         <v>111</v>
       </c>
       <c r="B113" t="s">
@@ -3697,7 +3716,7 @@
       <c r="C113" t="s">
         <v>17</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113">
         <v>20260609</v>
       </c>
       <c r="E113" t="s">
@@ -3707,8 +3726,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="n">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114">
         <v>112</v>
       </c>
       <c r="B114" t="s">
@@ -3717,7 +3736,7 @@
       <c r="C114" t="s">
         <v>17</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114">
         <v>20260609</v>
       </c>
       <c r="E114" t="s">
@@ -3727,8 +3746,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="n">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115">
         <v>113</v>
       </c>
       <c r="B115" t="s">
@@ -3737,7 +3756,7 @@
       <c r="C115" t="s">
         <v>17</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115">
         <v>20260609</v>
       </c>
       <c r="E115" t="s">
@@ -3747,8 +3766,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="n">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116">
         <v>114</v>
       </c>
       <c r="B116" t="s">
@@ -3757,7 +3776,7 @@
       <c r="C116" t="s">
         <v>17</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116">
         <v>20260609</v>
       </c>
       <c r="E116" t="s">
@@ -3767,8 +3786,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="n">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117">
         <v>115</v>
       </c>
       <c r="B117" t="s">
@@ -3777,7 +3796,7 @@
       <c r="C117" t="s">
         <v>17</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117">
         <v>20260609</v>
       </c>
       <c r="E117" t="s">
@@ -3787,8 +3806,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="n">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118">
         <v>116</v>
       </c>
       <c r="B118" t="s">
@@ -3797,7 +3816,7 @@
       <c r="C118" t="s">
         <v>17</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118">
         <v>20260609</v>
       </c>
       <c r="E118" t="s">
@@ -3807,8 +3826,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="n">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119">
         <v>117</v>
       </c>
       <c r="B119" t="s">
@@ -3817,7 +3836,7 @@
       <c r="C119" t="s">
         <v>25</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119">
         <v>20260609</v>
       </c>
       <c r="E119" t="s">
@@ -3827,8 +3846,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="n">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120">
         <v>118</v>
       </c>
       <c r="B120" t="s">
@@ -3837,7 +3856,7 @@
       <c r="C120" t="s">
         <v>25</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120">
         <v>20260609</v>
       </c>
       <c r="E120" t="s">
@@ -3847,8 +3866,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="n">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121">
         <v>119</v>
       </c>
       <c r="B121" t="s">
@@ -3857,7 +3876,7 @@
       <c r="C121" t="s">
         <v>25</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121">
         <v>20260609</v>
       </c>
       <c r="E121" t="s">
@@ -3867,8 +3886,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="n">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122">
         <v>120</v>
       </c>
       <c r="B122" t="s">
@@ -3877,7 +3896,7 @@
       <c r="C122" t="s">
         <v>25</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D122">
         <v>20260609</v>
       </c>
       <c r="E122" t="s">
@@ -3887,8 +3906,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="n">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123">
         <v>121</v>
       </c>
       <c r="B123" t="s">
@@ -3897,7 +3916,7 @@
       <c r="C123" t="s">
         <v>25</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123">
         <v>20260609</v>
       </c>
       <c r="E123" t="s">
@@ -3907,8 +3926,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="n">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124">
         <v>122</v>
       </c>
       <c r="B124" t="s">
@@ -3917,7 +3936,7 @@
       <c r="C124" t="s">
         <v>25</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124">
         <v>20260609</v>
       </c>
       <c r="E124" t="s">
@@ -3927,8 +3946,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="n">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125">
         <v>123</v>
       </c>
       <c r="B125" t="s">
@@ -3937,7 +3956,7 @@
       <c r="C125" t="s">
         <v>25</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125">
         <v>20260609</v>
       </c>
       <c r="E125" t="s">
@@ -3947,8 +3966,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="n">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126">
         <v>124</v>
       </c>
       <c r="B126" t="s">
@@ -3957,7 +3976,7 @@
       <c r="C126" t="s">
         <v>25</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126">
         <v>20260609</v>
       </c>
       <c r="E126" t="s">
@@ -3967,8 +3986,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="n">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127">
         <v>125</v>
       </c>
       <c r="B127" t="s">
@@ -3977,7 +3996,7 @@
       <c r="C127" t="s">
         <v>25</v>
       </c>
-      <c r="D127" t="n">
+      <c r="D127">
         <v>20260609</v>
       </c>
       <c r="E127" t="s">
@@ -3987,8 +4006,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="n">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128">
         <v>126</v>
       </c>
       <c r="B128" t="s">
@@ -3997,7 +4016,7 @@
       <c r="C128" t="s">
         <v>25</v>
       </c>
-      <c r="D128" t="n">
+      <c r="D128">
         <v>20260609</v>
       </c>
       <c r="E128" t="s">
@@ -4007,8 +4026,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="n">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129">
         <v>127</v>
       </c>
       <c r="B129" t="s">
@@ -4017,7 +4036,7 @@
       <c r="C129" t="s">
         <v>25</v>
       </c>
-      <c r="D129" t="n">
+      <c r="D129">
         <v>20260609</v>
       </c>
       <c r="E129" t="s">
@@ -4027,8 +4046,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="n">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130">
         <v>128</v>
       </c>
       <c r="B130" t="s">
@@ -4037,7 +4056,7 @@
       <c r="C130" t="s">
         <v>25</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D130">
         <v>20260609</v>
       </c>
       <c r="E130" t="s">
@@ -4047,8 +4066,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="n">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131">
         <v>129</v>
       </c>
       <c r="B131" t="s">
@@ -4057,7 +4076,7 @@
       <c r="C131" t="s">
         <v>25</v>
       </c>
-      <c r="D131" t="n">
+      <c r="D131">
         <v>20260609</v>
       </c>
       <c r="E131" t="s">
@@ -4067,8 +4086,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="n">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132">
         <v>130</v>
       </c>
       <c r="B132" t="s">
@@ -4077,7 +4096,7 @@
       <c r="C132" t="s">
         <v>25</v>
       </c>
-      <c r="D132" t="n">
+      <c r="D132">
         <v>20260609</v>
       </c>
       <c r="E132" t="s">
@@ -4087,8 +4106,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="n">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133">
         <v>131</v>
       </c>
       <c r="B133" t="s">
@@ -4097,7 +4116,7 @@
       <c r="C133" t="s">
         <v>25</v>
       </c>
-      <c r="D133" t="n">
+      <c r="D133">
         <v>20260609</v>
       </c>
       <c r="E133" t="s">
@@ -4107,8 +4126,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="n">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134">
         <v>132</v>
       </c>
       <c r="B134" t="s">
@@ -4117,7 +4136,7 @@
       <c r="C134" t="s">
         <v>25</v>
       </c>
-      <c r="D134" t="n">
+      <c r="D134">
         <v>20260609</v>
       </c>
       <c r="E134" t="s">
@@ -4127,8 +4146,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="n">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135">
         <v>133</v>
       </c>
       <c r="B135" t="s">
@@ -4137,7 +4156,7 @@
       <c r="C135" t="s">
         <v>25</v>
       </c>
-      <c r="D135" t="n">
+      <c r="D135">
         <v>20260609</v>
       </c>
       <c r="E135" t="s">
@@ -4147,8 +4166,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="n">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136">
         <v>134</v>
       </c>
       <c r="B136" t="s">
@@ -4157,7 +4176,7 @@
       <c r="C136" t="s">
         <v>17</v>
       </c>
-      <c r="D136" t="n">
+      <c r="D136">
         <v>20260610</v>
       </c>
       <c r="E136" t="s">
@@ -4167,8 +4186,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="n">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137">
         <v>135</v>
       </c>
       <c r="B137" t="s">
@@ -4177,7 +4196,7 @@
       <c r="C137" t="s">
         <v>17</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D137">
         <v>20260610</v>
       </c>
       <c r="E137" t="s">
@@ -4187,8 +4206,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="n">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138">
         <v>136</v>
       </c>
       <c r="B138" t="s">
@@ -4197,7 +4216,7 @@
       <c r="C138" t="s">
         <v>17</v>
       </c>
-      <c r="D138" t="n">
+      <c r="D138">
         <v>20260610</v>
       </c>
       <c r="E138" t="s">
@@ -4207,8 +4226,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="n">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139">
         <v>137</v>
       </c>
       <c r="B139" t="s">
@@ -4217,7 +4236,7 @@
       <c r="C139" t="s">
         <v>17</v>
       </c>
-      <c r="D139" t="n">
+      <c r="D139">
         <v>20260610</v>
       </c>
       <c r="E139" t="s">
@@ -4227,8 +4246,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="n">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140">
         <v>138</v>
       </c>
       <c r="B140" t="s">
@@ -4237,7 +4256,7 @@
       <c r="C140" t="s">
         <v>17</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D140">
         <v>20260610</v>
       </c>
       <c r="E140" t="s">
@@ -4247,8 +4266,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="n">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141">
         <v>139</v>
       </c>
       <c r="B141" t="s">
@@ -4257,7 +4276,7 @@
       <c r="C141" t="s">
         <v>17</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D141">
         <v>20260610</v>
       </c>
       <c r="E141" t="s">
@@ -4267,8 +4286,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="n">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142">
         <v>140</v>
       </c>
       <c r="B142" t="s">
@@ -4277,7 +4296,7 @@
       <c r="C142" t="s">
         <v>17</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D142">
         <v>20260610</v>
       </c>
       <c r="E142" t="s">
@@ -4287,8 +4306,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="n">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143">
         <v>141</v>
       </c>
       <c r="B143" t="s">
@@ -4297,7 +4316,7 @@
       <c r="C143" t="s">
         <v>17</v>
       </c>
-      <c r="D143" t="n">
+      <c r="D143">
         <v>20260610</v>
       </c>
       <c r="E143" t="s">
@@ -4307,8 +4326,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="n">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144">
         <v>142</v>
       </c>
       <c r="B144" t="s">
@@ -4317,7 +4336,7 @@
       <c r="C144" t="s">
         <v>17</v>
       </c>
-      <c r="D144" t="n">
+      <c r="D144">
         <v>20260610</v>
       </c>
       <c r="E144" t="s">
@@ -4327,8 +4346,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="n">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145">
         <v>143</v>
       </c>
       <c r="B145" t="s">
@@ -4337,7 +4356,7 @@
       <c r="C145" t="s">
         <v>17</v>
       </c>
-      <c r="D145" t="n">
+      <c r="D145">
         <v>20260610</v>
       </c>
       <c r="E145" t="s">
@@ -4347,8 +4366,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="n">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146">
         <v>144</v>
       </c>
       <c r="B146" t="s">
@@ -4357,7 +4376,7 @@
       <c r="C146" t="s">
         <v>17</v>
       </c>
-      <c r="D146" t="n">
+      <c r="D146">
         <v>20260610</v>
       </c>
       <c r="E146" t="s">
@@ -4367,8 +4386,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="n">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147">
         <v>145</v>
       </c>
       <c r="B147" t="s">
@@ -4377,7 +4396,7 @@
       <c r="C147" t="s">
         <v>17</v>
       </c>
-      <c r="D147" t="n">
+      <c r="D147">
         <v>20260610</v>
       </c>
       <c r="E147" t="s">
@@ -4387,8 +4406,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="n">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148">
         <v>146</v>
       </c>
       <c r="B148" t="s">
@@ -4397,7 +4416,7 @@
       <c r="C148" t="s">
         <v>17</v>
       </c>
-      <c r="D148" t="n">
+      <c r="D148">
         <v>20260610</v>
       </c>
       <c r="E148" t="s">
@@ -4407,8 +4426,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="n">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149">
         <v>147</v>
       </c>
       <c r="B149" t="s">
@@ -4417,7 +4436,7 @@
       <c r="C149" t="s">
         <v>17</v>
       </c>
-      <c r="D149" t="n">
+      <c r="D149">
         <v>20260610</v>
       </c>
       <c r="E149" t="s">
@@ -4427,8 +4446,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="n">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150">
         <v>148</v>
       </c>
       <c r="B150" t="s">
@@ -4437,7 +4456,7 @@
       <c r="C150" t="s">
         <v>17</v>
       </c>
-      <c r="D150" t="n">
+      <c r="D150">
         <v>20260610</v>
       </c>
       <c r="E150" t="s">
@@ -4447,8 +4466,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="n">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151">
         <v>149</v>
       </c>
       <c r="B151" t="s">
@@ -4457,7 +4476,7 @@
       <c r="C151" t="s">
         <v>17</v>
       </c>
-      <c r="D151" t="n">
+      <c r="D151">
         <v>20260610</v>
       </c>
       <c r="E151" t="s">
@@ -4467,8 +4486,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="n">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152">
         <v>150</v>
       </c>
       <c r="B152" t="s">
@@ -4477,7 +4496,7 @@
       <c r="C152" t="s">
         <v>17</v>
       </c>
-      <c r="D152" t="n">
+      <c r="D152">
         <v>20260610</v>
       </c>
       <c r="E152" t="s">
@@ -4487,8 +4506,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="n">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153">
         <v>151</v>
       </c>
       <c r="B153" t="s">
@@ -4497,7 +4516,7 @@
       <c r="C153" t="s">
         <v>17</v>
       </c>
-      <c r="D153" t="n">
+      <c r="D153">
         <v>20260610</v>
       </c>
       <c r="E153" t="s">
@@ -4507,8 +4526,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="n">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154">
         <v>152</v>
       </c>
       <c r="B154" t="s">
@@ -4517,7 +4536,7 @@
       <c r="C154" t="s">
         <v>25</v>
       </c>
-      <c r="D154" t="n">
+      <c r="D154">
         <v>20260610</v>
       </c>
       <c r="E154" t="s">
@@ -4527,8 +4546,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="n">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155">
         <v>153</v>
       </c>
       <c r="B155" t="s">
@@ -4537,7 +4556,7 @@
       <c r="C155" t="s">
         <v>25</v>
       </c>
-      <c r="D155" t="n">
+      <c r="D155">
         <v>20260610</v>
       </c>
       <c r="E155" t="s">
@@ -4547,8 +4566,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="n">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156">
         <v>154</v>
       </c>
       <c r="B156" t="s">
@@ -4557,7 +4576,7 @@
       <c r="C156" t="s">
         <v>25</v>
       </c>
-      <c r="D156" t="n">
+      <c r="D156">
         <v>20260610</v>
       </c>
       <c r="E156" t="s">
@@ -4567,8 +4586,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="n">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157">
         <v>155</v>
       </c>
       <c r="B157" t="s">
@@ -4577,7 +4596,7 @@
       <c r="C157" t="s">
         <v>25</v>
       </c>
-      <c r="D157" t="n">
+      <c r="D157">
         <v>20260610</v>
       </c>
       <c r="E157" t="s">
@@ -4587,8 +4606,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="n">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158">
         <v>156</v>
       </c>
       <c r="B158" t="s">
@@ -4597,7 +4616,7 @@
       <c r="C158" t="s">
         <v>25</v>
       </c>
-      <c r="D158" t="n">
+      <c r="D158">
         <v>20260610</v>
       </c>
       <c r="E158" t="s">
@@ -4607,8 +4626,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="n">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159">
         <v>157</v>
       </c>
       <c r="B159" t="s">
@@ -4617,7 +4636,7 @@
       <c r="C159" t="s">
         <v>25</v>
       </c>
-      <c r="D159" t="n">
+      <c r="D159">
         <v>20260610</v>
       </c>
       <c r="E159" t="s">
@@ -4627,8 +4646,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="n">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160">
         <v>158</v>
       </c>
       <c r="B160" t="s">
@@ -4637,7 +4656,7 @@
       <c r="C160" t="s">
         <v>25</v>
       </c>
-      <c r="D160" t="n">
+      <c r="D160">
         <v>20260610</v>
       </c>
       <c r="E160" t="s">
@@ -4647,8 +4666,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="n">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161">
         <v>159</v>
       </c>
       <c r="B161" t="s">
@@ -4657,7 +4676,7 @@
       <c r="C161" t="s">
         <v>25</v>
       </c>
-      <c r="D161" t="n">
+      <c r="D161">
         <v>20260610</v>
       </c>
       <c r="E161" t="s">
@@ -4667,8 +4686,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="n">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162">
         <v>160</v>
       </c>
       <c r="B162" t="s">
@@ -4677,7 +4696,7 @@
       <c r="C162" t="s">
         <v>25</v>
       </c>
-      <c r="D162" t="n">
+      <c r="D162">
         <v>20260610</v>
       </c>
       <c r="E162" t="s">
@@ -4687,8 +4706,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="n">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163">
         <v>161</v>
       </c>
       <c r="B163" t="s">
@@ -4697,7 +4716,7 @@
       <c r="C163" t="s">
         <v>25</v>
       </c>
-      <c r="D163" t="n">
+      <c r="D163">
         <v>20260610</v>
       </c>
       <c r="E163" t="s">
@@ -4707,8 +4726,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="n">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164">
         <v>162</v>
       </c>
       <c r="B164" t="s">
@@ -4717,7 +4736,7 @@
       <c r="C164" t="s">
         <v>25</v>
       </c>
-      <c r="D164" t="n">
+      <c r="D164">
         <v>20260610</v>
       </c>
       <c r="E164" t="s">
@@ -4727,8 +4746,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="n">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165">
         <v>163</v>
       </c>
       <c r="B165" t="s">
@@ -4737,7 +4756,7 @@
       <c r="C165" t="s">
         <v>25</v>
       </c>
-      <c r="D165" t="n">
+      <c r="D165">
         <v>20260610</v>
       </c>
       <c r="E165" t="s">
@@ -4747,8 +4766,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="n">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166">
         <v>164</v>
       </c>
       <c r="B166" t="s">
@@ -4757,7 +4776,7 @@
       <c r="C166" t="s">
         <v>25</v>
       </c>
-      <c r="D166" t="n">
+      <c r="D166">
         <v>20260610</v>
       </c>
       <c r="E166" t="s">
@@ -4767,8 +4786,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="n">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167">
         <v>165</v>
       </c>
       <c r="B167" t="s">
@@ -4777,7 +4796,7 @@
       <c r="C167" t="s">
         <v>25</v>
       </c>
-      <c r="D167" t="n">
+      <c r="D167">
         <v>20260610</v>
       </c>
       <c r="E167" t="s">
@@ -4787,8 +4806,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="n">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168">
         <v>166</v>
       </c>
       <c r="B168" t="s">
@@ -4797,7 +4816,7 @@
       <c r="C168" t="s">
         <v>25</v>
       </c>
-      <c r="D168" t="n">
+      <c r="D168">
         <v>20260610</v>
       </c>
       <c r="E168" t="s">
@@ -4807,8 +4826,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="n">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169">
         <v>167</v>
       </c>
       <c r="B169" t="s">
@@ -4817,7 +4836,7 @@
       <c r="C169" t="s">
         <v>25</v>
       </c>
-      <c r="D169" t="n">
+      <c r="D169">
         <v>20260610</v>
       </c>
       <c r="E169" t="s">
@@ -4827,8 +4846,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="n">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170">
         <v>168</v>
       </c>
       <c r="B170" t="s">
@@ -4837,7 +4856,7 @@
       <c r="C170" t="s">
         <v>25</v>
       </c>
-      <c r="D170" t="n">
+      <c r="D170">
         <v>20260610</v>
       </c>
       <c r="E170" t="s">
@@ -4847,8 +4866,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="n">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171">
         <v>169</v>
       </c>
       <c r="B171" t="s">
@@ -4857,7 +4876,7 @@
       <c r="C171" t="s">
         <v>25</v>
       </c>
-      <c r="D171" t="n">
+      <c r="D171">
         <v>20260610</v>
       </c>
       <c r="E171" t="s">
@@ -4867,8 +4886,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="n">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172">
         <v>170</v>
       </c>
       <c r="B172" t="s">
@@ -4877,7 +4896,7 @@
       <c r="C172" t="s">
         <v>17</v>
       </c>
-      <c r="D172" t="n">
+      <c r="D172">
         <v>20260610</v>
       </c>
       <c r="E172" t="s">
@@ -4887,8 +4906,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="n">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173">
         <v>171</v>
       </c>
       <c r="B173" t="s">
@@ -4897,7 +4916,7 @@
       <c r="C173" t="s">
         <v>25</v>
       </c>
-      <c r="D173" t="n">
+      <c r="D173">
         <v>20260610</v>
       </c>
       <c r="E173" t="s">
@@ -4907,8 +4926,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="n">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174">
         <v>172</v>
       </c>
       <c r="B174" t="s">
@@ -4917,7 +4936,7 @@
       <c r="C174" t="s">
         <v>46</v>
       </c>
-      <c r="D174" t="n">
+      <c r="D174">
         <v>20260610</v>
       </c>
       <c r="E174" t="s">
@@ -4927,8 +4946,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="n">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175">
         <v>173</v>
       </c>
       <c r="B175" t="s">
@@ -4937,7 +4956,7 @@
       <c r="C175" t="s">
         <v>17</v>
       </c>
-      <c r="D175" t="n">
+      <c r="D175">
         <v>20260610</v>
       </c>
       <c r="E175" t="s">
@@ -4947,8 +4966,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="n">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176">
         <v>174</v>
       </c>
       <c r="B176" t="s">
@@ -4957,7 +4976,7 @@
       <c r="C176" t="s">
         <v>17</v>
       </c>
-      <c r="D176" t="n">
+      <c r="D176">
         <v>20260610</v>
       </c>
       <c r="E176" t="s">
@@ -4967,8 +4986,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="n">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177">
         <v>175</v>
       </c>
       <c r="B177" t="s">
@@ -4977,7 +4996,7 @@
       <c r="C177" t="s">
         <v>17</v>
       </c>
-      <c r="D177" t="n">
+      <c r="D177">
         <v>20260610</v>
       </c>
       <c r="E177" t="s">
@@ -4987,8 +5006,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="n">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178">
         <v>176</v>
       </c>
       <c r="B178" t="s">
@@ -4997,7 +5016,7 @@
       <c r="C178" t="s">
         <v>17</v>
       </c>
-      <c r="D178" t="n">
+      <c r="D178">
         <v>20260610</v>
       </c>
       <c r="E178" t="s">
@@ -5007,8 +5026,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="n">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179">
         <v>177</v>
       </c>
       <c r="B179" t="s">
@@ -5017,7 +5036,7 @@
       <c r="C179" t="s">
         <v>17</v>
       </c>
-      <c r="D179" t="n">
+      <c r="D179">
         <v>20260610</v>
       </c>
       <c r="E179" t="s">
@@ -5027,8 +5046,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="n">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180">
         <v>178</v>
       </c>
       <c r="B180" t="s">
@@ -5037,7 +5056,7 @@
       <c r="C180" t="s">
         <v>17</v>
       </c>
-      <c r="D180" t="n">
+      <c r="D180">
         <v>20260610</v>
       </c>
       <c r="E180" t="s">
@@ -5047,8 +5066,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="n">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181">
         <v>179</v>
       </c>
       <c r="B181" t="s">
@@ -5057,7 +5076,7 @@
       <c r="C181" t="s">
         <v>17</v>
       </c>
-      <c r="D181" t="n">
+      <c r="D181">
         <v>20260610</v>
       </c>
       <c r="E181" t="s">
@@ -5067,8 +5086,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="n">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182">
         <v>180</v>
       </c>
       <c r="B182" t="s">
@@ -5077,7 +5096,7 @@
       <c r="C182" t="s">
         <v>17</v>
       </c>
-      <c r="D182" t="n">
+      <c r="D182">
         <v>20260610</v>
       </c>
       <c r="E182" t="s">
@@ -5087,8 +5106,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="n">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183">
         <v>181</v>
       </c>
       <c r="B183" t="s">
@@ -5097,7 +5116,7 @@
       <c r="C183" t="s">
         <v>17</v>
       </c>
-      <c r="D183" t="n">
+      <c r="D183">
         <v>20260610</v>
       </c>
       <c r="E183" t="s">
@@ -5107,8 +5126,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="n">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184">
         <v>182</v>
       </c>
       <c r="B184" t="s">
@@ -5117,7 +5136,7 @@
       <c r="C184" t="s">
         <v>17</v>
       </c>
-      <c r="D184" t="n">
+      <c r="D184">
         <v>20260610</v>
       </c>
       <c r="E184" t="s">
@@ -5127,8 +5146,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="n">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185">
         <v>183</v>
       </c>
       <c r="B185" t="s">
@@ -5137,7 +5156,7 @@
       <c r="C185" t="s">
         <v>17</v>
       </c>
-      <c r="D185" t="n">
+      <c r="D185">
         <v>20260610</v>
       </c>
       <c r="E185" t="s">
@@ -5147,8 +5166,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="n">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186">
         <v>184</v>
       </c>
       <c r="B186" t="s">
@@ -5157,7 +5176,7 @@
       <c r="C186" t="s">
         <v>17</v>
       </c>
-      <c r="D186" t="n">
+      <c r="D186">
         <v>20260610</v>
       </c>
       <c r="E186" t="s">
@@ -5167,8 +5186,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="n">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187">
         <v>185</v>
       </c>
       <c r="B187" t="s">
@@ -5177,7 +5196,7 @@
       <c r="C187" t="s">
         <v>17</v>
       </c>
-      <c r="D187" t="n">
+      <c r="D187">
         <v>20260610</v>
       </c>
       <c r="E187" t="s">
@@ -5187,8 +5206,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="n">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188">
         <v>186</v>
       </c>
       <c r="B188" t="s">
@@ -5197,7 +5216,7 @@
       <c r="C188" t="s">
         <v>25</v>
       </c>
-      <c r="D188" t="n">
+      <c r="D188">
         <v>20260610</v>
       </c>
       <c r="E188" t="s">
@@ -5207,8 +5226,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="n">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189">
         <v>187</v>
       </c>
       <c r="B189" t="s">
@@ -5217,7 +5236,7 @@
       <c r="C189" t="s">
         <v>25</v>
       </c>
-      <c r="D189" t="n">
+      <c r="D189">
         <v>20260610</v>
       </c>
       <c r="E189" t="s">
@@ -5227,8 +5246,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="n">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190">
         <v>188</v>
       </c>
       <c r="B190" t="s">
@@ -5237,7 +5256,7 @@
       <c r="C190" t="s">
         <v>25</v>
       </c>
-      <c r="D190" t="n">
+      <c r="D190">
         <v>20260610</v>
       </c>
       <c r="E190" t="s">
@@ -5247,8 +5266,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="n">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191">
         <v>189</v>
       </c>
       <c r="B191" t="s">
@@ -5257,7 +5276,7 @@
       <c r="C191" t="s">
         <v>25</v>
       </c>
-      <c r="D191" t="n">
+      <c r="D191">
         <v>20260610</v>
       </c>
       <c r="E191" t="s">
@@ -5267,8 +5286,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="n">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192">
         <v>190</v>
       </c>
       <c r="B192" t="s">
@@ -5277,7 +5296,7 @@
       <c r="C192" t="s">
         <v>25</v>
       </c>
-      <c r="D192" t="n">
+      <c r="D192">
         <v>20260610</v>
       </c>
       <c r="E192" t="s">
@@ -5287,8 +5306,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="n">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193">
         <v>191</v>
       </c>
       <c r="B193" t="s">
@@ -5297,7 +5316,7 @@
       <c r="C193" t="s">
         <v>25</v>
       </c>
-      <c r="D193" t="n">
+      <c r="D193">
         <v>20260610</v>
       </c>
       <c r="E193" t="s">
@@ -5307,8 +5326,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="n">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194">
         <v>192</v>
       </c>
       <c r="B194" t="s">
@@ -5317,7 +5336,7 @@
       <c r="C194" t="s">
         <v>25</v>
       </c>
-      <c r="D194" t="n">
+      <c r="D194">
         <v>20260610</v>
       </c>
       <c r="E194" t="s">
@@ -5327,8 +5346,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="n">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195">
         <v>193</v>
       </c>
       <c r="B195" t="s">
@@ -5337,7 +5356,7 @@
       <c r="C195" t="s">
         <v>25</v>
       </c>
-      <c r="D195" t="n">
+      <c r="D195">
         <v>20260610</v>
       </c>
       <c r="E195" t="s">
@@ -5347,8 +5366,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="n">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196">
         <v>194</v>
       </c>
       <c r="B196" t="s">
@@ -5357,7 +5376,7 @@
       <c r="C196" t="s">
         <v>25</v>
       </c>
-      <c r="D196" t="n">
+      <c r="D196">
         <v>20260610</v>
       </c>
       <c r="E196" t="s">
@@ -5367,8 +5386,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="n">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197">
         <v>195</v>
       </c>
       <c r="B197" t="s">
@@ -5377,7 +5396,7 @@
       <c r="C197" t="s">
         <v>25</v>
       </c>
-      <c r="D197" t="n">
+      <c r="D197">
         <v>20260610</v>
       </c>
       <c r="E197" t="s">
@@ -5387,8 +5406,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="n">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198">
         <v>196</v>
       </c>
       <c r="B198" t="s">
@@ -5397,7 +5416,7 @@
       <c r="C198" t="s">
         <v>25</v>
       </c>
-      <c r="D198" t="n">
+      <c r="D198">
         <v>20260610</v>
       </c>
       <c r="E198" t="s">
@@ -5407,8 +5426,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="n">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199">
         <v>197</v>
       </c>
       <c r="B199" t="s">
@@ -5417,7 +5436,7 @@
       <c r="C199" t="s">
         <v>25</v>
       </c>
-      <c r="D199" t="n">
+      <c r="D199">
         <v>20260610</v>
       </c>
       <c r="E199" t="s">
@@ -5427,8 +5446,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="n">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200">
         <v>198</v>
       </c>
       <c r="B200" t="s">
@@ -5437,7 +5456,7 @@
       <c r="C200" t="s">
         <v>25</v>
       </c>
-      <c r="D200" t="n">
+      <c r="D200">
         <v>20260610</v>
       </c>
       <c r="E200" t="s">
@@ -5447,8 +5466,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="n">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201">
         <v>199</v>
       </c>
       <c r="B201" t="s">
@@ -5457,7 +5476,7 @@
       <c r="C201" t="s">
         <v>25</v>
       </c>
-      <c r="D201" t="n">
+      <c r="D201">
         <v>20260610</v>
       </c>
       <c r="E201" t="s">
@@ -5467,8 +5486,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="n">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202">
         <v>200</v>
       </c>
       <c r="B202" t="s">
@@ -5477,7 +5496,7 @@
       <c r="C202" t="s">
         <v>25</v>
       </c>
-      <c r="D202" t="n">
+      <c r="D202">
         <v>20260610</v>
       </c>
       <c r="E202" t="s">
@@ -5487,8 +5506,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="n">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203">
         <v>201</v>
       </c>
       <c r="B203" t="s">
@@ -5497,7 +5516,7 @@
       <c r="C203" t="s">
         <v>25</v>
       </c>
-      <c r="D203" t="n">
+      <c r="D203">
         <v>20260610</v>
       </c>
       <c r="E203" t="s">
@@ -5507,8 +5526,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="n">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204">
         <v>202</v>
       </c>
       <c r="B204" t="s">
@@ -5517,7 +5536,7 @@
       <c r="C204" t="s">
         <v>25</v>
       </c>
-      <c r="D204" t="n">
+      <c r="D204">
         <v>20260610</v>
       </c>
       <c r="E204" t="s">
@@ -5527,8 +5546,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="n">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205">
         <v>203</v>
       </c>
       <c r="B205" t="s">
@@ -5537,7 +5556,7 @@
       <c r="C205" t="s">
         <v>25</v>
       </c>
-      <c r="D205" t="n">
+      <c r="D205">
         <v>20260610</v>
       </c>
       <c r="E205" t="s">
@@ -5547,8 +5566,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="n">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206">
         <v>204</v>
       </c>
       <c r="B206" t="s">
@@ -5557,7 +5576,7 @@
       <c r="C206" t="s">
         <v>17</v>
       </c>
-      <c r="D206" t="n">
+      <c r="D206">
         <v>20260610</v>
       </c>
       <c r="E206" t="s">
@@ -5567,8 +5586,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="n">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207">
         <v>205</v>
       </c>
       <c r="B207" t="s">
@@ -5577,7 +5596,7 @@
       <c r="C207" t="s">
         <v>25</v>
       </c>
-      <c r="D207" t="n">
+      <c r="D207">
         <v>20260610</v>
       </c>
       <c r="E207" t="s">
@@ -5587,8 +5606,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="n">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208">
         <v>206</v>
       </c>
       <c r="B208" t="s">
@@ -5597,7 +5616,7 @@
       <c r="C208" t="s">
         <v>46</v>
       </c>
-      <c r="D208" t="n">
+      <c r="D208">
         <v>20260610</v>
       </c>
       <c r="E208" t="s">
@@ -5607,8 +5626,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="n">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209">
         <v>207</v>
       </c>
       <c r="B209" t="s">
@@ -5617,7 +5636,7 @@
       <c r="C209" t="s">
         <v>17</v>
       </c>
-      <c r="D209" t="n">
+      <c r="D209">
         <v>20260610</v>
       </c>
       <c r="E209" t="s">
@@ -5627,8 +5646,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="n">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210">
         <v>208</v>
       </c>
       <c r="B210" t="s">
@@ -5637,7 +5656,7 @@
       <c r="C210" t="s">
         <v>25</v>
       </c>
-      <c r="D210" t="n">
+      <c r="D210">
         <v>20260610</v>
       </c>
       <c r="E210" t="s">
@@ -5647,8 +5666,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="n">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211">
         <v>209</v>
       </c>
       <c r="B211" t="s">
@@ -5657,7 +5676,7 @@
       <c r="C211" t="s">
         <v>17</v>
       </c>
-      <c r="D211" t="n">
+      <c r="D211">
         <v>20260610</v>
       </c>
       <c r="E211" t="s">
@@ -5667,8 +5686,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="n">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212">
         <v>210</v>
       </c>
       <c r="B212" t="s">
@@ -5677,7 +5696,7 @@
       <c r="C212" t="s">
         <v>25</v>
       </c>
-      <c r="D212" t="n">
+      <c r="D212">
         <v>20260610</v>
       </c>
       <c r="E212" t="s">
@@ -5687,8 +5706,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="n">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213">
         <v>211</v>
       </c>
       <c r="B213" t="s">
@@ -5697,7 +5716,7 @@
       <c r="C213" t="s">
         <v>17</v>
       </c>
-      <c r="D213" t="n">
+      <c r="D213">
         <v>20260611</v>
       </c>
       <c r="E213" t="s">
@@ -5707,8 +5726,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="n">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214">
         <v>212</v>
       </c>
       <c r="B214" t="s">
@@ -5717,7 +5736,7 @@
       <c r="C214" t="s">
         <v>17</v>
       </c>
-      <c r="D214" t="n">
+      <c r="D214">
         <v>20260611</v>
       </c>
       <c r="E214" t="s">
@@ -5727,8 +5746,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="n">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215">
         <v>213</v>
       </c>
       <c r="B215" t="s">
@@ -5737,7 +5756,7 @@
       <c r="C215" t="s">
         <v>17</v>
       </c>
-      <c r="D215" t="n">
+      <c r="D215">
         <v>20260611</v>
       </c>
       <c r="E215" t="s">
@@ -5747,8 +5766,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="n">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216">
         <v>214</v>
       </c>
       <c r="B216" t="s">
@@ -5757,7 +5776,7 @@
       <c r="C216" t="s">
         <v>17</v>
       </c>
-      <c r="D216" t="n">
+      <c r="D216">
         <v>20260611</v>
       </c>
       <c r="E216" t="s">
@@ -5767,8 +5786,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="n">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217">
         <v>215</v>
       </c>
       <c r="B217" t="s">
@@ -5777,7 +5796,7 @@
       <c r="C217" t="s">
         <v>17</v>
       </c>
-      <c r="D217" t="n">
+      <c r="D217">
         <v>20260611</v>
       </c>
       <c r="E217" t="s">
@@ -5787,8 +5806,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="n">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218">
         <v>216</v>
       </c>
       <c r="B218" t="s">
@@ -5797,7 +5816,7 @@
       <c r="C218" t="s">
         <v>17</v>
       </c>
-      <c r="D218" t="n">
+      <c r="D218">
         <v>20260611</v>
       </c>
       <c r="E218" t="s">
@@ -5807,8 +5826,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="n">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219">
         <v>217</v>
       </c>
       <c r="B219" t="s">
@@ -5817,7 +5836,7 @@
       <c r="C219" t="s">
         <v>17</v>
       </c>
-      <c r="D219" t="n">
+      <c r="D219">
         <v>20260611</v>
       </c>
       <c r="E219" t="s">
@@ -5827,8 +5846,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="n">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220">
         <v>218</v>
       </c>
       <c r="B220" t="s">
@@ -5837,7 +5856,7 @@
       <c r="C220" t="s">
         <v>17</v>
       </c>
-      <c r="D220" t="n">
+      <c r="D220">
         <v>20260611</v>
       </c>
       <c r="E220" t="s">
@@ -5847,8 +5866,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="n">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221">
         <v>219</v>
       </c>
       <c r="B221" t="s">
@@ -5857,7 +5876,7 @@
       <c r="C221" t="s">
         <v>17</v>
       </c>
-      <c r="D221" t="n">
+      <c r="D221">
         <v>20260611</v>
       </c>
       <c r="E221" t="s">
@@ -5867,8 +5886,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="n">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222">
         <v>220</v>
       </c>
       <c r="B222" t="s">
@@ -5877,7 +5896,7 @@
       <c r="C222" t="s">
         <v>17</v>
       </c>
-      <c r="D222" t="n">
+      <c r="D222">
         <v>20260611</v>
       </c>
       <c r="E222" t="s">
@@ -5887,8 +5906,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="n">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223">
         <v>221</v>
       </c>
       <c r="B223" t="s">
@@ -5897,7 +5916,7 @@
       <c r="C223" t="s">
         <v>17</v>
       </c>
-      <c r="D223" t="n">
+      <c r="D223">
         <v>20260611</v>
       </c>
       <c r="E223" t="s">
@@ -5907,8 +5926,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="n">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224">
         <v>222</v>
       </c>
       <c r="B224" t="s">
@@ -5917,7 +5936,7 @@
       <c r="C224" t="s">
         <v>17</v>
       </c>
-      <c r="D224" t="n">
+      <c r="D224">
         <v>20260611</v>
       </c>
       <c r="E224" t="s">
@@ -5927,8 +5946,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="n">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225">
         <v>223</v>
       </c>
       <c r="B225" t="s">
@@ -5937,7 +5956,7 @@
       <c r="C225" t="s">
         <v>17</v>
       </c>
-      <c r="D225" t="n">
+      <c r="D225">
         <v>20260611</v>
       </c>
       <c r="E225" t="s">
@@ -5947,8 +5966,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="n">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226">
         <v>224</v>
       </c>
       <c r="B226" t="s">
@@ -5957,7 +5976,7 @@
       <c r="C226" t="s">
         <v>17</v>
       </c>
-      <c r="D226" t="n">
+      <c r="D226">
         <v>20260611</v>
       </c>
       <c r="E226" t="s">
@@ -5967,8 +5986,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" t="n">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227">
         <v>225</v>
       </c>
       <c r="B227" t="s">
@@ -5977,7 +5996,7 @@
       <c r="C227" t="s">
         <v>17</v>
       </c>
-      <c r="D227" t="n">
+      <c r="D227">
         <v>20260611</v>
       </c>
       <c r="E227" t="s">
@@ -5987,8 +6006,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="n">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A228">
         <v>226</v>
       </c>
       <c r="B228" t="s">
@@ -5997,7 +6016,7 @@
       <c r="C228" t="s">
         <v>17</v>
       </c>
-      <c r="D228" t="n">
+      <c r="D228">
         <v>20260611</v>
       </c>
       <c r="E228" t="s">
@@ -6007,8 +6026,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="n">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A229">
         <v>227</v>
       </c>
       <c r="B229" t="s">
@@ -6017,7 +6036,7 @@
       <c r="C229" t="s">
         <v>17</v>
       </c>
-      <c r="D229" t="n">
+      <c r="D229">
         <v>20260611</v>
       </c>
       <c r="E229" t="s">
@@ -6027,8 +6046,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="n">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230">
         <v>228</v>
       </c>
       <c r="B230" t="s">
@@ -6037,7 +6056,7 @@
       <c r="C230" t="s">
         <v>17</v>
       </c>
-      <c r="D230" t="n">
+      <c r="D230">
         <v>20260611</v>
       </c>
       <c r="E230" t="s">
@@ -6047,8 +6066,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="n">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231">
         <v>229</v>
       </c>
       <c r="B231" t="s">
@@ -6057,7 +6076,7 @@
       <c r="C231" t="s">
         <v>17</v>
       </c>
-      <c r="D231" t="n">
+      <c r="D231">
         <v>20260611</v>
       </c>
       <c r="E231" t="s">
@@ -6067,8 +6086,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" t="n">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232">
         <v>230</v>
       </c>
       <c r="B232" t="s">
@@ -6077,7 +6096,7 @@
       <c r="C232" t="s">
         <v>17</v>
       </c>
-      <c r="D232" t="n">
+      <c r="D232">
         <v>20260611</v>
       </c>
       <c r="E232" t="s">
@@ -6087,8 +6106,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="n">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233">
         <v>231</v>
       </c>
       <c r="B233" t="s">
@@ -6097,7 +6116,7 @@
       <c r="C233" t="s">
         <v>25</v>
       </c>
-      <c r="D233" t="n">
+      <c r="D233">
         <v>20260611</v>
       </c>
       <c r="E233" t="s">
@@ -6107,8 +6126,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="n">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234">
         <v>232</v>
       </c>
       <c r="B234" t="s">
@@ -6117,7 +6136,7 @@
       <c r="C234" t="s">
         <v>25</v>
       </c>
-      <c r="D234" t="n">
+      <c r="D234">
         <v>20260611</v>
       </c>
       <c r="E234" t="s">
@@ -6127,8 +6146,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="n">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235">
         <v>233</v>
       </c>
       <c r="B235" t="s">
@@ -6137,7 +6156,7 @@
       <c r="C235" t="s">
         <v>25</v>
       </c>
-      <c r="D235" t="n">
+      <c r="D235">
         <v>20260611</v>
       </c>
       <c r="E235" t="s">
@@ -6147,8 +6166,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="n">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236">
         <v>234</v>
       </c>
       <c r="B236" t="s">
@@ -6157,7 +6176,7 @@
       <c r="C236" t="s">
         <v>25</v>
       </c>
-      <c r="D236" t="n">
+      <c r="D236">
         <v>20260611</v>
       </c>
       <c r="E236" t="s">
@@ -6167,8 +6186,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="n">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237">
         <v>235</v>
       </c>
       <c r="B237" t="s">
@@ -6177,7 +6196,7 @@
       <c r="C237" t="s">
         <v>25</v>
       </c>
-      <c r="D237" t="n">
+      <c r="D237">
         <v>20260611</v>
       </c>
       <c r="E237" t="s">
@@ -6187,8 +6206,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="n">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A238">
         <v>236</v>
       </c>
       <c r="B238" t="s">
@@ -6197,7 +6216,7 @@
       <c r="C238" t="s">
         <v>25</v>
       </c>
-      <c r="D238" t="n">
+      <c r="D238">
         <v>20260611</v>
       </c>
       <c r="E238" t="s">
@@ -6207,8 +6226,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="n">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A239">
         <v>237</v>
       </c>
       <c r="B239" t="s">
@@ -6217,7 +6236,7 @@
       <c r="C239" t="s">
         <v>25</v>
       </c>
-      <c r="D239" t="n">
+      <c r="D239">
         <v>20260611</v>
       </c>
       <c r="E239" t="s">
@@ -6227,8 +6246,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="n">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A240">
         <v>238</v>
       </c>
       <c r="B240" t="s">
@@ -6237,7 +6256,7 @@
       <c r="C240" t="s">
         <v>25</v>
       </c>
-      <c r="D240" t="n">
+      <c r="D240">
         <v>20260611</v>
       </c>
       <c r="E240" t="s">
@@ -6247,8 +6266,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="n">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A241">
         <v>239</v>
       </c>
       <c r="B241" t="s">
@@ -6257,7 +6276,7 @@
       <c r="C241" t="s">
         <v>25</v>
       </c>
-      <c r="D241" t="n">
+      <c r="D241">
         <v>20260611</v>
       </c>
       <c r="E241" t="s">
@@ -6267,8 +6286,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="n">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A242">
         <v>240</v>
       </c>
       <c r="B242" t="s">
@@ -6277,7 +6296,7 @@
       <c r="C242" t="s">
         <v>25</v>
       </c>
-      <c r="D242" t="n">
+      <c r="D242">
         <v>20260611</v>
       </c>
       <c r="E242" t="s">
@@ -6287,8 +6306,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="n">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A243">
         <v>241</v>
       </c>
       <c r="B243" t="s">
@@ -6297,7 +6316,7 @@
       <c r="C243" t="s">
         <v>25</v>
       </c>
-      <c r="D243" t="n">
+      <c r="D243">
         <v>20260611</v>
       </c>
       <c r="E243" t="s">
@@ -6307,8 +6326,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" t="n">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A244">
         <v>242</v>
       </c>
       <c r="B244" t="s">
@@ -6317,7 +6336,7 @@
       <c r="C244" t="s">
         <v>25</v>
       </c>
-      <c r="D244" t="n">
+      <c r="D244">
         <v>20260611</v>
       </c>
       <c r="E244" t="s">
@@ -6327,8 +6346,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" t="n">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A245">
         <v>243</v>
       </c>
       <c r="B245" t="s">
@@ -6337,7 +6356,7 @@
       <c r="C245" t="s">
         <v>25</v>
       </c>
-      <c r="D245" t="n">
+      <c r="D245">
         <v>20260611</v>
       </c>
       <c r="E245" t="s">
@@ -6347,8 +6366,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="n">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A246">
         <v>244</v>
       </c>
       <c r="B246" t="s">
@@ -6357,7 +6376,7 @@
       <c r="C246" t="s">
         <v>25</v>
       </c>
-      <c r="D246" t="n">
+      <c r="D246">
         <v>20260611</v>
       </c>
       <c r="E246" t="s">
@@ -6367,8 +6386,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="n">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A247">
         <v>245</v>
       </c>
       <c r="B247" t="s">
@@ -6377,7 +6396,7 @@
       <c r="C247" t="s">
         <v>25</v>
       </c>
-      <c r="D247" t="n">
+      <c r="D247">
         <v>20260611</v>
       </c>
       <c r="E247" t="s">
@@ -6387,8 +6406,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="n">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A248">
         <v>246</v>
       </c>
       <c r="B248" t="s">
@@ -6397,7 +6416,7 @@
       <c r="C248" t="s">
         <v>25</v>
       </c>
-      <c r="D248" t="n">
+      <c r="D248">
         <v>20260611</v>
       </c>
       <c r="E248" t="s">
@@ -6407,8 +6426,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" t="n">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A249">
         <v>247</v>
       </c>
       <c r="B249" t="s">
@@ -6417,7 +6436,7 @@
       <c r="C249" t="s">
         <v>25</v>
       </c>
-      <c r="D249" t="n">
+      <c r="D249">
         <v>20260611</v>
       </c>
       <c r="E249" t="s">
@@ -6427,8 +6446,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="n">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A250">
         <v>248</v>
       </c>
       <c r="B250" t="s">
@@ -6437,7 +6456,7 @@
       <c r="C250" t="s">
         <v>25</v>
       </c>
-      <c r="D250" t="n">
+      <c r="D250">
         <v>20260611</v>
       </c>
       <c r="E250" t="s">
@@ -6447,8 +6466,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="n">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A251">
         <v>249</v>
       </c>
       <c r="B251" t="s">
@@ -6457,7 +6476,7 @@
       <c r="C251" t="s">
         <v>25</v>
       </c>
-      <c r="D251" t="n">
+      <c r="D251">
         <v>20260611</v>
       </c>
       <c r="E251" t="s">
@@ -6467,8 +6486,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" t="n">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A252">
         <v>250</v>
       </c>
       <c r="B252" t="s">
@@ -6477,7 +6496,7 @@
       <c r="C252" t="s">
         <v>17</v>
       </c>
-      <c r="D252" t="n">
+      <c r="D252">
         <v>20260611</v>
       </c>
       <c r="E252" t="s">
@@ -6487,8 +6506,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" t="n">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A253">
         <v>251</v>
       </c>
       <c r="B253" t="s">
@@ -6497,7 +6516,7 @@
       <c r="C253" t="s">
         <v>25</v>
       </c>
-      <c r="D253" t="n">
+      <c r="D253">
         <v>20260611</v>
       </c>
       <c r="E253" t="s">
@@ -6507,8 +6526,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="n">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A254">
         <v>252</v>
       </c>
       <c r="B254" t="s">
@@ -6517,7 +6536,7 @@
       <c r="C254" t="s">
         <v>46</v>
       </c>
-      <c r="D254" t="n">
+      <c r="D254">
         <v>20260611</v>
       </c>
       <c r="E254" t="s">
@@ -6527,8 +6546,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" t="n">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A255">
         <v>253</v>
       </c>
       <c r="B255" t="s">
@@ -6537,7 +6556,7 @@
       <c r="C255" t="s">
         <v>8</v>
       </c>
-      <c r="D255" t="n">
+      <c r="D255">
         <v>20260611</v>
       </c>
       <c r="E255" t="s">
@@ -6547,8 +6566,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" t="n">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A256">
         <v>254</v>
       </c>
       <c r="B256" t="s">
@@ -6557,7 +6576,7 @@
       <c r="C256" t="s">
         <v>17</v>
       </c>
-      <c r="D256" t="n">
+      <c r="D256">
         <v>20260611</v>
       </c>
       <c r="E256" t="s">
@@ -6567,8 +6586,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" t="n">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A257">
         <v>255</v>
       </c>
       <c r="B257" t="s">
@@ -6577,7 +6596,7 @@
       <c r="C257" t="s">
         <v>17</v>
       </c>
-      <c r="D257" t="n">
+      <c r="D257">
         <v>20260611</v>
       </c>
       <c r="E257" t="s">
@@ -6587,8 +6606,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="n">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A258">
         <v>256</v>
       </c>
       <c r="B258" t="s">
@@ -6597,7 +6616,7 @@
       <c r="C258" t="s">
         <v>17</v>
       </c>
-      <c r="D258" t="n">
+      <c r="D258">
         <v>20260611</v>
       </c>
       <c r="E258" t="s">
@@ -6607,8 +6626,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="n">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A259">
         <v>257</v>
       </c>
       <c r="B259" t="s">
@@ -6617,7 +6636,7 @@
       <c r="C259" t="s">
         <v>17</v>
       </c>
-      <c r="D259" t="n">
+      <c r="D259">
         <v>20260611</v>
       </c>
       <c r="E259" t="s">
@@ -6627,8 +6646,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="n">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A260">
         <v>258</v>
       </c>
       <c r="B260" t="s">
@@ -6637,7 +6656,7 @@
       <c r="C260" t="s">
         <v>17</v>
       </c>
-      <c r="D260" t="n">
+      <c r="D260">
         <v>20260611</v>
       </c>
       <c r="E260" t="s">
@@ -6647,8 +6666,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="n">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A261">
         <v>259</v>
       </c>
       <c r="B261" t="s">
@@ -6657,7 +6676,7 @@
       <c r="C261" t="s">
         <v>17</v>
       </c>
-      <c r="D261" t="n">
+      <c r="D261">
         <v>20260611</v>
       </c>
       <c r="E261" t="s">
@@ -6667,8 +6686,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="n">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A262">
         <v>260</v>
       </c>
       <c r="B262" t="s">
@@ -6677,7 +6696,7 @@
       <c r="C262" t="s">
         <v>17</v>
       </c>
-      <c r="D262" t="n">
+      <c r="D262">
         <v>20260611</v>
       </c>
       <c r="E262" t="s">
@@ -6687,8 +6706,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" t="n">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A263">
         <v>261</v>
       </c>
       <c r="B263" t="s">
@@ -6697,7 +6716,7 @@
       <c r="C263" t="s">
         <v>17</v>
       </c>
-      <c r="D263" t="n">
+      <c r="D263">
         <v>20260611</v>
       </c>
       <c r="E263" t="s">
@@ -6707,8 +6726,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" t="n">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264">
         <v>262</v>
       </c>
       <c r="B264" t="s">
@@ -6717,7 +6736,7 @@
       <c r="C264" t="s">
         <v>17</v>
       </c>
-      <c r="D264" t="n">
+      <c r="D264">
         <v>20260611</v>
       </c>
       <c r="E264" t="s">
@@ -6727,8 +6746,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="n">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A265">
         <v>263</v>
       </c>
       <c r="B265" t="s">
@@ -6737,7 +6756,7 @@
       <c r="C265" t="s">
         <v>17</v>
       </c>
-      <c r="D265" t="n">
+      <c r="D265">
         <v>20260611</v>
       </c>
       <c r="E265" t="s">
@@ -6747,8 +6766,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" t="n">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A266">
         <v>264</v>
       </c>
       <c r="B266" t="s">
@@ -6757,7 +6776,7 @@
       <c r="C266" t="s">
         <v>17</v>
       </c>
-      <c r="D266" t="n">
+      <c r="D266">
         <v>20260611</v>
       </c>
       <c r="E266" t="s">
@@ -6767,8 +6786,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" t="n">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A267">
         <v>265</v>
       </c>
       <c r="B267" t="s">
@@ -6777,7 +6796,7 @@
       <c r="C267" t="s">
         <v>17</v>
       </c>
-      <c r="D267" t="n">
+      <c r="D267">
         <v>20260611</v>
       </c>
       <c r="E267" t="s">
@@ -6787,8 +6806,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" t="n">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A268">
         <v>266</v>
       </c>
       <c r="B268" t="s">
@@ -6797,7 +6816,7 @@
       <c r="C268" t="s">
         <v>17</v>
       </c>
-      <c r="D268" t="n">
+      <c r="D268">
         <v>20260611</v>
       </c>
       <c r="E268" t="s">
@@ -6807,8 +6826,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" t="n">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A269">
         <v>267</v>
       </c>
       <c r="B269" t="s">
@@ -6817,7 +6836,7 @@
       <c r="C269" t="s">
         <v>17</v>
       </c>
-      <c r="D269" t="n">
+      <c r="D269">
         <v>20260611</v>
       </c>
       <c r="E269" t="s">
@@ -6827,8 +6846,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="n">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A270">
         <v>268</v>
       </c>
       <c r="B270" t="s">
@@ -6837,7 +6856,7 @@
       <c r="C270" t="s">
         <v>17</v>
       </c>
-      <c r="D270" t="n">
+      <c r="D270">
         <v>20260611</v>
       </c>
       <c r="E270" t="s">
@@ -6847,8 +6866,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" t="n">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A271">
         <v>269</v>
       </c>
       <c r="B271" t="s">
@@ -6857,7 +6876,7 @@
       <c r="C271" t="s">
         <v>17</v>
       </c>
-      <c r="D271" t="n">
+      <c r="D271">
         <v>20260611</v>
       </c>
       <c r="E271" t="s">
@@ -6867,8 +6886,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="n">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A272">
         <v>270</v>
       </c>
       <c r="B272" t="s">
@@ -6877,7 +6896,7 @@
       <c r="C272" t="s">
         <v>17</v>
       </c>
-      <c r="D272" t="n">
+      <c r="D272">
         <v>20260611</v>
       </c>
       <c r="E272" t="s">
@@ -6887,8 +6906,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" t="n">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A273">
         <v>271</v>
       </c>
       <c r="B273" t="s">
@@ -6897,7 +6916,7 @@
       <c r="C273" t="s">
         <v>17</v>
       </c>
-      <c r="D273" t="n">
+      <c r="D273">
         <v>20260611</v>
       </c>
       <c r="E273" t="s">
@@ -6907,8 +6926,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" t="n">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A274">
         <v>272</v>
       </c>
       <c r="B274" t="s">
@@ -6917,7 +6936,7 @@
       <c r="C274" t="s">
         <v>17</v>
       </c>
-      <c r="D274" t="n">
+      <c r="D274">
         <v>20260611</v>
       </c>
       <c r="E274" t="s">
@@ -6927,8 +6946,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" t="n">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A275">
         <v>273</v>
       </c>
       <c r="B275" t="s">
@@ -6937,7 +6956,7 @@
       <c r="C275" t="s">
         <v>25</v>
       </c>
-      <c r="D275" t="n">
+      <c r="D275">
         <v>20260611</v>
       </c>
       <c r="E275" t="s">
@@ -6947,8 +6966,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" t="n">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A276">
         <v>274</v>
       </c>
       <c r="B276" t="s">
@@ -6957,7 +6976,7 @@
       <c r="C276" t="s">
         <v>25</v>
       </c>
-      <c r="D276" t="n">
+      <c r="D276">
         <v>20260611</v>
       </c>
       <c r="E276" t="s">
@@ -6967,8 +6986,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" t="n">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A277">
         <v>275</v>
       </c>
       <c r="B277" t="s">
@@ -6977,7 +6996,7 @@
       <c r="C277" t="s">
         <v>25</v>
       </c>
-      <c r="D277" t="n">
+      <c r="D277">
         <v>20260611</v>
       </c>
       <c r="E277" t="s">
@@ -6987,8 +7006,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" t="n">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A278">
         <v>276</v>
       </c>
       <c r="B278" t="s">
@@ -6997,7 +7016,7 @@
       <c r="C278" t="s">
         <v>25</v>
       </c>
-      <c r="D278" t="n">
+      <c r="D278">
         <v>20260611</v>
       </c>
       <c r="E278" t="s">
@@ -7007,8 +7026,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" t="n">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A279">
         <v>277</v>
       </c>
       <c r="B279" t="s">
@@ -7017,7 +7036,7 @@
       <c r="C279" t="s">
         <v>25</v>
       </c>
-      <c r="D279" t="n">
+      <c r="D279">
         <v>20260611</v>
       </c>
       <c r="E279" t="s">
@@ -7027,8 +7046,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" t="n">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A280">
         <v>278</v>
       </c>
       <c r="B280" t="s">
@@ -7037,7 +7056,7 @@
       <c r="C280" t="s">
         <v>25</v>
       </c>
-      <c r="D280" t="n">
+      <c r="D280">
         <v>20260611</v>
       </c>
       <c r="E280" t="s">
@@ -7047,8 +7066,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" t="n">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A281">
         <v>279</v>
       </c>
       <c r="B281" t="s">
@@ -7057,7 +7076,7 @@
       <c r="C281" t="s">
         <v>25</v>
       </c>
-      <c r="D281" t="n">
+      <c r="D281">
         <v>20260611</v>
       </c>
       <c r="E281" t="s">
@@ -7067,8 +7086,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" t="n">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A282">
         <v>280</v>
       </c>
       <c r="B282" t="s">
@@ -7077,7 +7096,7 @@
       <c r="C282" t="s">
         <v>25</v>
       </c>
-      <c r="D282" t="n">
+      <c r="D282">
         <v>20260611</v>
       </c>
       <c r="E282" t="s">
@@ -7087,8 +7106,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" t="n">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A283">
         <v>281</v>
       </c>
       <c r="B283" t="s">
@@ -7097,7 +7116,7 @@
       <c r="C283" t="s">
         <v>25</v>
       </c>
-      <c r="D283" t="n">
+      <c r="D283">
         <v>20260611</v>
       </c>
       <c r="E283" t="s">
@@ -7107,8 +7126,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" t="n">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A284">
         <v>282</v>
       </c>
       <c r="B284" t="s">
@@ -7117,7 +7136,7 @@
       <c r="C284" t="s">
         <v>25</v>
       </c>
-      <c r="D284" t="n">
+      <c r="D284">
         <v>20260611</v>
       </c>
       <c r="E284" t="s">
@@ -7127,8 +7146,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" t="n">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A285">
         <v>283</v>
       </c>
       <c r="B285" t="s">
@@ -7137,7 +7156,7 @@
       <c r="C285" t="s">
         <v>25</v>
       </c>
-      <c r="D285" t="n">
+      <c r="D285">
         <v>20260611</v>
       </c>
       <c r="E285" t="s">
@@ -7147,8 +7166,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" t="n">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A286">
         <v>284</v>
       </c>
       <c r="B286" t="s">
@@ -7157,7 +7176,7 @@
       <c r="C286" t="s">
         <v>25</v>
       </c>
-      <c r="D286" t="n">
+      <c r="D286">
         <v>20260611</v>
       </c>
       <c r="E286" t="s">
@@ -7167,8 +7186,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" t="n">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A287">
         <v>285</v>
       </c>
       <c r="B287" t="s">
@@ -7177,7 +7196,7 @@
       <c r="C287" t="s">
         <v>25</v>
       </c>
-      <c r="D287" t="n">
+      <c r="D287">
         <v>20260611</v>
       </c>
       <c r="E287" t="s">
@@ -7187,8 +7206,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" t="n">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A288">
         <v>286</v>
       </c>
       <c r="B288" t="s">
@@ -7197,7 +7216,7 @@
       <c r="C288" t="s">
         <v>25</v>
       </c>
-      <c r="D288" t="n">
+      <c r="D288">
         <v>20260611</v>
       </c>
       <c r="E288" t="s">
@@ -7207,8 +7226,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" t="n">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A289">
         <v>287</v>
       </c>
       <c r="B289" t="s">
@@ -7217,7 +7236,7 @@
       <c r="C289" t="s">
         <v>25</v>
       </c>
-      <c r="D289" t="n">
+      <c r="D289">
         <v>20260611</v>
       </c>
       <c r="E289" t="s">
@@ -7227,8 +7246,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" t="n">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A290">
         <v>288</v>
       </c>
       <c r="B290" t="s">
@@ -7237,7 +7256,7 @@
       <c r="C290" t="s">
         <v>25</v>
       </c>
-      <c r="D290" t="n">
+      <c r="D290">
         <v>20260611</v>
       </c>
       <c r="E290" t="s">
@@ -7247,8 +7266,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" t="n">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A291">
         <v>289</v>
       </c>
       <c r="B291" t="s">
@@ -7257,7 +7276,7 @@
       <c r="C291" t="s">
         <v>25</v>
       </c>
-      <c r="D291" t="n">
+      <c r="D291">
         <v>20260611</v>
       </c>
       <c r="E291" t="s">
@@ -7267,8 +7286,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" t="n">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A292">
         <v>290</v>
       </c>
       <c r="B292" t="s">
@@ -7277,7 +7296,7 @@
       <c r="C292" t="s">
         <v>25</v>
       </c>
-      <c r="D292" t="n">
+      <c r="D292">
         <v>20260611</v>
       </c>
       <c r="E292" t="s">
@@ -7287,8 +7306,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" t="n">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A293">
         <v>291</v>
       </c>
       <c r="B293" t="s">
@@ -7297,7 +7316,7 @@
       <c r="C293" t="s">
         <v>25</v>
       </c>
-      <c r="D293" t="n">
+      <c r="D293">
         <v>20260611</v>
       </c>
       <c r="E293" t="s">
@@ -7307,8 +7326,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" t="n">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A294">
         <v>292</v>
       </c>
       <c r="B294" t="s">
@@ -7317,7 +7336,7 @@
       <c r="C294" t="s">
         <v>25</v>
       </c>
-      <c r="D294" t="n">
+      <c r="D294">
         <v>20260611</v>
       </c>
       <c r="E294" t="s">
@@ -7327,8 +7346,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" t="n">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A295">
         <v>293</v>
       </c>
       <c r="B295" t="s">
@@ -7337,7 +7356,7 @@
       <c r="C295" t="s">
         <v>17</v>
       </c>
-      <c r="D295" t="n">
+      <c r="D295">
         <v>20260611</v>
       </c>
       <c r="E295" t="s">
@@ -7347,8 +7366,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" t="n">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A296">
         <v>294</v>
       </c>
       <c r="B296" t="s">
@@ -7357,7 +7376,7 @@
       <c r="C296" t="s">
         <v>25</v>
       </c>
-      <c r="D296" t="n">
+      <c r="D296">
         <v>20260611</v>
       </c>
       <c r="E296" t="s">
@@ -7367,8 +7386,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" t="n">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A297">
         <v>295</v>
       </c>
       <c r="B297" t="s">
@@ -7377,7 +7396,7 @@
       <c r="C297" t="s">
         <v>46</v>
       </c>
-      <c r="D297" t="n">
+      <c r="D297">
         <v>20260611</v>
       </c>
       <c r="E297" t="s">
@@ -7387,8 +7406,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="298">
-      <c r="A298" t="n">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A298">
         <v>296</v>
       </c>
       <c r="B298" t="s">
@@ -7397,7 +7416,7 @@
       <c r="C298" t="s">
         <v>17</v>
       </c>
-      <c r="D298" t="n">
+      <c r="D298">
         <v>20260611</v>
       </c>
       <c r="E298" t="s">
@@ -7407,8 +7426,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" t="n">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A299">
         <v>297</v>
       </c>
       <c r="B299" t="s">
@@ -7417,7 +7436,7 @@
       <c r="C299" t="s">
         <v>25</v>
       </c>
-      <c r="D299" t="n">
+      <c r="D299">
         <v>20260611</v>
       </c>
       <c r="E299" t="s">
@@ -7427,8 +7446,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" t="n">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A300">
         <v>298</v>
       </c>
       <c r="B300" t="s">
@@ -7437,7 +7456,7 @@
       <c r="C300" t="s">
         <v>17</v>
       </c>
-      <c r="D300" t="n">
+      <c r="D300">
         <v>20260611</v>
       </c>
       <c r="E300" t="s">
@@ -7447,8 +7466,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" t="n">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301">
         <v>299</v>
       </c>
       <c r="B301" t="s">
@@ -7457,7 +7476,7 @@
       <c r="C301" t="s">
         <v>25</v>
       </c>
-      <c r="D301" t="n">
+      <c r="D301">
         <v>20260611</v>
       </c>
       <c r="E301" t="s">
@@ -7467,8 +7486,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" t="n">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A302">
         <v>300</v>
       </c>
       <c r="B302" t="s">
@@ -7477,7 +7496,7 @@
       <c r="C302" t="s">
         <v>17</v>
       </c>
-      <c r="D302" t="n">
+      <c r="D302">
         <v>20260612</v>
       </c>
       <c r="E302" t="s">
@@ -7487,8 +7506,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" t="n">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A303">
         <v>301</v>
       </c>
       <c r="B303" t="s">
@@ -7497,7 +7516,7 @@
       <c r="C303" t="s">
         <v>17</v>
       </c>
-      <c r="D303" t="n">
+      <c r="D303">
         <v>20260612</v>
       </c>
       <c r="E303" t="s">
@@ -7507,8 +7526,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" t="n">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A304">
         <v>302</v>
       </c>
       <c r="B304" t="s">
@@ -7517,7 +7536,7 @@
       <c r="C304" t="s">
         <v>17</v>
       </c>
-      <c r="D304" t="n">
+      <c r="D304">
         <v>20260612</v>
       </c>
       <c r="E304" t="s">
@@ -7527,8 +7546,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" t="n">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A305">
         <v>303</v>
       </c>
       <c r="B305" t="s">
@@ -7537,7 +7556,7 @@
       <c r="C305" t="s">
         <v>17</v>
       </c>
-      <c r="D305" t="n">
+      <c r="D305">
         <v>20260612</v>
       </c>
       <c r="E305" t="s">
@@ -7547,8 +7566,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" t="n">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A306">
         <v>304</v>
       </c>
       <c r="B306" t="s">
@@ -7557,7 +7576,7 @@
       <c r="C306" t="s">
         <v>17</v>
       </c>
-      <c r="D306" t="n">
+      <c r="D306">
         <v>20260612</v>
       </c>
       <c r="E306" t="s">
@@ -7567,8 +7586,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" t="n">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A307">
         <v>305</v>
       </c>
       <c r="B307" t="s">
@@ -7577,7 +7596,7 @@
       <c r="C307" t="s">
         <v>17</v>
       </c>
-      <c r="D307" t="n">
+      <c r="D307">
         <v>20260612</v>
       </c>
       <c r="E307" t="s">
@@ -7587,8 +7606,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" t="n">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A308">
         <v>306</v>
       </c>
       <c r="B308" t="s">
@@ -7597,7 +7616,7 @@
       <c r="C308" t="s">
         <v>17</v>
       </c>
-      <c r="D308" t="n">
+      <c r="D308">
         <v>20260612</v>
       </c>
       <c r="E308" t="s">
@@ -7607,8 +7626,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" t="n">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A309">
         <v>307</v>
       </c>
       <c r="B309" t="s">
@@ -7617,7 +7636,7 @@
       <c r="C309" t="s">
         <v>17</v>
       </c>
-      <c r="D309" t="n">
+      <c r="D309">
         <v>20260612</v>
       </c>
       <c r="E309" t="s">
@@ -7627,8 +7646,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="310">
-      <c r="A310" t="n">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A310">
         <v>308</v>
       </c>
       <c r="B310" t="s">
@@ -7637,7 +7656,7 @@
       <c r="C310" t="s">
         <v>17</v>
       </c>
-      <c r="D310" t="n">
+      <c r="D310">
         <v>20260612</v>
       </c>
       <c r="E310" t="s">
@@ -7647,8 +7666,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" t="n">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A311">
         <v>309</v>
       </c>
       <c r="B311" t="s">
@@ -7657,7 +7676,7 @@
       <c r="C311" t="s">
         <v>17</v>
       </c>
-      <c r="D311" t="n">
+      <c r="D311">
         <v>20260612</v>
       </c>
       <c r="E311" t="s">
@@ -7667,8 +7686,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" t="n">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A312">
         <v>310</v>
       </c>
       <c r="B312" t="s">
@@ -7677,7 +7696,7 @@
       <c r="C312" t="s">
         <v>17</v>
       </c>
-      <c r="D312" t="n">
+      <c r="D312">
         <v>20260612</v>
       </c>
       <c r="E312" t="s">
@@ -7687,8 +7706,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" t="n">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A313">
         <v>311</v>
       </c>
       <c r="B313" t="s">
@@ -7697,7 +7716,7 @@
       <c r="C313" t="s">
         <v>17</v>
       </c>
-      <c r="D313" t="n">
+      <c r="D313">
         <v>20260612</v>
       </c>
       <c r="E313" t="s">
@@ -7707,8 +7726,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" t="n">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A314">
         <v>312</v>
       </c>
       <c r="B314" t="s">
@@ -7717,7 +7736,7 @@
       <c r="C314" t="s">
         <v>17</v>
       </c>
-      <c r="D314" t="n">
+      <c r="D314">
         <v>20260612</v>
       </c>
       <c r="E314" t="s">
@@ -7727,8 +7746,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="315">
-      <c r="A315" t="n">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A315">
         <v>313</v>
       </c>
       <c r="B315" t="s">
@@ -7737,7 +7756,7 @@
       <c r="C315" t="s">
         <v>17</v>
       </c>
-      <c r="D315" t="n">
+      <c r="D315">
         <v>20260612</v>
       </c>
       <c r="E315" t="s">
@@ -7747,8 +7766,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="316">
-      <c r="A316" t="n">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A316">
         <v>314</v>
       </c>
       <c r="B316" t="s">
@@ -7757,7 +7776,7 @@
       <c r="C316" t="s">
         <v>17</v>
       </c>
-      <c r="D316" t="n">
+      <c r="D316">
         <v>20260612</v>
       </c>
       <c r="E316" t="s">
@@ -7767,8 +7786,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" t="n">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A317">
         <v>315</v>
       </c>
       <c r="B317" t="s">
@@ -7777,7 +7796,7 @@
       <c r="C317" t="s">
         <v>17</v>
       </c>
-      <c r="D317" t="n">
+      <c r="D317">
         <v>20260612</v>
       </c>
       <c r="E317" t="s">
@@ -7787,8 +7806,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" t="n">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A318">
         <v>316</v>
       </c>
       <c r="B318" t="s">
@@ -7797,7 +7816,7 @@
       <c r="C318" t="s">
         <v>17</v>
       </c>
-      <c r="D318" t="n">
+      <c r="D318">
         <v>20260612</v>
       </c>
       <c r="E318" t="s">
@@ -7807,8 +7826,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" t="n">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A319">
         <v>317</v>
       </c>
       <c r="B319" t="s">
@@ -7817,7 +7836,7 @@
       <c r="C319" t="s">
         <v>17</v>
       </c>
-      <c r="D319" t="n">
+      <c r="D319">
         <v>20260612</v>
       </c>
       <c r="E319" t="s">
@@ -7827,8 +7846,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="320">
-      <c r="A320" t="n">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A320">
         <v>318</v>
       </c>
       <c r="B320" t="s">
@@ -7837,7 +7856,7 @@
       <c r="C320" t="s">
         <v>17</v>
       </c>
-      <c r="D320" t="n">
+      <c r="D320">
         <v>20260612</v>
       </c>
       <c r="E320" t="s">
@@ -7847,8 +7866,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" t="n">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A321">
         <v>319</v>
       </c>
       <c r="B321" t="s">
@@ -7857,7 +7876,7 @@
       <c r="C321" t="s">
         <v>25</v>
       </c>
-      <c r="D321" t="n">
+      <c r="D321">
         <v>20260612</v>
       </c>
       <c r="E321" t="s">
@@ -7867,8 +7886,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" t="n">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A322">
         <v>320</v>
       </c>
       <c r="B322" t="s">
@@ -7877,7 +7896,7 @@
       <c r="C322" t="s">
         <v>25</v>
       </c>
-      <c r="D322" t="n">
+      <c r="D322">
         <v>20260612</v>
       </c>
       <c r="E322" t="s">
@@ -7887,8 +7906,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" t="n">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A323">
         <v>321</v>
       </c>
       <c r="B323" t="s">
@@ -7897,7 +7916,7 @@
       <c r="C323" t="s">
         <v>25</v>
       </c>
-      <c r="D323" t="n">
+      <c r="D323">
         <v>20260612</v>
       </c>
       <c r="E323" t="s">
@@ -7907,8 +7926,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" t="n">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A324">
         <v>322</v>
       </c>
       <c r="B324" t="s">
@@ -7917,7 +7936,7 @@
       <c r="C324" t="s">
         <v>25</v>
       </c>
-      <c r="D324" t="n">
+      <c r="D324">
         <v>20260612</v>
       </c>
       <c r="E324" t="s">
@@ -7927,8 +7946,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" t="n">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A325">
         <v>323</v>
       </c>
       <c r="B325" t="s">
@@ -7937,7 +7956,7 @@
       <c r="C325" t="s">
         <v>25</v>
       </c>
-      <c r="D325" t="n">
+      <c r="D325">
         <v>20260612</v>
       </c>
       <c r="E325" t="s">
@@ -7947,8 +7966,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" t="n">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A326">
         <v>324</v>
       </c>
       <c r="B326" t="s">
@@ -7957,7 +7976,7 @@
       <c r="C326" t="s">
         <v>25</v>
       </c>
-      <c r="D326" t="n">
+      <c r="D326">
         <v>20260612</v>
       </c>
       <c r="E326" t="s">
@@ -7967,8 +7986,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327">
-      <c r="A327" t="n">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A327">
         <v>325</v>
       </c>
       <c r="B327" t="s">
@@ -7977,7 +7996,7 @@
       <c r="C327" t="s">
         <v>25</v>
       </c>
-      <c r="D327" t="n">
+      <c r="D327">
         <v>20260612</v>
       </c>
       <c r="E327" t="s">
@@ -7987,8 +8006,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="328">
-      <c r="A328" t="n">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A328">
         <v>326</v>
       </c>
       <c r="B328" t="s">
@@ -7997,7 +8016,7 @@
       <c r="C328" t="s">
         <v>25</v>
       </c>
-      <c r="D328" t="n">
+      <c r="D328">
         <v>20260612</v>
       </c>
       <c r="E328" t="s">
@@ -8007,8 +8026,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="329">
-      <c r="A329" t="n">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A329">
         <v>327</v>
       </c>
       <c r="B329" t="s">
@@ -8017,7 +8036,7 @@
       <c r="C329" t="s">
         <v>25</v>
       </c>
-      <c r="D329" t="n">
+      <c r="D329">
         <v>20260612</v>
       </c>
       <c r="E329" t="s">
@@ -8027,8 +8046,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" t="n">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A330">
         <v>328</v>
       </c>
       <c r="B330" t="s">
@@ -8037,7 +8056,7 @@
       <c r="C330" t="s">
         <v>25</v>
       </c>
-      <c r="D330" t="n">
+      <c r="D330">
         <v>20260612</v>
       </c>
       <c r="E330" t="s">
@@ -8047,8 +8066,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="331">
-      <c r="A331" t="n">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A331">
         <v>329</v>
       </c>
       <c r="B331" t="s">
@@ -8057,7 +8076,7 @@
       <c r="C331" t="s">
         <v>25</v>
       </c>
-      <c r="D331" t="n">
+      <c r="D331">
         <v>20260612</v>
       </c>
       <c r="E331" t="s">
@@ -8067,8 +8086,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="332">
-      <c r="A332" t="n">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A332">
         <v>330</v>
       </c>
       <c r="B332" t="s">
@@ -8077,7 +8096,7 @@
       <c r="C332" t="s">
         <v>25</v>
       </c>
-      <c r="D332" t="n">
+      <c r="D332">
         <v>20260612</v>
       </c>
       <c r="E332" t="s">
@@ -8087,8 +8106,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="333">
-      <c r="A333" t="n">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A333">
         <v>331</v>
       </c>
       <c r="B333" t="s">
@@ -8097,7 +8116,7 @@
       <c r="C333" t="s">
         <v>25</v>
       </c>
-      <c r="D333" t="n">
+      <c r="D333">
         <v>20260612</v>
       </c>
       <c r="E333" t="s">
@@ -8107,8 +8126,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="334">
-      <c r="A334" t="n">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A334">
         <v>332</v>
       </c>
       <c r="B334" t="s">
@@ -8117,7 +8136,7 @@
       <c r="C334" t="s">
         <v>25</v>
       </c>
-      <c r="D334" t="n">
+      <c r="D334">
         <v>20260612</v>
       </c>
       <c r="E334" t="s">
@@ -8127,8 +8146,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" t="n">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A335">
         <v>333</v>
       </c>
       <c r="B335" t="s">
@@ -8137,7 +8156,7 @@
       <c r="C335" t="s">
         <v>25</v>
       </c>
-      <c r="D335" t="n">
+      <c r="D335">
         <v>20260612</v>
       </c>
       <c r="E335" t="s">
@@ -8147,8 +8166,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="336">
-      <c r="A336" t="n">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A336">
         <v>334</v>
       </c>
       <c r="B336" t="s">
@@ -8157,7 +8176,7 @@
       <c r="C336" t="s">
         <v>25</v>
       </c>
-      <c r="D336" t="n">
+      <c r="D336">
         <v>20260612</v>
       </c>
       <c r="E336" t="s">
@@ -8167,8 +8186,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" t="n">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A337">
         <v>335</v>
       </c>
       <c r="B337" t="s">
@@ -8177,7 +8196,7 @@
       <c r="C337" t="s">
         <v>25</v>
       </c>
-      <c r="D337" t="n">
+      <c r="D337">
         <v>20260612</v>
       </c>
       <c r="E337" t="s">
@@ -8187,8 +8206,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="338">
-      <c r="A338" t="n">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A338">
         <v>336</v>
       </c>
       <c r="B338" t="s">
@@ -8197,7 +8216,7 @@
       <c r="C338" t="s">
         <v>25</v>
       </c>
-      <c r="D338" t="n">
+      <c r="D338">
         <v>20260612</v>
       </c>
       <c r="E338" t="s">
@@ -8207,8 +8226,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="339">
-      <c r="A339" t="n">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A339">
         <v>337</v>
       </c>
       <c r="B339" t="s">
@@ -8217,7 +8236,7 @@
       <c r="C339" t="s">
         <v>25</v>
       </c>
-      <c r="D339" t="n">
+      <c r="D339">
         <v>20260612</v>
       </c>
       <c r="E339" t="s">
@@ -8227,8 +8246,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" t="n">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A340">
         <v>338</v>
       </c>
       <c r="B340" t="s">
@@ -8237,7 +8256,7 @@
       <c r="C340" t="s">
         <v>25</v>
       </c>
-      <c r="D340" t="n">
+      <c r="D340">
         <v>20260612</v>
       </c>
       <c r="E340" t="s">
@@ -8249,6 +8268,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/processing_scripts/Inventory_Processing/TEMPEST_SO4_20260501-20260612.xlsx
+++ b/processing_scripts/Inventory_Processing/TEMPEST_SO4_20260501-20260612.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sinet-my.sharepoint.com/personal/readz_si_edu1/Documents/TEMPEST_Porewater/processing_scripts/Inventory_Processing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_B89231273CF96668CBB5F26DB23E1D420A5CD295" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{070B892B-CF8C-4AC5-B85F-30394BB0384B}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_B99231273C69641A3F147E092E1C0F84929FC488" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C88745C-8A20-4959-8976-446D96FE6E27}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample List" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sample List'!$A$2:$F$340</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="384">
   <si>
     <t>TEMPEST Sample List: SO4/Cl/H2S 20260501 - 20260612</t>
   </si>
@@ -145,262 +148,118 @@
     <t>TMP_FW_PW_H6_50cm_SO4_20260607_D1_PM</t>
   </si>
   <si>
-    <t>TMP_SW_SCE_SO4_20260608_D2-AM</t>
-  </si>
-  <si>
-    <t>D2-AM</t>
+    <t>TMP_SW_SCE_SO4_20260608_D2_AM</t>
+  </si>
+  <si>
+    <t>D2_AM</t>
   </si>
   <si>
     <t>SCE</t>
   </si>
   <si>
-    <t>TMP_FW_SCE_SO4_20260608_D2-AM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SCE_SO4_20260608_D2-AM</t>
+    <t>TMP_FW_SCE_SO4_20260608_D2_AM</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260608_D2_HT</t>
   </si>
   <si>
     <t>Estuary</t>
   </si>
   <si>
-    <t>TMP_SW_SCE_SO4_20260608_D2-PM</t>
-  </si>
-  <si>
-    <t>D2-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_SCE_SO4_20260608_D2-PM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SCE_SO4_20260608_D2-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260608_D2-T1</t>
-  </si>
-  <si>
-    <t>D2-T1</t>
+    <t>D2_HT</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260608_D2_LT</t>
+  </si>
+  <si>
+    <t>D2_LT</t>
+  </si>
+  <si>
+    <t>TMP_C_PW_C6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_15cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_D5_15cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_30cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_50cm_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_SCE_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260608_D2_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260608_D2_T1</t>
+  </si>
+  <si>
+    <t>D2_T1</t>
   </si>
   <si>
     <t>RO</t>
   </si>
   <si>
-    <t>TMP_SW_RO_SO4_20260608_D2-T2</t>
-  </si>
-  <si>
-    <t>D2-T2</t>
-  </si>
-  <si>
-    <t>TMP_C_PW_C6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_15cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_D5_15cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_30cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_50cm_SO4_20260608_D2_PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_SCE_SO4_20260609_D3-AM</t>
-  </si>
-  <si>
-    <t>D3-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_SCE_SO4_20260609_D3-AM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SCE_SO4_20260609_D3-AM</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260609_D3-Macropore</t>
-  </si>
-  <si>
-    <t>D3-Macropore</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_B4_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C3_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_C6_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_D5_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_E3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_F4_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H3_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_H6_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_PW_I5_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C3_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_C6_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_D5_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_E3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_F4_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H3_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_30cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_H6_50cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_PW_I5_15cm_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_SCE_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_SCE_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SCE_SO4_20260609_D3-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260609_D3-T1</t>
-  </si>
-  <si>
-    <t>D3-T1</t>
-  </si>
-  <si>
-    <t>TMP_FW_RO_SO4_20260609_D3-T1</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260609_D3-T2</t>
-  </si>
-  <si>
-    <t>D3-T2</t>
-  </si>
-  <si>
-    <t>TMP_FW_RO_SO4_20260609_D3-T2</t>
+    <t>TMP_SW_RO_SO4_20260608_D2_T2</t>
+  </si>
+  <si>
+    <t>D2_T2</t>
   </si>
   <si>
     <t>TMP_SW_PW_B4_15cm_SO4_20260609_D3_AM</t>
@@ -502,6 +361,156 @@
     <t>TMP_FW_PW_H6_50cm_SO4_20260609_D3_AM</t>
   </si>
   <si>
+    <t>TMP_SW_SCE_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260609_D3_AM</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260609_D3_HT</t>
+  </si>
+  <si>
+    <t>D3_HT</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260609_D3_LT</t>
+  </si>
+  <si>
+    <t>D3_LT</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260609_D3_Macropore</t>
+  </si>
+  <si>
+    <t>D3_Macropore</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_B4_15cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_30cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C3_50cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_30cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_C6_50cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_D5_15cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_E3_15cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_15cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_30cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_F4_50cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_15cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H3_30cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_30cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_H6_50cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_PW_I5_15cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_15cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_30cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C3_50cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_15cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_30cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_C6_50cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_D5_15cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_E3_15cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_15cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_30cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_F4_50cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_15cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_30cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H3_50cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_15cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_30cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_H6_50cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_PW_I5_15cm_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_SCE_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260609_D3_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260609_D3_T1</t>
+  </si>
+  <si>
+    <t>D3_T1</t>
+  </si>
+  <si>
+    <t>TMP_FW_RO_SO4_20260609_D3_T1</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260609_D3_T2</t>
+  </si>
+  <si>
+    <t>D3_T2</t>
+  </si>
+  <si>
+    <t>TMP_FW_RO_SO4_20260609_D3_T2</t>
+  </si>
+  <si>
     <t>TMP_SW_PW_B4_15cm_SO4_20260610_D4-AM</t>
   </si>
   <si>
@@ -613,15 +622,6 @@
     <t>TMP_FW_PW_I5_15cm_SO4_20260610_D4-AM</t>
   </si>
   <si>
-    <t>TMP_SW_SCE_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_SCE_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SCE_SO4_20260610_D4-AM</t>
-  </si>
-  <si>
     <t>TMP_SW_PW_B4_15cm_SO4_20260610_D4-PM</t>
   </si>
   <si>
@@ -718,31 +718,52 @@
     <t>TMP_FW_PW_F6_15cm_SO4_20260610_D4-PM</t>
   </si>
   <si>
-    <t>TMP_SW_SCE_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_SCE_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SCE_SO4_20260610_D4-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260610_D4-T1</t>
-  </si>
-  <si>
-    <t>D4-T1</t>
-  </si>
-  <si>
-    <t>TMP_FW_RO_SO4_20260610_D4-T1</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260610_D4-T2</t>
-  </si>
-  <si>
-    <t>D4-T2</t>
-  </si>
-  <si>
-    <t>TMP_FW_RO_SO4_20260610_D4-T2</t>
+    <t>TMP_SW_SCE_SO4_20260610_D4_AM</t>
+  </si>
+  <si>
+    <t>D4_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260610_D4_AM</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260610_D4_HT</t>
+  </si>
+  <si>
+    <t>D4_HT</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260610_D4_LT</t>
+  </si>
+  <si>
+    <t>D4_LT</t>
+  </si>
+  <si>
+    <t>TMP_SW_SCE_SO4_20260610_D4_PM</t>
+  </si>
+  <si>
+    <t>D4_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260610_D4_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260610_D4_T1</t>
+  </si>
+  <si>
+    <t>D4_T1</t>
+  </si>
+  <si>
+    <t>TMP_FW_RO_SO4_20260610_D4_T1</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260610_D4_T2</t>
+  </si>
+  <si>
+    <t>D4_T2</t>
+  </si>
+  <si>
+    <t>TMP_FW_RO_SO4_20260610_D4_T2</t>
   </si>
   <si>
     <t>TMP_SW_PW_B4_15cm_SO4_20260611_D5-AM</t>
@@ -865,15 +886,6 @@
     <t>TMP_FW_PW_I5_15cm_SO4_20260611_D5-AM</t>
   </si>
   <si>
-    <t>TMP_SW_SCE_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_FW_SCE_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SCE_SO4_20260611_D5-AM</t>
-  </si>
-  <si>
     <t>TMP_C_PW_C6_50cm_SO4_20260611_D5-PM</t>
   </si>
   <si>
@@ -997,31 +1009,52 @@
     <t>TMP_FW_PW_F6_15cm_SO4_20260611_D5-PM</t>
   </si>
   <si>
-    <t>TMP_SW_SCE_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_FW_SCE_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_EST_SCE_SO4_20260611_D5-PM</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260611_D5-T1</t>
-  </si>
-  <si>
-    <t>D5-T1</t>
-  </si>
-  <si>
-    <t>TMP_FW_RO_SO4_20260611_D5-T1</t>
-  </si>
-  <si>
-    <t>TMP_SW_RO_SO4_20260611_D5-T2</t>
-  </si>
-  <si>
-    <t>D5-T2</t>
-  </si>
-  <si>
-    <t>TMP_FW_RO_SO4_20260611_D5-T2</t>
+    <t>TMP_SW_SCE_SO4_20260611_D5_AM</t>
+  </si>
+  <si>
+    <t>D5_AM</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260611_D5_AM</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260611_D5_HT</t>
+  </si>
+  <si>
+    <t>D5_HT</t>
+  </si>
+  <si>
+    <t>TMP_EST_SCE_SO4_20260611_D5_LT</t>
+  </si>
+  <si>
+    <t>D5_LT</t>
+  </si>
+  <si>
+    <t>TMP_SW_SCE_SO4_20260611_D5_PM</t>
+  </si>
+  <si>
+    <t>D5_PM</t>
+  </si>
+  <si>
+    <t>TMP_FW_SCE_SO4_20260611_D5_PM</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260611_D5_T1</t>
+  </si>
+  <si>
+    <t>D5_T1</t>
+  </si>
+  <si>
+    <t>TMP_FW_RO_SO4_20260611_D5_T1</t>
+  </si>
+  <si>
+    <t>TMP_SW_RO_SO4_20260611_D5_T2</t>
+  </si>
+  <si>
+    <t>D5_T2</t>
+  </si>
+  <si>
+    <t>TMP_FW_RO_SO4_20260611_D5_T2</t>
   </si>
   <si>
     <t>TMP_SW_PW_B4_15cm_SO4_20260612_D6_PM</t>
@@ -1194,6 +1227,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1478,7 +1515,7 @@
   <dimension ref="A1:F340"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="55.28515625" customWidth="1"/>
+    <col min="2" max="2" width="43.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2120,7 +2157,7 @@
         <v>20260608</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F33" t="s">
         <v>43</v>
@@ -2131,16 +2168,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D34">
         <v>20260608</v>
       </c>
       <c r="E34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F34" t="s">
         <v>43</v>
@@ -2151,19 +2188,19 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D35">
         <v>20260608</v>
       </c>
       <c r="E35" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F35" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2171,19 +2208,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D36">
         <v>20260608</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F36" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2191,7 +2228,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
         <v>17</v>
@@ -2200,10 +2237,10 @@
         <v>20260608</v>
       </c>
       <c r="E37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F37" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2220,10 +2257,10 @@
         <v>20260608</v>
       </c>
       <c r="E38" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F38" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2231,16 +2268,16 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D39">
         <v>20260608</v>
       </c>
       <c r="E39" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F39" t="s">
         <v>10</v>
@@ -2251,7 +2288,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
@@ -2260,7 +2297,7 @@
         <v>20260608</v>
       </c>
       <c r="E40" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F40" t="s">
         <v>10</v>
@@ -2271,7 +2308,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C41" t="s">
         <v>17</v>
@@ -2280,7 +2317,7 @@
         <v>20260608</v>
       </c>
       <c r="E41" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F41" t="s">
         <v>10</v>
@@ -2291,7 +2328,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
@@ -2300,7 +2337,7 @@
         <v>20260608</v>
       </c>
       <c r="E42" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F42" t="s">
         <v>10</v>
@@ -2311,7 +2348,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C43" t="s">
         <v>17</v>
@@ -2320,7 +2357,7 @@
         <v>20260608</v>
       </c>
       <c r="E43" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F43" t="s">
         <v>10</v>
@@ -2331,16 +2368,16 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D44">
         <v>20260608</v>
       </c>
       <c r="E44" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F44" t="s">
         <v>10</v>
@@ -2351,16 +2388,16 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D45">
         <v>20260608</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F45" t="s">
         <v>10</v>
@@ -2371,16 +2408,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D46">
         <v>20260608</v>
       </c>
       <c r="E46" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F46" t="s">
         <v>10</v>
@@ -2391,16 +2428,16 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D47">
         <v>20260608</v>
       </c>
       <c r="E47" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F47" t="s">
         <v>10</v>
@@ -2411,7 +2448,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C48" t="s">
         <v>25</v>
@@ -2420,7 +2457,7 @@
         <v>20260608</v>
       </c>
       <c r="E48" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F48" t="s">
         <v>10</v>
@@ -2431,7 +2468,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C49" t="s">
         <v>25</v>
@@ -2440,7 +2477,7 @@
         <v>20260608</v>
       </c>
       <c r="E49" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F49" t="s">
         <v>10</v>
@@ -2451,7 +2488,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C50" t="s">
         <v>25</v>
@@ -2460,7 +2497,7 @@
         <v>20260608</v>
       </c>
       <c r="E50" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F50" t="s">
         <v>10</v>
@@ -2471,7 +2508,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C51" t="s">
         <v>25</v>
@@ -2480,7 +2517,7 @@
         <v>20260608</v>
       </c>
       <c r="E51" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F51" t="s">
         <v>10</v>
@@ -2491,7 +2528,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C52" t="s">
         <v>25</v>
@@ -2500,7 +2537,7 @@
         <v>20260608</v>
       </c>
       <c r="E52" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F52" t="s">
         <v>10</v>
@@ -2511,7 +2548,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C53" t="s">
         <v>25</v>
@@ -2520,7 +2557,7 @@
         <v>20260608</v>
       </c>
       <c r="E53" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F53" t="s">
         <v>10</v>
@@ -2531,7 +2568,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C54" t="s">
         <v>25</v>
@@ -2540,7 +2577,7 @@
         <v>20260608</v>
       </c>
       <c r="E54" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F54" t="s">
         <v>10</v>
@@ -2551,7 +2588,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C55" t="s">
         <v>25</v>
@@ -2560,7 +2597,7 @@
         <v>20260608</v>
       </c>
       <c r="E55" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F55" t="s">
         <v>10</v>
@@ -2571,19 +2608,19 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D56">
         <v>20260608</v>
       </c>
       <c r="E56" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F56" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2591,7 +2628,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C57" t="s">
         <v>25</v>
@@ -2600,10 +2637,10 @@
         <v>20260608</v>
       </c>
       <c r="E57" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F57" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2611,19 +2648,19 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D58">
         <v>20260608</v>
       </c>
       <c r="E58" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F58" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2634,16 +2671,16 @@
         <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D59">
         <v>20260608</v>
       </c>
       <c r="E59" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="F59" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2651,7 +2688,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C60" t="s">
         <v>17</v>
@@ -2660,10 +2697,10 @@
         <v>20260609</v>
       </c>
       <c r="E60" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F60" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2671,19 +2708,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D61">
         <v>20260609</v>
       </c>
       <c r="E61" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F61" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2691,19 +2728,19 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C62" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D62">
         <v>20260609</v>
       </c>
       <c r="E62" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F62" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2711,7 +2748,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C63" t="s">
         <v>17</v>
@@ -2720,10 +2757,10 @@
         <v>20260609</v>
       </c>
       <c r="E63" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F63" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2740,7 +2777,7 @@
         <v>20260609</v>
       </c>
       <c r="E64" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F64" t="s">
         <v>10</v>
@@ -2751,7 +2788,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
@@ -2760,7 +2797,7 @@
         <v>20260609</v>
       </c>
       <c r="E65" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F65" t="s">
         <v>10</v>
@@ -2771,7 +2808,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C66" t="s">
         <v>17</v>
@@ -2780,7 +2817,7 @@
         <v>20260609</v>
       </c>
       <c r="E66" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F66" t="s">
         <v>10</v>
@@ -2791,7 +2828,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C67" t="s">
         <v>17</v>
@@ -2800,7 +2837,7 @@
         <v>20260609</v>
       </c>
       <c r="E67" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F67" t="s">
         <v>10</v>
@@ -2811,7 +2848,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C68" t="s">
         <v>17</v>
@@ -2820,7 +2857,7 @@
         <v>20260609</v>
       </c>
       <c r="E68" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F68" t="s">
         <v>10</v>
@@ -2831,7 +2868,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C69" t="s">
         <v>17</v>
@@ -2840,7 +2877,7 @@
         <v>20260609</v>
       </c>
       <c r="E69" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F69" t="s">
         <v>10</v>
@@ -2851,7 +2888,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C70" t="s">
         <v>17</v>
@@ -2860,7 +2897,7 @@
         <v>20260609</v>
       </c>
       <c r="E70" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F70" t="s">
         <v>10</v>
@@ -2871,7 +2908,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C71" t="s">
         <v>17</v>
@@ -2880,7 +2917,7 @@
         <v>20260609</v>
       </c>
       <c r="E71" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F71" t="s">
         <v>10</v>
@@ -2891,7 +2928,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C72" t="s">
         <v>17</v>
@@ -2900,7 +2937,7 @@
         <v>20260609</v>
       </c>
       <c r="E72" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F72" t="s">
         <v>10</v>
@@ -2911,7 +2948,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
@@ -2920,7 +2957,7 @@
         <v>20260609</v>
       </c>
       <c r="E73" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F73" t="s">
         <v>10</v>
@@ -2931,7 +2968,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C74" t="s">
         <v>17</v>
@@ -2940,7 +2977,7 @@
         <v>20260609</v>
       </c>
       <c r="E74" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F74" t="s">
         <v>10</v>
@@ -2951,16 +2988,16 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C75" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D75">
         <v>20260609</v>
       </c>
       <c r="E75" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F75" t="s">
         <v>10</v>
@@ -2971,16 +3008,16 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C76" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D76">
         <v>20260609</v>
       </c>
       <c r="E76" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F76" t="s">
         <v>10</v>
@@ -2991,16 +3028,16 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C77" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D77">
         <v>20260609</v>
       </c>
       <c r="E77" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F77" t="s">
         <v>10</v>
@@ -3011,16 +3048,16 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C78" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D78">
         <v>20260609</v>
       </c>
       <c r="E78" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F78" t="s">
         <v>10</v>
@@ -3031,7 +3068,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C79" t="s">
         <v>25</v>
@@ -3040,7 +3077,7 @@
         <v>20260609</v>
       </c>
       <c r="E79" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F79" t="s">
         <v>10</v>
@@ -3051,7 +3088,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C80" t="s">
         <v>25</v>
@@ -3060,7 +3097,7 @@
         <v>20260609</v>
       </c>
       <c r="E80" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F80" t="s">
         <v>10</v>
@@ -3071,7 +3108,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C81" t="s">
         <v>25</v>
@@ -3080,7 +3117,7 @@
         <v>20260609</v>
       </c>
       <c r="E81" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F81" t="s">
         <v>10</v>
@@ -3091,7 +3128,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C82" t="s">
         <v>25</v>
@@ -3100,7 +3137,7 @@
         <v>20260609</v>
       </c>
       <c r="E82" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F82" t="s">
         <v>10</v>
@@ -3111,7 +3148,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C83" t="s">
         <v>25</v>
@@ -3120,7 +3157,7 @@
         <v>20260609</v>
       </c>
       <c r="E83" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F83" t="s">
         <v>10</v>
@@ -3131,7 +3168,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C84" t="s">
         <v>25</v>
@@ -3140,7 +3177,7 @@
         <v>20260609</v>
       </c>
       <c r="E84" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F84" t="s">
         <v>10</v>
@@ -3151,7 +3188,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C85" t="s">
         <v>25</v>
@@ -3160,7 +3197,7 @@
         <v>20260609</v>
       </c>
       <c r="E85" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F85" t="s">
         <v>10</v>
@@ -3171,7 +3208,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C86" t="s">
         <v>25</v>
@@ -3180,7 +3217,7 @@
         <v>20260609</v>
       </c>
       <c r="E86" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F86" t="s">
         <v>10</v>
@@ -3191,7 +3228,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C87" t="s">
         <v>25</v>
@@ -3200,7 +3237,7 @@
         <v>20260609</v>
       </c>
       <c r="E87" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F87" t="s">
         <v>10</v>
@@ -3211,7 +3248,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C88" t="s">
         <v>25</v>
@@ -3220,7 +3257,7 @@
         <v>20260609</v>
       </c>
       <c r="E88" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F88" t="s">
         <v>10</v>
@@ -3231,7 +3268,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C89" t="s">
         <v>25</v>
@@ -3240,7 +3277,7 @@
         <v>20260609</v>
       </c>
       <c r="E89" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F89" t="s">
         <v>10</v>
@@ -3251,7 +3288,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C90" t="s">
         <v>25</v>
@@ -3260,7 +3297,7 @@
         <v>20260609</v>
       </c>
       <c r="E90" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F90" t="s">
         <v>10</v>
@@ -3271,7 +3308,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C91" t="s">
         <v>25</v>
@@ -3280,7 +3317,7 @@
         <v>20260609</v>
       </c>
       <c r="E91" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F91" t="s">
         <v>10</v>
@@ -3291,19 +3328,19 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C92" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D92">
         <v>20260609</v>
       </c>
       <c r="E92" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F92" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3311,7 +3348,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C93" t="s">
         <v>25</v>
@@ -3320,10 +3357,10 @@
         <v>20260609</v>
       </c>
       <c r="E93" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F93" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3331,19 +3368,19 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C94" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D94">
         <v>20260609</v>
       </c>
       <c r="E94" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="F94" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3354,16 +3391,16 @@
         <v>116</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D95">
         <v>20260609</v>
       </c>
       <c r="E95" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="F95" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3371,19 +3408,19 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C96" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D96">
         <v>20260609</v>
       </c>
       <c r="E96" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="F96" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3391,7 +3428,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C97" t="s">
         <v>17</v>
@@ -3400,10 +3437,10 @@
         <v>20260609</v>
       </c>
       <c r="E97" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="F97" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3411,19 +3448,19 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C98" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D98">
         <v>20260609</v>
       </c>
       <c r="E98" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="F98" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3431,19 +3468,19 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C99" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D99">
         <v>20260609</v>
       </c>
       <c r="E99" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="F99" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3451,7 +3488,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C100" t="s">
         <v>17</v>
@@ -3460,10 +3497,10 @@
         <v>20260609</v>
       </c>
       <c r="E100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F100" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3471,19 +3508,19 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C101" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D101">
         <v>20260609</v>
       </c>
       <c r="E101" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F101" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3491,7 +3528,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C102" t="s">
         <v>17</v>
@@ -3500,10 +3537,10 @@
         <v>20260609</v>
       </c>
       <c r="E102" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F102" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3511,19 +3548,19 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C103" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D103">
         <v>20260609</v>
       </c>
       <c r="E103" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F103" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3531,7 +3568,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C104" t="s">
         <v>17</v>
@@ -3540,7 +3577,7 @@
         <v>20260609</v>
       </c>
       <c r="E104" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F104" t="s">
         <v>10</v>
@@ -3560,7 +3597,7 @@
         <v>20260609</v>
       </c>
       <c r="E105" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F105" t="s">
         <v>10</v>
@@ -3580,7 +3617,7 @@
         <v>20260609</v>
       </c>
       <c r="E106" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F106" t="s">
         <v>10</v>
@@ -3600,7 +3637,7 @@
         <v>20260609</v>
       </c>
       <c r="E107" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F107" t="s">
         <v>10</v>
@@ -3620,7 +3657,7 @@
         <v>20260609</v>
       </c>
       <c r="E108" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F108" t="s">
         <v>10</v>
@@ -3640,7 +3677,7 @@
         <v>20260609</v>
       </c>
       <c r="E109" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F109" t="s">
         <v>10</v>
@@ -3660,7 +3697,7 @@
         <v>20260609</v>
       </c>
       <c r="E110" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F110" t="s">
         <v>10</v>
@@ -3680,7 +3717,7 @@
         <v>20260609</v>
       </c>
       <c r="E111" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F111" t="s">
         <v>10</v>
@@ -3694,13 +3731,13 @@
         <v>136</v>
       </c>
       <c r="C112" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D112">
         <v>20260609</v>
       </c>
       <c r="E112" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F112" t="s">
         <v>10</v>
@@ -3714,13 +3751,13 @@
         <v>137</v>
       </c>
       <c r="C113" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D113">
         <v>20260609</v>
       </c>
       <c r="E113" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F113" t="s">
         <v>10</v>
@@ -3734,13 +3771,13 @@
         <v>138</v>
       </c>
       <c r="C114" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D114">
         <v>20260609</v>
       </c>
       <c r="E114" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F114" t="s">
         <v>10</v>
@@ -3754,13 +3791,13 @@
         <v>139</v>
       </c>
       <c r="C115" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D115">
         <v>20260609</v>
       </c>
       <c r="E115" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F115" t="s">
         <v>10</v>
@@ -3774,13 +3811,13 @@
         <v>140</v>
       </c>
       <c r="C116" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D116">
         <v>20260609</v>
       </c>
       <c r="E116" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F116" t="s">
         <v>10</v>
@@ -3794,13 +3831,13 @@
         <v>141</v>
       </c>
       <c r="C117" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D117">
         <v>20260609</v>
       </c>
       <c r="E117" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F117" t="s">
         <v>10</v>
@@ -3814,13 +3851,13 @@
         <v>142</v>
       </c>
       <c r="C118" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D118">
         <v>20260609</v>
       </c>
       <c r="E118" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F118" t="s">
         <v>10</v>
@@ -3840,7 +3877,7 @@
         <v>20260609</v>
       </c>
       <c r="E119" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F119" t="s">
         <v>10</v>
@@ -3860,7 +3897,7 @@
         <v>20260609</v>
       </c>
       <c r="E120" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F120" t="s">
         <v>10</v>
@@ -3880,7 +3917,7 @@
         <v>20260609</v>
       </c>
       <c r="E121" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F121" t="s">
         <v>10</v>
@@ -3900,7 +3937,7 @@
         <v>20260609</v>
       </c>
       <c r="E122" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F122" t="s">
         <v>10</v>
@@ -3920,7 +3957,7 @@
         <v>20260609</v>
       </c>
       <c r="E123" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F123" t="s">
         <v>10</v>
@@ -3940,7 +3977,7 @@
         <v>20260609</v>
       </c>
       <c r="E124" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F124" t="s">
         <v>10</v>
@@ -3960,7 +3997,7 @@
         <v>20260609</v>
       </c>
       <c r="E125" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F125" t="s">
         <v>10</v>
@@ -3980,7 +4017,7 @@
         <v>20260609</v>
       </c>
       <c r="E126" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F126" t="s">
         <v>10</v>
@@ -4000,7 +4037,7 @@
         <v>20260609</v>
       </c>
       <c r="E127" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F127" t="s">
         <v>10</v>
@@ -4020,7 +4057,7 @@
         <v>20260609</v>
       </c>
       <c r="E128" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F128" t="s">
         <v>10</v>
@@ -4040,7 +4077,7 @@
         <v>20260609</v>
       </c>
       <c r="E129" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F129" t="s">
         <v>10</v>
@@ -4054,16 +4091,16 @@
         <v>154</v>
       </c>
       <c r="C130" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D130">
         <v>20260609</v>
       </c>
       <c r="E130" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F130" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4080,10 +4117,10 @@
         <v>20260609</v>
       </c>
       <c r="E131" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F131" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4094,16 +4131,16 @@
         <v>156</v>
       </c>
       <c r="C132" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D132">
         <v>20260609</v>
       </c>
       <c r="E132" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="F132" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4111,7 +4148,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C133" t="s">
         <v>25</v>
@@ -4120,10 +4157,10 @@
         <v>20260609</v>
       </c>
       <c r="E133" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="F133" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4131,19 +4168,19 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C134" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D134">
         <v>20260609</v>
       </c>
       <c r="E134" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="F134" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4151,7 +4188,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C135" t="s">
         <v>25</v>
@@ -4160,10 +4197,10 @@
         <v>20260609</v>
       </c>
       <c r="E135" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="F135" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4171,7 +4208,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C136" t="s">
         <v>17</v>
@@ -4180,7 +4217,7 @@
         <v>20260610</v>
       </c>
       <c r="E136" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F136" t="s">
         <v>10</v>
@@ -4191,7 +4228,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C137" t="s">
         <v>17</v>
@@ -4200,7 +4237,7 @@
         <v>20260610</v>
       </c>
       <c r="E137" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F137" t="s">
         <v>10</v>
@@ -4211,7 +4248,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C138" t="s">
         <v>17</v>
@@ -4220,7 +4257,7 @@
         <v>20260610</v>
       </c>
       <c r="E138" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F138" t="s">
         <v>10</v>
@@ -4231,7 +4268,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
@@ -4240,7 +4277,7 @@
         <v>20260610</v>
       </c>
       <c r="E139" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F139" t="s">
         <v>10</v>
@@ -4251,7 +4288,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
@@ -4260,7 +4297,7 @@
         <v>20260610</v>
       </c>
       <c r="E140" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F140" t="s">
         <v>10</v>
@@ -4271,7 +4308,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
@@ -4280,7 +4317,7 @@
         <v>20260610</v>
       </c>
       <c r="E141" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F141" t="s">
         <v>10</v>
@@ -4291,7 +4328,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C142" t="s">
         <v>17</v>
@@ -4300,7 +4337,7 @@
         <v>20260610</v>
       </c>
       <c r="E142" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F142" t="s">
         <v>10</v>
@@ -4311,7 +4348,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C143" t="s">
         <v>17</v>
@@ -4320,7 +4357,7 @@
         <v>20260610</v>
       </c>
       <c r="E143" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F143" t="s">
         <v>10</v>
@@ -4331,7 +4368,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -4340,7 +4377,7 @@
         <v>20260610</v>
       </c>
       <c r="E144" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F144" t="s">
         <v>10</v>
@@ -4351,7 +4388,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -4360,7 +4397,7 @@
         <v>20260610</v>
       </c>
       <c r="E145" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F145" t="s">
         <v>10</v>
@@ -4371,7 +4408,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
@@ -4380,7 +4417,7 @@
         <v>20260610</v>
       </c>
       <c r="E146" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F146" t="s">
         <v>10</v>
@@ -4391,7 +4428,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
@@ -4400,7 +4437,7 @@
         <v>20260610</v>
       </c>
       <c r="E147" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F147" t="s">
         <v>10</v>
@@ -4411,7 +4448,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
@@ -4420,7 +4457,7 @@
         <v>20260610</v>
       </c>
       <c r="E148" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F148" t="s">
         <v>10</v>
@@ -4431,7 +4468,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
@@ -4440,7 +4477,7 @@
         <v>20260610</v>
       </c>
       <c r="E149" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F149" t="s">
         <v>10</v>
@@ -4451,7 +4488,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C150" t="s">
         <v>17</v>
@@ -4460,7 +4497,7 @@
         <v>20260610</v>
       </c>
       <c r="E150" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F150" t="s">
         <v>10</v>
@@ -4471,7 +4508,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -4480,7 +4517,7 @@
         <v>20260610</v>
       </c>
       <c r="E151" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F151" t="s">
         <v>10</v>
@@ -4491,7 +4528,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C152" t="s">
         <v>17</v>
@@ -4500,7 +4537,7 @@
         <v>20260610</v>
       </c>
       <c r="E152" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F152" t="s">
         <v>10</v>
@@ -4511,7 +4548,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C153" t="s">
         <v>17</v>
@@ -4520,7 +4557,7 @@
         <v>20260610</v>
       </c>
       <c r="E153" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F153" t="s">
         <v>10</v>
@@ -4531,7 +4568,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C154" t="s">
         <v>25</v>
@@ -4540,7 +4577,7 @@
         <v>20260610</v>
       </c>
       <c r="E154" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F154" t="s">
         <v>10</v>
@@ -4551,7 +4588,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C155" t="s">
         <v>25</v>
@@ -4560,7 +4597,7 @@
         <v>20260610</v>
       </c>
       <c r="E155" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F155" t="s">
         <v>10</v>
@@ -4571,7 +4608,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C156" t="s">
         <v>25</v>
@@ -4580,7 +4617,7 @@
         <v>20260610</v>
       </c>
       <c r="E156" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F156" t="s">
         <v>10</v>
@@ -4591,7 +4628,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C157" t="s">
         <v>25</v>
@@ -4600,7 +4637,7 @@
         <v>20260610</v>
       </c>
       <c r="E157" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F157" t="s">
         <v>10</v>
@@ -4611,7 +4648,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C158" t="s">
         <v>25</v>
@@ -4620,7 +4657,7 @@
         <v>20260610</v>
       </c>
       <c r="E158" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F158" t="s">
         <v>10</v>
@@ -4631,7 +4668,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C159" t="s">
         <v>25</v>
@@ -4640,7 +4677,7 @@
         <v>20260610</v>
       </c>
       <c r="E159" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F159" t="s">
         <v>10</v>
@@ -4651,7 +4688,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C160" t="s">
         <v>25</v>
@@ -4660,7 +4697,7 @@
         <v>20260610</v>
       </c>
       <c r="E160" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F160" t="s">
         <v>10</v>
@@ -4671,7 +4708,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C161" t="s">
         <v>25</v>
@@ -4680,7 +4717,7 @@
         <v>20260610</v>
       </c>
       <c r="E161" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F161" t="s">
         <v>10</v>
@@ -4691,7 +4728,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C162" t="s">
         <v>25</v>
@@ -4700,7 +4737,7 @@
         <v>20260610</v>
       </c>
       <c r="E162" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F162" t="s">
         <v>10</v>
@@ -4711,7 +4748,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C163" t="s">
         <v>25</v>
@@ -4720,7 +4757,7 @@
         <v>20260610</v>
       </c>
       <c r="E163" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F163" t="s">
         <v>10</v>
@@ -4731,7 +4768,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C164" t="s">
         <v>25</v>
@@ -4740,7 +4777,7 @@
         <v>20260610</v>
       </c>
       <c r="E164" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F164" t="s">
         <v>10</v>
@@ -4751,7 +4788,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C165" t="s">
         <v>25</v>
@@ -4760,7 +4797,7 @@
         <v>20260610</v>
       </c>
       <c r="E165" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F165" t="s">
         <v>10</v>
@@ -4771,7 +4808,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C166" t="s">
         <v>25</v>
@@ -4780,7 +4817,7 @@
         <v>20260610</v>
       </c>
       <c r="E166" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F166" t="s">
         <v>10</v>
@@ -4791,7 +4828,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C167" t="s">
         <v>25</v>
@@ -4800,7 +4837,7 @@
         <v>20260610</v>
       </c>
       <c r="E167" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F167" t="s">
         <v>10</v>
@@ -4811,7 +4848,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C168" t="s">
         <v>25</v>
@@ -4820,7 +4857,7 @@
         <v>20260610</v>
       </c>
       <c r="E168" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F168" t="s">
         <v>10</v>
@@ -4831,7 +4868,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C169" t="s">
         <v>25</v>
@@ -4840,7 +4877,7 @@
         <v>20260610</v>
       </c>
       <c r="E169" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F169" t="s">
         <v>10</v>
@@ -4851,7 +4888,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C170" t="s">
         <v>25</v>
@@ -4860,7 +4897,7 @@
         <v>20260610</v>
       </c>
       <c r="E170" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F170" t="s">
         <v>10</v>
@@ -4871,7 +4908,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C171" t="s">
         <v>25</v>
@@ -4880,7 +4917,7 @@
         <v>20260610</v>
       </c>
       <c r="E171" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F171" t="s">
         <v>10</v>
@@ -4891,7 +4928,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C172" t="s">
         <v>17</v>
@@ -4900,10 +4937,10 @@
         <v>20260610</v>
       </c>
       <c r="E172" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="F172" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -4911,19 +4948,19 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C173" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D173">
         <v>20260610</v>
       </c>
       <c r="E173" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="F173" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -4931,19 +4968,19 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C174" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D174">
         <v>20260610</v>
       </c>
       <c r="E174" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="F174" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -4951,7 +4988,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C175" t="s">
         <v>17</v>
@@ -4960,7 +4997,7 @@
         <v>20260610</v>
       </c>
       <c r="E175" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F175" t="s">
         <v>10</v>
@@ -4971,7 +5008,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C176" t="s">
         <v>17</v>
@@ -4980,7 +5017,7 @@
         <v>20260610</v>
       </c>
       <c r="E176" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F176" t="s">
         <v>10</v>
@@ -4991,7 +5028,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C177" t="s">
         <v>17</v>
@@ -5000,7 +5037,7 @@
         <v>20260610</v>
       </c>
       <c r="E177" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F177" t="s">
         <v>10</v>
@@ -5011,7 +5048,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C178" t="s">
         <v>17</v>
@@ -5020,7 +5057,7 @@
         <v>20260610</v>
       </c>
       <c r="E178" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F178" t="s">
         <v>10</v>
@@ -5031,7 +5068,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C179" t="s">
         <v>17</v>
@@ -5040,7 +5077,7 @@
         <v>20260610</v>
       </c>
       <c r="E179" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F179" t="s">
         <v>10</v>
@@ -5051,7 +5088,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C180" t="s">
         <v>17</v>
@@ -5060,7 +5097,7 @@
         <v>20260610</v>
       </c>
       <c r="E180" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F180" t="s">
         <v>10</v>
@@ -5071,7 +5108,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C181" t="s">
         <v>17</v>
@@ -5080,7 +5117,7 @@
         <v>20260610</v>
       </c>
       <c r="E181" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F181" t="s">
         <v>10</v>
@@ -5091,7 +5128,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C182" t="s">
         <v>17</v>
@@ -5100,7 +5137,7 @@
         <v>20260610</v>
       </c>
       <c r="E182" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F182" t="s">
         <v>10</v>
@@ -5111,7 +5148,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C183" t="s">
         <v>17</v>
@@ -5120,7 +5157,7 @@
         <v>20260610</v>
       </c>
       <c r="E183" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F183" t="s">
         <v>10</v>
@@ -5131,7 +5168,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C184" t="s">
         <v>17</v>
@@ -5140,7 +5177,7 @@
         <v>20260610</v>
       </c>
       <c r="E184" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F184" t="s">
         <v>10</v>
@@ -5151,16 +5188,16 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C185" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D185">
         <v>20260610</v>
       </c>
       <c r="E185" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F185" t="s">
         <v>10</v>
@@ -5171,16 +5208,16 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C186" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D186">
         <v>20260610</v>
       </c>
       <c r="E186" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F186" t="s">
         <v>10</v>
@@ -5191,16 +5228,16 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C187" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D187">
         <v>20260610</v>
       </c>
       <c r="E187" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F187" t="s">
         <v>10</v>
@@ -5211,7 +5248,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C188" t="s">
         <v>25</v>
@@ -5220,7 +5257,7 @@
         <v>20260610</v>
       </c>
       <c r="E188" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F188" t="s">
         <v>10</v>
@@ -5231,7 +5268,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C189" t="s">
         <v>25</v>
@@ -5240,7 +5277,7 @@
         <v>20260610</v>
       </c>
       <c r="E189" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F189" t="s">
         <v>10</v>
@@ -5251,7 +5288,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C190" t="s">
         <v>25</v>
@@ -5260,7 +5297,7 @@
         <v>20260610</v>
       </c>
       <c r="E190" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F190" t="s">
         <v>10</v>
@@ -5271,7 +5308,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C191" t="s">
         <v>25</v>
@@ -5280,7 +5317,7 @@
         <v>20260610</v>
       </c>
       <c r="E191" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F191" t="s">
         <v>10</v>
@@ -5291,7 +5328,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C192" t="s">
         <v>25</v>
@@ -5300,7 +5337,7 @@
         <v>20260610</v>
       </c>
       <c r="E192" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F192" t="s">
         <v>10</v>
@@ -5311,7 +5348,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C193" t="s">
         <v>25</v>
@@ -5320,7 +5357,7 @@
         <v>20260610</v>
       </c>
       <c r="E193" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F193" t="s">
         <v>10</v>
@@ -5331,7 +5368,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C194" t="s">
         <v>25</v>
@@ -5340,7 +5377,7 @@
         <v>20260610</v>
       </c>
       <c r="E194" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F194" t="s">
         <v>10</v>
@@ -5351,7 +5388,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C195" t="s">
         <v>25</v>
@@ -5360,7 +5397,7 @@
         <v>20260610</v>
       </c>
       <c r="E195" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F195" t="s">
         <v>10</v>
@@ -5371,7 +5408,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C196" t="s">
         <v>25</v>
@@ -5380,7 +5417,7 @@
         <v>20260610</v>
       </c>
       <c r="E196" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F196" t="s">
         <v>10</v>
@@ -5391,7 +5428,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C197" t="s">
         <v>25</v>
@@ -5400,7 +5437,7 @@
         <v>20260610</v>
       </c>
       <c r="E197" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F197" t="s">
         <v>10</v>
@@ -5411,7 +5448,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C198" t="s">
         <v>25</v>
@@ -5420,7 +5457,7 @@
         <v>20260610</v>
       </c>
       <c r="E198" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F198" t="s">
         <v>10</v>
@@ -5431,7 +5468,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C199" t="s">
         <v>25</v>
@@ -5440,7 +5477,7 @@
         <v>20260610</v>
       </c>
       <c r="E199" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F199" t="s">
         <v>10</v>
@@ -5451,7 +5488,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C200" t="s">
         <v>25</v>
@@ -5460,7 +5497,7 @@
         <v>20260610</v>
       </c>
       <c r="E200" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F200" t="s">
         <v>10</v>
@@ -5471,7 +5508,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C201" t="s">
         <v>25</v>
@@ -5480,7 +5517,7 @@
         <v>20260610</v>
       </c>
       <c r="E201" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F201" t="s">
         <v>10</v>
@@ -5491,7 +5528,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C202" t="s">
         <v>25</v>
@@ -5500,7 +5537,7 @@
         <v>20260610</v>
       </c>
       <c r="E202" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F202" t="s">
         <v>10</v>
@@ -5511,19 +5548,19 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C203" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D203">
         <v>20260610</v>
       </c>
       <c r="E203" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="F203" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -5531,7 +5568,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C204" t="s">
         <v>25</v>
@@ -5540,10 +5577,10 @@
         <v>20260610</v>
       </c>
       <c r="E204" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="F204" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -5551,19 +5588,19 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C205" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D205">
         <v>20260610</v>
       </c>
       <c r="E205" t="s">
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="F205" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -5571,16 +5608,16 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C206" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D206">
         <v>20260610</v>
       </c>
       <c r="E206" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F206" t="s">
         <v>43</v>
@@ -5591,16 +5628,16 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C207" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D207">
         <v>20260610</v>
       </c>
       <c r="E207" t="s">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="F207" t="s">
         <v>43</v>
@@ -5611,16 +5648,16 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C208" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D208">
         <v>20260610</v>
       </c>
       <c r="E208" t="s">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="F208" t="s">
         <v>43</v>
@@ -5631,7 +5668,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C209" t="s">
         <v>17</v>
@@ -5640,10 +5677,10 @@
         <v>20260610</v>
       </c>
       <c r="E209" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F209" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -5651,7 +5688,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C210" t="s">
         <v>25</v>
@@ -5660,10 +5697,10 @@
         <v>20260610</v>
       </c>
       <c r="E210" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F210" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -5671,7 +5708,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C211" t="s">
         <v>17</v>
@@ -5680,10 +5717,10 @@
         <v>20260610</v>
       </c>
       <c r="E211" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F211" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -5691,7 +5728,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C212" t="s">
         <v>25</v>
@@ -5700,10 +5737,10 @@
         <v>20260610</v>
       </c>
       <c r="E212" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F212" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -5711,7 +5748,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C213" t="s">
         <v>17</v>
@@ -5720,7 +5757,7 @@
         <v>20260611</v>
       </c>
       <c r="E213" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F213" t="s">
         <v>10</v>
@@ -5731,7 +5768,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C214" t="s">
         <v>17</v>
@@ -5740,7 +5777,7 @@
         <v>20260611</v>
       </c>
       <c r="E214" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F214" t="s">
         <v>10</v>
@@ -5751,7 +5788,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C215" t="s">
         <v>17</v>
@@ -5760,7 +5797,7 @@
         <v>20260611</v>
       </c>
       <c r="E215" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F215" t="s">
         <v>10</v>
@@ -5771,7 +5808,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C216" t="s">
         <v>17</v>
@@ -5780,7 +5817,7 @@
         <v>20260611</v>
       </c>
       <c r="E216" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F216" t="s">
         <v>10</v>
@@ -5791,7 +5828,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C217" t="s">
         <v>17</v>
@@ -5800,7 +5837,7 @@
         <v>20260611</v>
       </c>
       <c r="E217" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F217" t="s">
         <v>10</v>
@@ -5811,7 +5848,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C218" t="s">
         <v>17</v>
@@ -5820,7 +5857,7 @@
         <v>20260611</v>
       </c>
       <c r="E218" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F218" t="s">
         <v>10</v>
@@ -5831,16 +5868,16 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
+        <v>254</v>
+      </c>
+      <c r="C219" t="s">
+        <v>17</v>
+      </c>
+      <c r="D219">
+        <v>20260611</v>
+      </c>
+      <c r="E219" t="s">
         <v>248</v>
-      </c>
-      <c r="C219" t="s">
-        <v>17</v>
-      </c>
-      <c r="D219">
-        <v>20260611</v>
-      </c>
-      <c r="E219" t="s">
-        <v>242</v>
       </c>
       <c r="F219" t="s">
         <v>10</v>
@@ -5851,7 +5888,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C220" t="s">
         <v>17</v>
@@ -5860,7 +5897,7 @@
         <v>20260611</v>
       </c>
       <c r="E220" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F220" t="s">
         <v>10</v>
@@ -5871,7 +5908,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C221" t="s">
         <v>17</v>
@@ -5880,7 +5917,7 @@
         <v>20260611</v>
       </c>
       <c r="E221" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F221" t="s">
         <v>10</v>
@@ -5891,7 +5928,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C222" t="s">
         <v>17</v>
@@ -5900,7 +5937,7 @@
         <v>20260611</v>
       </c>
       <c r="E222" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F222" t="s">
         <v>10</v>
@@ -5911,7 +5948,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C223" t="s">
         <v>17</v>
@@ -5920,7 +5957,7 @@
         <v>20260611</v>
       </c>
       <c r="E223" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F223" t="s">
         <v>10</v>
@@ -5931,7 +5968,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C224" t="s">
         <v>17</v>
@@ -5940,7 +5977,7 @@
         <v>20260611</v>
       </c>
       <c r="E224" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F224" t="s">
         <v>10</v>
@@ -5951,7 +5988,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C225" t="s">
         <v>17</v>
@@ -5960,7 +5997,7 @@
         <v>20260611</v>
       </c>
       <c r="E225" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F225" t="s">
         <v>10</v>
@@ -5971,7 +6008,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C226" t="s">
         <v>17</v>
@@ -5980,7 +6017,7 @@
         <v>20260611</v>
       </c>
       <c r="E226" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F226" t="s">
         <v>10</v>
@@ -5991,7 +6028,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C227" t="s">
         <v>17</v>
@@ -6000,7 +6037,7 @@
         <v>20260611</v>
       </c>
       <c r="E227" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F227" t="s">
         <v>10</v>
@@ -6011,7 +6048,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C228" t="s">
         <v>17</v>
@@ -6020,7 +6057,7 @@
         <v>20260611</v>
       </c>
       <c r="E228" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F228" t="s">
         <v>10</v>
@@ -6031,7 +6068,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C229" t="s">
         <v>17</v>
@@ -6040,7 +6077,7 @@
         <v>20260611</v>
       </c>
       <c r="E229" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F229" t="s">
         <v>10</v>
@@ -6051,7 +6088,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C230" t="s">
         <v>17</v>
@@ -6060,7 +6097,7 @@
         <v>20260611</v>
       </c>
       <c r="E230" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F230" t="s">
         <v>10</v>
@@ -6071,7 +6108,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C231" t="s">
         <v>17</v>
@@ -6080,7 +6117,7 @@
         <v>20260611</v>
       </c>
       <c r="E231" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F231" t="s">
         <v>10</v>
@@ -6091,7 +6128,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C232" t="s">
         <v>17</v>
@@ -6100,7 +6137,7 @@
         <v>20260611</v>
       </c>
       <c r="E232" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F232" t="s">
         <v>10</v>
@@ -6111,7 +6148,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C233" t="s">
         <v>25</v>
@@ -6120,7 +6157,7 @@
         <v>20260611</v>
       </c>
       <c r="E233" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F233" t="s">
         <v>10</v>
@@ -6131,7 +6168,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C234" t="s">
         <v>25</v>
@@ -6140,7 +6177,7 @@
         <v>20260611</v>
       </c>
       <c r="E234" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F234" t="s">
         <v>10</v>
@@ -6151,7 +6188,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C235" t="s">
         <v>25</v>
@@ -6160,7 +6197,7 @@
         <v>20260611</v>
       </c>
       <c r="E235" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F235" t="s">
         <v>10</v>
@@ -6171,7 +6208,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C236" t="s">
         <v>25</v>
@@ -6180,7 +6217,7 @@
         <v>20260611</v>
       </c>
       <c r="E236" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F236" t="s">
         <v>10</v>
@@ -6191,7 +6228,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C237" t="s">
         <v>25</v>
@@ -6200,7 +6237,7 @@
         <v>20260611</v>
       </c>
       <c r="E237" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F237" t="s">
         <v>10</v>
@@ -6211,7 +6248,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C238" t="s">
         <v>25</v>
@@ -6220,7 +6257,7 @@
         <v>20260611</v>
       </c>
       <c r="E238" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F238" t="s">
         <v>10</v>
@@ -6231,7 +6268,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C239" t="s">
         <v>25</v>
@@ -6240,7 +6277,7 @@
         <v>20260611</v>
       </c>
       <c r="E239" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F239" t="s">
         <v>10</v>
@@ -6251,7 +6288,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C240" t="s">
         <v>25</v>
@@ -6260,7 +6297,7 @@
         <v>20260611</v>
       </c>
       <c r="E240" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F240" t="s">
         <v>10</v>
@@ -6271,7 +6308,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C241" t="s">
         <v>25</v>
@@ -6280,7 +6317,7 @@
         <v>20260611</v>
       </c>
       <c r="E241" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F241" t="s">
         <v>10</v>
@@ -6291,7 +6328,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C242" t="s">
         <v>25</v>
@@ -6300,7 +6337,7 @@
         <v>20260611</v>
       </c>
       <c r="E242" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F242" t="s">
         <v>10</v>
@@ -6311,7 +6348,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C243" t="s">
         <v>25</v>
@@ -6320,7 +6357,7 @@
         <v>20260611</v>
       </c>
       <c r="E243" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F243" t="s">
         <v>10</v>
@@ -6331,7 +6368,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C244" t="s">
         <v>25</v>
@@ -6340,7 +6377,7 @@
         <v>20260611</v>
       </c>
       <c r="E244" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F244" t="s">
         <v>10</v>
@@ -6351,7 +6388,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C245" t="s">
         <v>25</v>
@@ -6360,7 +6397,7 @@
         <v>20260611</v>
       </c>
       <c r="E245" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F245" t="s">
         <v>10</v>
@@ -6371,7 +6408,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C246" t="s">
         <v>25</v>
@@ -6380,7 +6417,7 @@
         <v>20260611</v>
       </c>
       <c r="E246" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F246" t="s">
         <v>10</v>
@@ -6391,7 +6428,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C247" t="s">
         <v>25</v>
@@ -6400,7 +6437,7 @@
         <v>20260611</v>
       </c>
       <c r="E247" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F247" t="s">
         <v>10</v>
@@ -6411,7 +6448,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C248" t="s">
         <v>25</v>
@@ -6420,7 +6457,7 @@
         <v>20260611</v>
       </c>
       <c r="E248" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F248" t="s">
         <v>10</v>
@@ -6431,7 +6468,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C249" t="s">
         <v>25</v>
@@ -6440,7 +6477,7 @@
         <v>20260611</v>
       </c>
       <c r="E249" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F249" t="s">
         <v>10</v>
@@ -6451,7 +6488,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C250" t="s">
         <v>25</v>
@@ -6460,7 +6497,7 @@
         <v>20260611</v>
       </c>
       <c r="E250" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F250" t="s">
         <v>10</v>
@@ -6471,7 +6508,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C251" t="s">
         <v>25</v>
@@ -6480,7 +6517,7 @@
         <v>20260611</v>
       </c>
       <c r="E251" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F251" t="s">
         <v>10</v>
@@ -6491,19 +6528,19 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C252" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D252">
         <v>20260611</v>
       </c>
       <c r="E252" t="s">
-        <v>242</v>
+        <v>288</v>
       </c>
       <c r="F252" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -6511,19 +6548,19 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C253" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D253">
         <v>20260611</v>
       </c>
       <c r="E253" t="s">
-        <v>242</v>
+        <v>288</v>
       </c>
       <c r="F253" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -6531,19 +6568,19 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C254" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D254">
         <v>20260611</v>
       </c>
       <c r="E254" t="s">
-        <v>242</v>
+        <v>288</v>
       </c>
       <c r="F254" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -6551,16 +6588,16 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C255" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D255">
         <v>20260611</v>
       </c>
       <c r="E255" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F255" t="s">
         <v>10</v>
@@ -6571,7 +6608,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C256" t="s">
         <v>17</v>
@@ -6580,7 +6617,7 @@
         <v>20260611</v>
       </c>
       <c r="E256" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F256" t="s">
         <v>10</v>
@@ -6591,7 +6628,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C257" t="s">
         <v>17</v>
@@ -6600,7 +6637,7 @@
         <v>20260611</v>
       </c>
       <c r="E257" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F257" t="s">
         <v>10</v>
@@ -6611,16 +6648,16 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
+        <v>294</v>
+      </c>
+      <c r="C258" t="s">
+        <v>17</v>
+      </c>
+      <c r="D258">
+        <v>20260611</v>
+      </c>
+      <c r="E258" t="s">
         <v>288</v>
-      </c>
-      <c r="C258" t="s">
-        <v>17</v>
-      </c>
-      <c r="D258">
-        <v>20260611</v>
-      </c>
-      <c r="E258" t="s">
-        <v>285</v>
       </c>
       <c r="F258" t="s">
         <v>10</v>
@@ -6631,7 +6668,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C259" t="s">
         <v>17</v>
@@ -6640,7 +6677,7 @@
         <v>20260611</v>
       </c>
       <c r="E259" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F259" t="s">
         <v>10</v>
@@ -6651,7 +6688,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C260" t="s">
         <v>17</v>
@@ -6660,7 +6697,7 @@
         <v>20260611</v>
       </c>
       <c r="E260" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F260" t="s">
         <v>10</v>
@@ -6671,7 +6708,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C261" t="s">
         <v>17</v>
@@ -6680,7 +6717,7 @@
         <v>20260611</v>
       </c>
       <c r="E261" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F261" t="s">
         <v>10</v>
@@ -6691,7 +6728,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C262" t="s">
         <v>17</v>
@@ -6700,7 +6737,7 @@
         <v>20260611</v>
       </c>
       <c r="E262" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F262" t="s">
         <v>10</v>
@@ -6711,7 +6748,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C263" t="s">
         <v>17</v>
@@ -6720,7 +6757,7 @@
         <v>20260611</v>
       </c>
       <c r="E263" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F263" t="s">
         <v>10</v>
@@ -6731,7 +6768,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C264" t="s">
         <v>17</v>
@@ -6740,7 +6777,7 @@
         <v>20260611</v>
       </c>
       <c r="E264" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F264" t="s">
         <v>10</v>
@@ -6751,7 +6788,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C265" t="s">
         <v>17</v>
@@ -6760,7 +6797,7 @@
         <v>20260611</v>
       </c>
       <c r="E265" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F265" t="s">
         <v>10</v>
@@ -6771,7 +6808,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C266" t="s">
         <v>17</v>
@@ -6780,7 +6817,7 @@
         <v>20260611</v>
       </c>
       <c r="E266" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F266" t="s">
         <v>10</v>
@@ -6791,7 +6828,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C267" t="s">
         <v>17</v>
@@ -6800,7 +6837,7 @@
         <v>20260611</v>
       </c>
       <c r="E267" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F267" t="s">
         <v>10</v>
@@ -6811,7 +6848,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C268" t="s">
         <v>17</v>
@@ -6820,7 +6857,7 @@
         <v>20260611</v>
       </c>
       <c r="E268" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F268" t="s">
         <v>10</v>
@@ -6831,7 +6868,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C269" t="s">
         <v>17</v>
@@ -6840,7 +6877,7 @@
         <v>20260611</v>
       </c>
       <c r="E269" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F269" t="s">
         <v>10</v>
@@ -6851,7 +6888,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C270" t="s">
         <v>17</v>
@@ -6860,7 +6897,7 @@
         <v>20260611</v>
       </c>
       <c r="E270" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F270" t="s">
         <v>10</v>
@@ -6871,7 +6908,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C271" t="s">
         <v>17</v>
@@ -6880,7 +6917,7 @@
         <v>20260611</v>
       </c>
       <c r="E271" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F271" t="s">
         <v>10</v>
@@ -6891,16 +6928,16 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C272" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D272">
         <v>20260611</v>
       </c>
       <c r="E272" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F272" t="s">
         <v>10</v>
@@ -6911,16 +6948,16 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C273" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D273">
         <v>20260611</v>
       </c>
       <c r="E273" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F273" t="s">
         <v>10</v>
@@ -6931,16 +6968,16 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C274" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D274">
         <v>20260611</v>
       </c>
       <c r="E274" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F274" t="s">
         <v>10</v>
@@ -6951,7 +6988,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C275" t="s">
         <v>25</v>
@@ -6960,7 +6997,7 @@
         <v>20260611</v>
       </c>
       <c r="E275" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F275" t="s">
         <v>10</v>
@@ -6971,7 +7008,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C276" t="s">
         <v>25</v>
@@ -6980,7 +7017,7 @@
         <v>20260611</v>
       </c>
       <c r="E276" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F276" t="s">
         <v>10</v>
@@ -6991,7 +7028,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C277" t="s">
         <v>25</v>
@@ -7000,7 +7037,7 @@
         <v>20260611</v>
       </c>
       <c r="E277" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F277" t="s">
         <v>10</v>
@@ -7011,7 +7048,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C278" t="s">
         <v>25</v>
@@ -7020,7 +7057,7 @@
         <v>20260611</v>
       </c>
       <c r="E278" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F278" t="s">
         <v>10</v>
@@ -7031,7 +7068,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C279" t="s">
         <v>25</v>
@@ -7040,7 +7077,7 @@
         <v>20260611</v>
       </c>
       <c r="E279" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F279" t="s">
         <v>10</v>
@@ -7051,7 +7088,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C280" t="s">
         <v>25</v>
@@ -7060,7 +7097,7 @@
         <v>20260611</v>
       </c>
       <c r="E280" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F280" t="s">
         <v>10</v>
@@ -7071,7 +7108,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C281" t="s">
         <v>25</v>
@@ -7080,7 +7117,7 @@
         <v>20260611</v>
       </c>
       <c r="E281" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F281" t="s">
         <v>10</v>
@@ -7091,7 +7128,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C282" t="s">
         <v>25</v>
@@ -7100,7 +7137,7 @@
         <v>20260611</v>
       </c>
       <c r="E282" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F282" t="s">
         <v>10</v>
@@ -7111,7 +7148,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C283" t="s">
         <v>25</v>
@@ -7120,7 +7157,7 @@
         <v>20260611</v>
       </c>
       <c r="E283" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F283" t="s">
         <v>10</v>
@@ -7131,7 +7168,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C284" t="s">
         <v>25</v>
@@ -7140,7 +7177,7 @@
         <v>20260611</v>
       </c>
       <c r="E284" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F284" t="s">
         <v>10</v>
@@ -7151,7 +7188,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C285" t="s">
         <v>25</v>
@@ -7160,7 +7197,7 @@
         <v>20260611</v>
       </c>
       <c r="E285" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F285" t="s">
         <v>10</v>
@@ -7171,7 +7208,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C286" t="s">
         <v>25</v>
@@ -7180,7 +7217,7 @@
         <v>20260611</v>
       </c>
       <c r="E286" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F286" t="s">
         <v>10</v>
@@ -7191,7 +7228,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C287" t="s">
         <v>25</v>
@@ -7200,7 +7237,7 @@
         <v>20260611</v>
       </c>
       <c r="E287" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F287" t="s">
         <v>10</v>
@@ -7211,7 +7248,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C288" t="s">
         <v>25</v>
@@ -7220,7 +7257,7 @@
         <v>20260611</v>
       </c>
       <c r="E288" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F288" t="s">
         <v>10</v>
@@ -7231,7 +7268,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C289" t="s">
         <v>25</v>
@@ -7240,7 +7277,7 @@
         <v>20260611</v>
       </c>
       <c r="E289" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F289" t="s">
         <v>10</v>
@@ -7251,7 +7288,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C290" t="s">
         <v>25</v>
@@ -7260,7 +7297,7 @@
         <v>20260611</v>
       </c>
       <c r="E290" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F290" t="s">
         <v>10</v>
@@ -7271,7 +7308,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C291" t="s">
         <v>25</v>
@@ -7280,7 +7317,7 @@
         <v>20260611</v>
       </c>
       <c r="E291" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F291" t="s">
         <v>10</v>
@@ -7291,19 +7328,19 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C292" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D292">
         <v>20260611</v>
       </c>
       <c r="E292" t="s">
-        <v>285</v>
+        <v>329</v>
       </c>
       <c r="F292" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -7311,7 +7348,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C293" t="s">
         <v>25</v>
@@ -7320,10 +7357,10 @@
         <v>20260611</v>
       </c>
       <c r="E293" t="s">
-        <v>285</v>
+        <v>329</v>
       </c>
       <c r="F293" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -7331,19 +7368,19 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C294" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D294">
         <v>20260611</v>
       </c>
       <c r="E294" t="s">
-        <v>285</v>
+        <v>332</v>
       </c>
       <c r="F294" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -7351,16 +7388,16 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C295" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D295">
         <v>20260611</v>
       </c>
       <c r="E295" t="s">
-        <v>285</v>
+        <v>334</v>
       </c>
       <c r="F295" t="s">
         <v>43</v>
@@ -7371,16 +7408,16 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C296" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D296">
         <v>20260611</v>
       </c>
       <c r="E296" t="s">
-        <v>285</v>
+        <v>336</v>
       </c>
       <c r="F296" t="s">
         <v>43</v>
@@ -7391,16 +7428,16 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C297" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D297">
         <v>20260611</v>
       </c>
       <c r="E297" t="s">
-        <v>285</v>
+        <v>336</v>
       </c>
       <c r="F297" t="s">
         <v>43</v>
@@ -7411,7 +7448,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C298" t="s">
         <v>17</v>
@@ -7420,10 +7457,10 @@
         <v>20260611</v>
       </c>
       <c r="E298" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="F298" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -7431,7 +7468,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C299" t="s">
         <v>25</v>
@@ -7440,10 +7477,10 @@
         <v>20260611</v>
       </c>
       <c r="E299" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="F299" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -7451,7 +7488,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="C300" t="s">
         <v>17</v>
@@ -7460,10 +7497,10 @@
         <v>20260611</v>
       </c>
       <c r="E300" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="F300" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -7471,7 +7508,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C301" t="s">
         <v>25</v>
@@ -7480,10 +7517,10 @@
         <v>20260611</v>
       </c>
       <c r="E301" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="F301" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -7491,7 +7528,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="C302" t="s">
         <v>17</v>
@@ -7500,7 +7537,7 @@
         <v>20260612</v>
       </c>
       <c r="E302" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F302" t="s">
         <v>10</v>
@@ -7511,7 +7548,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C303" t="s">
         <v>17</v>
@@ -7520,7 +7557,7 @@
         <v>20260612</v>
       </c>
       <c r="E303" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F303" t="s">
         <v>10</v>
@@ -7531,7 +7568,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="C304" t="s">
         <v>17</v>
@@ -7540,7 +7577,7 @@
         <v>20260612</v>
       </c>
       <c r="E304" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F304" t="s">
         <v>10</v>
@@ -7551,7 +7588,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="C305" t="s">
         <v>17</v>
@@ -7560,7 +7597,7 @@
         <v>20260612</v>
       </c>
       <c r="E305" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F305" t="s">
         <v>10</v>
@@ -7571,7 +7608,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="C306" t="s">
         <v>17</v>
@@ -7580,7 +7617,7 @@
         <v>20260612</v>
       </c>
       <c r="E306" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F306" t="s">
         <v>10</v>
@@ -7591,7 +7628,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="C307" t="s">
         <v>17</v>
@@ -7600,7 +7637,7 @@
         <v>20260612</v>
       </c>
       <c r="E307" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F307" t="s">
         <v>10</v>
@@ -7611,7 +7648,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="C308" t="s">
         <v>17</v>
@@ -7620,7 +7657,7 @@
         <v>20260612</v>
       </c>
       <c r="E308" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F308" t="s">
         <v>10</v>
@@ -7631,7 +7668,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="C309" t="s">
         <v>17</v>
@@ -7640,7 +7677,7 @@
         <v>20260612</v>
       </c>
       <c r="E309" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F309" t="s">
         <v>10</v>
@@ -7651,7 +7688,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="C310" t="s">
         <v>17</v>
@@ -7660,7 +7697,7 @@
         <v>20260612</v>
       </c>
       <c r="E310" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F310" t="s">
         <v>10</v>
@@ -7671,7 +7708,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="C311" t="s">
         <v>17</v>
@@ -7680,7 +7717,7 @@
         <v>20260612</v>
       </c>
       <c r="E311" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F311" t="s">
         <v>10</v>
@@ -7691,7 +7728,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C312" t="s">
         <v>17</v>
@@ -7700,7 +7737,7 @@
         <v>20260612</v>
       </c>
       <c r="E312" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F312" t="s">
         <v>10</v>
@@ -7711,7 +7748,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="C313" t="s">
         <v>17</v>
@@ -7720,7 +7757,7 @@
         <v>20260612</v>
       </c>
       <c r="E313" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F313" t="s">
         <v>10</v>
@@ -7731,7 +7768,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="C314" t="s">
         <v>17</v>
@@ -7740,7 +7777,7 @@
         <v>20260612</v>
       </c>
       <c r="E314" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F314" t="s">
         <v>10</v>
@@ -7751,7 +7788,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="C315" t="s">
         <v>17</v>
@@ -7760,7 +7797,7 @@
         <v>20260612</v>
       </c>
       <c r="E315" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F315" t="s">
         <v>10</v>
@@ -7771,7 +7808,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="C316" t="s">
         <v>17</v>
@@ -7780,7 +7817,7 @@
         <v>20260612</v>
       </c>
       <c r="E316" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F316" t="s">
         <v>10</v>
@@ -7791,7 +7828,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="C317" t="s">
         <v>17</v>
@@ -7800,7 +7837,7 @@
         <v>20260612</v>
       </c>
       <c r="E317" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F317" t="s">
         <v>10</v>
@@ -7811,7 +7848,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="C318" t="s">
         <v>17</v>
@@ -7820,7 +7857,7 @@
         <v>20260612</v>
       </c>
       <c r="E318" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F318" t="s">
         <v>10</v>
@@ -7831,7 +7868,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="C319" t="s">
         <v>17</v>
@@ -7840,7 +7877,7 @@
         <v>20260612</v>
       </c>
       <c r="E319" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F319" t="s">
         <v>10</v>
@@ -7851,7 +7888,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="C320" t="s">
         <v>17</v>
@@ -7860,7 +7897,7 @@
         <v>20260612</v>
       </c>
       <c r="E320" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F320" t="s">
         <v>10</v>
@@ -7871,7 +7908,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="C321" t="s">
         <v>25</v>
@@ -7880,7 +7917,7 @@
         <v>20260612</v>
       </c>
       <c r="E321" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F321" t="s">
         <v>10</v>
@@ -7891,7 +7928,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="C322" t="s">
         <v>25</v>
@@ -7900,7 +7937,7 @@
         <v>20260612</v>
       </c>
       <c r="E322" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F322" t="s">
         <v>10</v>
@@ -7911,7 +7948,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="C323" t="s">
         <v>25</v>
@@ -7920,7 +7957,7 @@
         <v>20260612</v>
       </c>
       <c r="E323" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F323" t="s">
         <v>10</v>
@@ -7931,7 +7968,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="C324" t="s">
         <v>25</v>
@@ -7940,7 +7977,7 @@
         <v>20260612</v>
       </c>
       <c r="E324" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F324" t="s">
         <v>10</v>
@@ -7951,7 +7988,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C325" t="s">
         <v>25</v>
@@ -7960,7 +7997,7 @@
         <v>20260612</v>
       </c>
       <c r="E325" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F325" t="s">
         <v>10</v>
@@ -7971,7 +8008,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="C326" t="s">
         <v>25</v>
@@ -7980,7 +8017,7 @@
         <v>20260612</v>
       </c>
       <c r="E326" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F326" t="s">
         <v>10</v>
@@ -7991,7 +8028,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C327" t="s">
         <v>25</v>
@@ -8000,7 +8037,7 @@
         <v>20260612</v>
       </c>
       <c r="E327" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F327" t="s">
         <v>10</v>
@@ -8011,7 +8048,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="C328" t="s">
         <v>25</v>
@@ -8020,7 +8057,7 @@
         <v>20260612</v>
       </c>
       <c r="E328" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F328" t="s">
         <v>10</v>
@@ -8031,7 +8068,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="C329" t="s">
         <v>25</v>
@@ -8040,7 +8077,7 @@
         <v>20260612</v>
       </c>
       <c r="E329" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F329" t="s">
         <v>10</v>
@@ -8051,7 +8088,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="C330" t="s">
         <v>25</v>
@@ -8060,7 +8097,7 @@
         <v>20260612</v>
       </c>
       <c r="E330" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F330" t="s">
         <v>10</v>
@@ -8071,7 +8108,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="C331" t="s">
         <v>25</v>
@@ -8080,7 +8117,7 @@
         <v>20260612</v>
       </c>
       <c r="E331" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F331" t="s">
         <v>10</v>
@@ -8091,7 +8128,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="C332" t="s">
         <v>25</v>
@@ -8100,7 +8137,7 @@
         <v>20260612</v>
       </c>
       <c r="E332" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F332" t="s">
         <v>10</v>
@@ -8111,7 +8148,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="C333" t="s">
         <v>25</v>
@@ -8120,7 +8157,7 @@
         <v>20260612</v>
       </c>
       <c r="E333" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F333" t="s">
         <v>10</v>
@@ -8131,7 +8168,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C334" t="s">
         <v>25</v>
@@ -8140,7 +8177,7 @@
         <v>20260612</v>
       </c>
       <c r="E334" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F334" t="s">
         <v>10</v>
@@ -8151,7 +8188,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="C335" t="s">
         <v>25</v>
@@ -8160,7 +8197,7 @@
         <v>20260612</v>
       </c>
       <c r="E335" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F335" t="s">
         <v>10</v>
@@ -8171,7 +8208,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="C336" t="s">
         <v>25</v>
@@ -8180,7 +8217,7 @@
         <v>20260612</v>
       </c>
       <c r="E336" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F336" t="s">
         <v>10</v>
@@ -8191,7 +8228,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="C337" t="s">
         <v>25</v>
@@ -8200,7 +8237,7 @@
         <v>20260612</v>
       </c>
       <c r="E337" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F337" t="s">
         <v>10</v>
@@ -8211,7 +8248,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="C338" t="s">
         <v>25</v>
@@ -8220,7 +8257,7 @@
         <v>20260612</v>
       </c>
       <c r="E338" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F338" t="s">
         <v>10</v>
@@ -8231,7 +8268,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="C339" t="s">
         <v>25</v>
@@ -8240,7 +8277,7 @@
         <v>20260612</v>
       </c>
       <c r="E339" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F339" t="s">
         <v>10</v>
@@ -8251,7 +8288,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C340" t="s">
         <v>25</v>
@@ -8260,13 +8297,14 @@
         <v>20260612</v>
       </c>
       <c r="E340" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F340" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:F340" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
